--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MonsterData!$A$3:$M$83</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="179">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,12 +64,6 @@
     <t>monsterDescription</t>
   </si>
   <si>
-    <t>monsterSource</t>
-  </si>
-  <si>
-    <t>objName</t>
-  </si>
-  <si>
     <t>skills</t>
   </si>
   <si>
@@ -87,7 +85,564 @@
     <t>测试怪物</t>
   </si>
   <si>
-    <t>Slime</t>
+    <t>抱石溪蛙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翼耳兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿狼枪兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豺狼兽人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿毛龟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忍者龟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风之精灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功夫青蛙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长颈兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩蚁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼蝠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩石史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>粘液史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石中剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地下鱼人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穴居怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩石精灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蚁王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石巨人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小毒菇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤蔓怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼虎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷路怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拟草兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狮蛇兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森林兽人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿皮怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹦鹉螺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贼鸥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海盗鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄居蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝鳄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水之精灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨齿鲨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螺巨人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水族枪兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棕熊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛头巨人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>氏族首领</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖叫仙人掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄生兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金蚂蚁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马面恶灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛头恶灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邪恶宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰狼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰熊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦魇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅咒师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨狼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血鬼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜鳄鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜狼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔之眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰牛怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扭曲僵尸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻蝠王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰元素恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monsters_113</t>
+  </si>
+  <si>
+    <t>Monsters_133</t>
+  </si>
+  <si>
+    <t>Monsters_134</t>
+  </si>
+  <si>
+    <t>Monsters_138</t>
+  </si>
+  <si>
+    <t>Monsters_136</t>
+  </si>
+  <si>
+    <t>Monsters_147</t>
+  </si>
+  <si>
+    <t>Monsters_152</t>
+  </si>
+  <si>
+    <t>Monsters_151</t>
+  </si>
+  <si>
+    <t>Monsters_159</t>
+  </si>
+  <si>
+    <t>Monsters_156</t>
+  </si>
+  <si>
+    <t>Monsters_157</t>
+  </si>
+  <si>
+    <t>Monsters_164</t>
+  </si>
+  <si>
+    <t>Monsters_166</t>
+  </si>
+  <si>
+    <t>Monsters_179</t>
+  </si>
+  <si>
+    <t>Monsters_172</t>
+  </si>
+  <si>
+    <t>Monsters_177</t>
+  </si>
+  <si>
+    <t>Monsters_185</t>
+  </si>
+  <si>
+    <t>Monsters_194</t>
+  </si>
+  <si>
+    <t>Monsters_195</t>
+  </si>
+  <si>
+    <t>Monsters_193</t>
+  </si>
+  <si>
+    <t>Monsters_209</t>
+  </si>
+  <si>
+    <t>Monsters_212</t>
+  </si>
+  <si>
+    <t>Monsters_219</t>
+  </si>
+  <si>
+    <t>Monsters_218</t>
+  </si>
+  <si>
+    <t>Monsters_222</t>
+  </si>
+  <si>
+    <t>Monsters_221</t>
+  </si>
+  <si>
+    <t>Monsters_230</t>
+  </si>
+  <si>
+    <t>Monsters_262</t>
+  </si>
+  <si>
+    <t>Monsters_263</t>
+  </si>
+  <si>
+    <t>Monsters_271</t>
+  </si>
+  <si>
+    <t>Monsters_274</t>
+  </si>
+  <si>
+    <t>Monsters_278</t>
+  </si>
+  <si>
+    <t>Monsters_314</t>
+  </si>
+  <si>
+    <t>Monsters_315</t>
+  </si>
+  <si>
+    <t>Monsters_323</t>
+  </si>
+  <si>
+    <t>Monsters_322</t>
+  </si>
+  <si>
+    <t>Monsters_325</t>
+  </si>
+  <si>
+    <t>Monsters_327</t>
+  </si>
+  <si>
+    <t>Monsters_317</t>
+  </si>
+  <si>
+    <t>Monsters_338</t>
+  </si>
+  <si>
+    <t>Monsters_05</t>
+  </si>
+  <si>
+    <t>Monsters_24</t>
+  </si>
+  <si>
+    <t>Monsters_09</t>
+  </si>
+  <si>
+    <t>Monsters_10</t>
+  </si>
+  <si>
+    <t>Monsters_55</t>
+  </si>
+  <si>
+    <t>Monsters_57</t>
+  </si>
+  <si>
+    <t>Monsters_63</t>
+  </si>
+  <si>
+    <t>Monsters_69</t>
+  </si>
+  <si>
+    <t>Monsters_82</t>
+  </si>
+  <si>
+    <t>Monsters_73</t>
+  </si>
+  <si>
+    <t>Monsters_68</t>
+  </si>
+  <si>
+    <t>Monsters_103</t>
+  </si>
+  <si>
+    <t>Monsters_104</t>
+  </si>
+  <si>
+    <t>Monsters_110</t>
+  </si>
+  <si>
+    <t>Monsters_94</t>
+  </si>
+  <si>
+    <t>Monsters_62</t>
+  </si>
+  <si>
+    <t>Monsters_88</t>
+  </si>
+  <si>
+    <t>Monsters_87</t>
+  </si>
+  <si>
+    <t>Monsters_89</t>
+  </si>
+  <si>
+    <t>Monsters_96</t>
+  </si>
+  <si>
+    <t>Monsters_118</t>
+  </si>
+  <si>
+    <t>Monsters_206</t>
+  </si>
+  <si>
+    <t>Monsters_256</t>
+  </si>
+  <si>
+    <t>Monsters_279</t>
+  </si>
+  <si>
+    <t>Monsters_13</t>
+  </si>
+  <si>
+    <t>Monsters_25</t>
+  </si>
+  <si>
+    <t>Monsters_45</t>
+  </si>
+  <si>
+    <t>Monsters_38</t>
+  </si>
+  <si>
+    <t>Monsters_16</t>
+  </si>
+  <si>
+    <t>Monsters_49</t>
+  </si>
+  <si>
+    <t>Monsters_182</t>
+  </si>
+  <si>
+    <t>Monsters_223</t>
+  </si>
+  <si>
+    <t>Monsters_286</t>
+  </si>
+  <si>
+    <t>Monsters_65</t>
+  </si>
+  <si>
+    <t>Monsters_97</t>
+  </si>
+  <si>
+    <t>Monsters_100</t>
+  </si>
+  <si>
+    <t>Monsters_130</t>
+  </si>
+  <si>
+    <t>Monsters_269</t>
+  </si>
+  <si>
+    <t>Monsters_144</t>
+  </si>
+  <si>
+    <t>SpriteName</t>
+  </si>
+  <si>
+    <t>Monsters_313</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -110,12 +665,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -130,9 +697,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -415,13 +988,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:N4"/>
+  <dimension ref="A2:M83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15.25" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,10 +1025,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>2</v>
@@ -461,11 +1036,8 @@
       <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -491,68 +1063,3315 @@
         <v>11</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>4001</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K4" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4100</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4101</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K6" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>4102</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K7" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>4103</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K8" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>4104</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K9" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>4105</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="1">
-        <v>1002</v>
-      </c>
-      <c r="L4" s="1">
-        <v>20000</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K10" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>4106</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K11" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>4107</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K12" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>4108</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K13" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>4109</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K14" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>4110</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K15" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>4111</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K16" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>4112</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K17" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>4113</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K18" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>4114</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K19" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>4115</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K20" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>4116</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K21" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>4117</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K22" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>4118</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K23" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>4119</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K24" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>4120</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K25" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>4121</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="1">
+        <v>10</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K26" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>4122</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1">
+        <v>10</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K27" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>4123</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="1">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K28" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>4124</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1">
+        <v>10</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>4125</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="1">
+        <v>10</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K30" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>4126</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K31" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>4127</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K32" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>4128</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K33" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>4129</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="1">
+        <v>10</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K34" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>4130</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="1">
+        <v>10</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K35" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>4131</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="1">
+        <v>10</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K36" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>4132</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="1">
+        <v>10</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K37" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>4133</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="1">
+        <v>10</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K38" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>4134</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="1">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K39" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>4135</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="1">
+        <v>10</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K40" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>4136</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="1">
+        <v>10</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1">
+        <v>10</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K41" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>4137</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="1">
+        <v>10</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K42" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>4138</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="1">
+        <v>10</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K43" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>4139</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K44" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>4140</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="1">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K45" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>4141</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="1">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1">
+        <v>10</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K46" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>4142</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="1">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1">
+        <v>10</v>
+      </c>
+      <c r="G47" s="1">
+        <v>10</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K47" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>4143</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>10</v>
+      </c>
+      <c r="G48" s="1">
+        <v>10</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K48" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>4144</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+      <c r="F49" s="1">
+        <v>10</v>
+      </c>
+      <c r="G49" s="1">
+        <v>10</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K49" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>4145</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="1">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1">
+        <v>10</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>4146</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1">
+        <v>10</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K51" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>4147</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>3</v>
+      </c>
+      <c r="F52" s="1">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1">
+        <v>10</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K52" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>4148</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="1">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1">
+        <v>10</v>
+      </c>
+      <c r="G53" s="1">
+        <v>10</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K53" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>4149</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="1">
+        <v>10</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1">
+        <v>10</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K54" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>4150</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="1">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1">
+        <v>10</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K55" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>4151</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
+        <v>10</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K56" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>4152</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="1">
+        <v>10</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1">
+        <v>10</v>
+      </c>
+      <c r="G57" s="1">
+        <v>10</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K57" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>4153</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="1">
+        <v>10</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1">
+        <v>10</v>
+      </c>
+      <c r="G58" s="1">
+        <v>10</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K58" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>4154</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" s="1">
+        <v>10</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2</v>
+      </c>
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1">
+        <v>10</v>
+      </c>
+      <c r="G59" s="1">
+        <v>10</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K59" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>4155</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="1">
+        <v>10</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3</v>
+      </c>
+      <c r="F60" s="1">
+        <v>10</v>
+      </c>
+      <c r="G60" s="1">
+        <v>10</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K60" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>4156</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="1">
+        <v>10</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1">
+        <v>10</v>
+      </c>
+      <c r="G61" s="1">
+        <v>10</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K61" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>4157</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="1">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1">
+        <v>10</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K62" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>4158</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="1">
+        <v>10</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" s="1">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1">
+        <v>10</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K63" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>4159</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="E64" s="1">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1">
+        <v>10</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K64" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>4160</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="1">
+        <v>10</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1">
+        <v>10</v>
+      </c>
+      <c r="G65" s="1">
+        <v>10</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K65" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>4161</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" s="1">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1">
+        <v>10</v>
+      </c>
+      <c r="G66" s="1">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K66" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>4162</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67" s="1">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="E67" s="1">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1">
+        <v>10</v>
+      </c>
+      <c r="G67" s="1">
+        <v>10</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K67" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>4163</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="1">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="E68" s="1">
+        <v>3</v>
+      </c>
+      <c r="F68" s="1">
+        <v>10</v>
+      </c>
+      <c r="G68" s="1">
+        <v>10</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K68" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>4164</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C69" s="1">
+        <v>10</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1">
+        <v>10</v>
+      </c>
+      <c r="G69" s="1">
+        <v>10</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K69" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>4165</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C70" s="1">
+        <v>10</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1">
+        <v>10</v>
+      </c>
+      <c r="G70" s="1">
+        <v>10</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K70" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>4166</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="E71" s="1">
+        <v>3</v>
+      </c>
+      <c r="F71" s="1">
+        <v>10</v>
+      </c>
+      <c r="G71" s="1">
+        <v>10</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K71" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>4167</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" s="1">
+        <v>10</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1">
+        <v>10</v>
+      </c>
+      <c r="G72" s="1">
+        <v>10</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K72" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>4168</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" s="1">
+        <v>10</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1">
+        <v>10</v>
+      </c>
+      <c r="G73" s="1">
+        <v>10</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K73" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>4169</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C74" s="1">
+        <v>10</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+      <c r="F74" s="1">
+        <v>10</v>
+      </c>
+      <c r="G74" s="1">
+        <v>10</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K74" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>4170</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" s="1">
+        <v>10</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+      <c r="E75" s="1">
+        <v>3</v>
+      </c>
+      <c r="F75" s="1">
+        <v>10</v>
+      </c>
+      <c r="G75" s="1">
+        <v>10</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K75" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>4171</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2</v>
+      </c>
+      <c r="E76" s="1">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1">
+        <v>10</v>
+      </c>
+      <c r="G76" s="1">
+        <v>10</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K76" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>4172</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="1">
+        <v>10</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+      <c r="F77" s="1">
+        <v>10</v>
+      </c>
+      <c r="G77" s="1">
+        <v>10</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K77" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>4173</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C78" s="1">
+        <v>10</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+      <c r="E78" s="1">
+        <v>3</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10</v>
+      </c>
+      <c r="G78" s="1">
+        <v>10</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K78" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>4174</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C79" s="1">
+        <v>10</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+      <c r="F79" s="1">
+        <v>10</v>
+      </c>
+      <c r="G79" s="1">
+        <v>10</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K79" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>4175</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="1">
+        <v>10</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
+      </c>
+      <c r="F80" s="1">
+        <v>10</v>
+      </c>
+      <c r="G80" s="1">
+        <v>10</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K80" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>4176</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" s="1">
+        <v>10</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2</v>
+      </c>
+      <c r="E81" s="1">
+        <v>3</v>
+      </c>
+      <c r="F81" s="1">
+        <v>10</v>
+      </c>
+      <c r="G81" s="1">
+        <v>10</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K81" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>4177</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C82" s="1">
+        <v>10</v>
+      </c>
+      <c r="D82" s="1">
+        <v>2</v>
+      </c>
+      <c r="E82" s="1">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K82" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>4178</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83" s="1">
+        <v>10</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2</v>
+      </c>
+      <c r="E83" s="1">
+        <v>3</v>
+      </c>
+      <c r="F83" s="1">
+        <v>10</v>
+      </c>
+      <c r="G83" s="1">
+        <v>10</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K83" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L83" s="1">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:M83"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MonsterData!$A$3:$M$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MonsterData!$A$3:$M$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$U$15:$U$115</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="271">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -912,6 +913,17 @@
   </si>
   <si>
     <t>冰元素恶魔</t>
+  </si>
+  <si>
+    <t>tt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monsters_29</t>
   </si>
 </sst>
 </file>
@@ -934,7 +946,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -968,18 +980,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,17 +1022,26 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1308,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M83"/>
+  <dimension ref="A2:M84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1435,7 +1444,7 @@
         <v>20000</v>
       </c>
       <c r="L4" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="1">
         <v>2</v>
@@ -1476,7 +1485,7 @@
         <v>20000</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="1">
         <v>2</v>
@@ -1517,7 +1526,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="1">
         <v>2</v>
@@ -1558,7 +1567,7 @@
         <v>20000</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" s="1">
         <v>2</v>
@@ -1599,7 +1608,7 @@
         <v>20000</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" s="1">
         <v>2</v>
@@ -1640,7 +1649,7 @@
         <v>20000</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M9" s="1">
         <v>2</v>
@@ -1681,7 +1690,7 @@
         <v>20000</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M10" s="1">
         <v>2</v>
@@ -1722,7 +1731,7 @@
         <v>20000</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M11" s="1">
         <v>2</v>
@@ -1763,7 +1772,7 @@
         <v>20000</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M12" s="1">
         <v>2</v>
@@ -1804,7 +1813,7 @@
         <v>20000</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M13" s="1">
         <v>2</v>
@@ -1845,7 +1854,7 @@
         <v>20000</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M14" s="1">
         <v>2</v>
@@ -1886,7 +1895,7 @@
         <v>20000</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M15" s="1">
         <v>2</v>
@@ -1927,7 +1936,7 @@
         <v>20000</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
@@ -1968,7 +1977,7 @@
         <v>20000</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M17" s="1">
         <v>2</v>
@@ -2009,7 +2018,7 @@
         <v>20000</v>
       </c>
       <c r="L18" s="1">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M18" s="1">
         <v>2</v>
@@ -2050,7 +2059,7 @@
         <v>20000</v>
       </c>
       <c r="L19" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M19" s="1">
         <v>2</v>
@@ -2091,7 +2100,7 @@
         <v>20000</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M20" s="1">
         <v>2</v>
@@ -2132,7 +2141,7 @@
         <v>20000</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
@@ -2173,7 +2182,7 @@
         <v>20000</v>
       </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M22" s="1">
         <v>2</v>
@@ -2214,7 +2223,7 @@
         <v>20000</v>
       </c>
       <c r="L23" s="1">
-        <v>0</v>
+        <v>1066</v>
       </c>
       <c r="M23" s="1">
         <v>2</v>
@@ -2255,7 +2264,7 @@
         <v>20000</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>1066</v>
       </c>
       <c r="M24" s="1">
         <v>2</v>
@@ -2296,7 +2305,7 @@
         <v>20000</v>
       </c>
       <c r="L25" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M25" s="1">
         <v>2</v>
@@ -2337,7 +2346,7 @@
         <v>20000</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M26" s="1">
         <v>2</v>
@@ -2378,7 +2387,7 @@
         <v>20000</v>
       </c>
       <c r="L27" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M27" s="1">
         <v>2</v>
@@ -2419,7 +2428,7 @@
         <v>20000</v>
       </c>
       <c r="L28" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M28" s="1">
         <v>2</v>
@@ -2460,7 +2469,7 @@
         <v>20000</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M29" s="1">
         <v>2</v>
@@ -2501,7 +2510,7 @@
         <v>20000</v>
       </c>
       <c r="L30" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M30" s="1">
         <v>2</v>
@@ -2542,7 +2551,7 @@
         <v>20000</v>
       </c>
       <c r="L31" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M31" s="1">
         <v>2</v>
@@ -2583,7 +2592,7 @@
         <v>20000</v>
       </c>
       <c r="L32" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M32" s="1">
         <v>2</v>
@@ -2624,7 +2633,7 @@
         <v>20000</v>
       </c>
       <c r="L33" s="1">
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="M33" s="1">
         <v>2</v>
@@ -2665,7 +2674,7 @@
         <v>20000</v>
       </c>
       <c r="L34" s="1">
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="M34" s="1">
         <v>2</v>
@@ -2706,7 +2715,7 @@
         <v>20000</v>
       </c>
       <c r="L35" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M35" s="1">
         <v>2</v>
@@ -2747,7 +2756,7 @@
         <v>20000</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M36" s="1">
         <v>2</v>
@@ -2788,7 +2797,7 @@
         <v>20000</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M37" s="1">
         <v>2</v>
@@ -2829,7 +2838,7 @@
         <v>20000</v>
       </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M38" s="1">
         <v>2</v>
@@ -2870,7 +2879,7 @@
         <v>20000</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M39" s="1">
         <v>2</v>
@@ -2911,7 +2920,7 @@
         <v>20000</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M40" s="1">
         <v>2</v>
@@ -2952,7 +2961,7 @@
         <v>20000</v>
       </c>
       <c r="L41" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" s="1">
         <v>2</v>
@@ -2993,7 +3002,7 @@
         <v>20000</v>
       </c>
       <c r="L42" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" s="1">
         <v>2</v>
@@ -3034,7 +3043,7 @@
         <v>20000</v>
       </c>
       <c r="L43" s="1">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="M43" s="1">
         <v>2</v>
@@ -3075,7 +3084,7 @@
         <v>20000</v>
       </c>
       <c r="L44" s="1">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="M44" s="1">
         <v>2</v>
@@ -3116,7 +3125,7 @@
         <v>20000</v>
       </c>
       <c r="L45" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M45" s="1">
         <v>2</v>
@@ -3157,7 +3166,7 @@
         <v>20000</v>
       </c>
       <c r="L46" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M46" s="1">
         <v>2</v>
@@ -3198,7 +3207,7 @@
         <v>20000</v>
       </c>
       <c r="L47" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M47" s="1">
         <v>2</v>
@@ -3239,7 +3248,7 @@
         <v>20000</v>
       </c>
       <c r="L48" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M48" s="1">
         <v>2</v>
@@ -3280,7 +3289,7 @@
         <v>20000</v>
       </c>
       <c r="L49" s="1">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M49" s="1">
         <v>2</v>
@@ -3291,7 +3300,7 @@
         <v>4145</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>62</v>
+        <v>269</v>
       </c>
       <c r="C50" s="1">
         <v>76</v>
@@ -3312,7 +3321,7 @@
         <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>169</v>
+        <v>270</v>
       </c>
       <c r="J50" s="1">
         <v>1002</v>
@@ -3321,7 +3330,7 @@
         <v>20000</v>
       </c>
       <c r="L50" s="1">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M50" s="1">
         <v>2</v>
@@ -3332,16 +3341,16 @@
         <v>4146</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="1">
         <v>76</v>
       </c>
       <c r="D51" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E51" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F51" s="1">
         <v>100</v>
@@ -3353,7 +3362,7 @@
         <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="J51" s="1">
         <v>1002</v>
@@ -3362,7 +3371,7 @@
         <v>20000</v>
       </c>
       <c r="L51" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M51" s="1">
         <v>2</v>
@@ -3373,28 +3382,28 @@
         <v>4147</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="1">
-        <v>420</v>
+        <v>76</v>
       </c>
       <c r="D52" s="1">
-        <v>252</v>
+        <v>50</v>
       </c>
       <c r="E52" s="1">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="F52" s="1">
         <v>100</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="J52" s="1">
         <v>1002</v>
@@ -3403,7 +3412,7 @@
         <v>20000</v>
       </c>
       <c r="L52" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M52" s="1">
         <v>2</v>
@@ -3414,13 +3423,13 @@
         <v>4148</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" s="1">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="D53" s="1">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="E53" s="1">
         <v>216</v>
@@ -3429,95 +3438,95 @@
         <v>100</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K53" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1936</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
+        <v>4149</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="1">
+        <v>432</v>
+      </c>
+      <c r="D54" s="1">
+        <v>240</v>
+      </c>
+      <c r="E54" s="1">
+        <v>216</v>
+      </c>
+      <c r="F54" s="1">
+        <v>100</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J53" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K53" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
-      <c r="M53" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="9">
-        <v>4149</v>
-      </c>
-      <c r="B54" s="3" t="s">
+      <c r="J54" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K54" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1936</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
+        <v>4150</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C54" s="1">
-        <v>92</v>
-      </c>
-      <c r="D54" s="1">
-        <v>64</v>
-      </c>
-      <c r="E54" s="1">
-        <v>52</v>
-      </c>
-      <c r="F54" s="1">
-        <v>100</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J54" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K54" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
-      <c r="M54" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="9">
-        <v>4150</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C55" s="1">
         <v>92</v>
       </c>
       <c r="D55" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E55" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F55" s="1">
         <v>100</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J55" s="1">
         <v>1002</v>
@@ -3526,39 +3535,39 @@
         <v>20000</v>
       </c>
       <c r="L55" s="1">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="M55" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>4151</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" s="1">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D56" s="1">
         <v>66</v>
       </c>
       <c r="E56" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F56" s="1">
         <v>100</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J56" s="1">
         <v>1002</v>
@@ -3567,367 +3576,367 @@
         <v>20000</v>
       </c>
       <c r="L56" s="1">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="M56" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>4152</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C57" s="1">
         <v>96</v>
       </c>
       <c r="D57" s="1">
+        <v>66</v>
+      </c>
+      <c r="E57" s="1">
+        <v>52</v>
+      </c>
+      <c r="F57" s="1">
+        <v>100</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K57" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L57" s="1">
+        <v>282</v>
+      </c>
+      <c r="M57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
+        <v>4153</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="1">
+        <v>96</v>
+      </c>
+      <c r="D58" s="1">
         <v>68</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E58" s="1">
         <v>50</v>
       </c>
-      <c r="F57" s="1">
-        <v>100</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="1" t="s">
+      <c r="F58" s="1">
+        <v>100</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J57" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K57" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="9">
-        <v>4153</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="J58" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K58" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L58" s="1">
+        <v>282</v>
+      </c>
+      <c r="M58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
+        <v>4154</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="1">
-        <v>100</v>
-      </c>
-      <c r="D58" s="1">
+      <c r="C59" s="1">
+        <v>100</v>
+      </c>
+      <c r="D59" s="1">
         <v>66</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E59" s="1">
         <v>54</v>
       </c>
-      <c r="F58" s="1">
-        <v>100</v>
-      </c>
-      <c r="G58" s="1">
+      <c r="F59" s="1">
+        <v>100</v>
+      </c>
+      <c r="G59" s="1">
         <v>5</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" s="1" t="s">
+      <c r="H59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J58" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K58" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L58" s="1">
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="9">
-        <v>4154</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="J59" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K59" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L59" s="1">
+        <v>300</v>
+      </c>
+      <c r="M59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
+        <v>4155</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C60" s="1">
         <v>102</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D60" s="1">
         <v>68</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E60" s="1">
         <v>50</v>
       </c>
-      <c r="F59" s="1">
-        <v>100</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="1" t="s">
+      <c r="F60" s="1">
+        <v>100</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J59" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K59" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A60" s="9">
-        <v>4155</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="J60" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K60" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L60" s="1">
+        <v>300</v>
+      </c>
+      <c r="M60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
+        <v>4156</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C61" s="1">
         <v>104</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D61" s="1">
         <v>70</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E61" s="1">
         <v>52</v>
       </c>
-      <c r="F60" s="1">
-        <v>100</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="F61" s="1">
+        <v>100</v>
+      </c>
+      <c r="G61" s="1">
         <v>5</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="1" t="s">
+      <c r="H61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J60" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K60" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="9">
-        <v>4156</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="J61" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K61" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L61" s="1">
+        <v>354</v>
+      </c>
+      <c r="M61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>4157</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C62" s="1">
         <v>102</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D62" s="1">
         <v>68</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E62" s="1">
         <v>56</v>
       </c>
-      <c r="F61" s="1">
-        <v>100</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" s="1" t="s">
+      <c r="F62" s="1">
+        <v>100</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J61" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K61" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A62" s="9">
-        <v>4157</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="J62" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K62" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L62" s="1">
+        <v>354</v>
+      </c>
+      <c r="M62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>4158</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C62" s="1">
-        <v>552</v>
-      </c>
-      <c r="D62" s="1">
-        <v>384</v>
-      </c>
-      <c r="E62" s="1">
-        <v>312</v>
-      </c>
-      <c r="F62" s="1">
-        <v>100</v>
-      </c>
-      <c r="G62" s="1">
-        <v>5</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J62" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K62" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0</v>
-      </c>
-      <c r="M62" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="9">
-        <v>4158</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C63" s="1">
         <v>552</v>
       </c>
       <c r="D63" s="1">
+        <v>384</v>
+      </c>
+      <c r="E63" s="1">
+        <v>312</v>
+      </c>
+      <c r="F63" s="1">
+        <v>100</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K63" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L63" s="1">
+        <v>4133</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>4159</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="1">
+        <v>552</v>
+      </c>
+      <c r="D64" s="1">
         <v>396</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E64" s="1">
         <v>300</v>
       </c>
-      <c r="F63" s="1">
-        <v>100</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I63" s="1" t="s">
+      <c r="F64" s="1">
+        <v>100</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J63" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K63" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L63" s="1">
-        <v>0</v>
-      </c>
-      <c r="M63" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A64" s="10">
-        <v>4159</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="J64" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K64" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L64" s="1">
+        <v>4133</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
+        <v>4160</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C64" s="1">
-        <v>82</v>
-      </c>
-      <c r="D64" s="1">
-        <v>53</v>
-      </c>
-      <c r="E64" s="1">
-        <v>43</v>
-      </c>
-      <c r="F64" s="1">
-        <v>100</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J64" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K64" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="10">
-        <v>4160</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C65" s="1">
         <v>82</v>
       </c>
       <c r="D65" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E65" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F65" s="1">
         <v>100</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J65" s="1">
         <v>1002</v>
@@ -3936,39 +3945,39 @@
         <v>20000</v>
       </c>
       <c r="L65" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M65" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="10">
+      <c r="A66" s="8">
         <v>4161</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C66" s="1">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D66" s="1">
         <v>55</v>
       </c>
       <c r="E66" s="1">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F66" s="1">
         <v>100</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J66" s="1">
         <v>1002</v>
@@ -3977,352 +3986,352 @@
         <v>20000</v>
       </c>
       <c r="L66" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M66" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A67" s="10">
+      <c r="A67" s="8">
         <v>4162</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C67" s="1">
         <v>84</v>
       </c>
       <c r="D67" s="1">
+        <v>55</v>
+      </c>
+      <c r="E67" s="1">
+        <v>45</v>
+      </c>
+      <c r="F67" s="1">
+        <v>100</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K67" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L67" s="1">
+        <v>204</v>
+      </c>
+      <c r="M67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>4163</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="1">
+        <v>84</v>
+      </c>
+      <c r="D68" s="1">
         <v>53</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E68" s="1">
         <v>47</v>
       </c>
-      <c r="F67" s="1">
-        <v>100</v>
-      </c>
-      <c r="G67" s="1">
+      <c r="F68" s="1">
+        <v>100</v>
+      </c>
+      <c r="G68" s="1">
         <v>3</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="1" t="s">
+      <c r="H68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J67" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K67" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L67" s="1">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="10">
-        <v>4163</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="J68" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K68" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L68" s="1">
+        <v>204</v>
+      </c>
+      <c r="M68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>4164</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C68" s="1">
-        <v>86</v>
-      </c>
-      <c r="D68" s="1">
-        <v>56</v>
-      </c>
-      <c r="E68" s="1">
-        <v>48</v>
-      </c>
-      <c r="F68" s="1">
-        <v>100</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J68" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K68" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A69" s="10">
-        <v>4164</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C69" s="1">
         <v>86</v>
       </c>
       <c r="D69" s="1">
+        <v>56</v>
+      </c>
+      <c r="E69" s="1">
+        <v>48</v>
+      </c>
+      <c r="F69" s="1">
+        <v>100</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K69" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L69" s="1">
+        <v>216</v>
+      </c>
+      <c r="M69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>4165</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" s="1">
+        <v>86</v>
+      </c>
+      <c r="D70" s="1">
         <v>54</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E70" s="1">
         <v>50</v>
       </c>
-      <c r="F69" s="1">
-        <v>100</v>
-      </c>
-      <c r="G69" s="1">
+      <c r="F70" s="1">
+        <v>100</v>
+      </c>
+      <c r="G70" s="1">
         <v>1</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="1" t="s">
+      <c r="H70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J69" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K69" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L69" s="1">
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A70" s="10">
-        <v>4165</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="J70" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K70" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L70" s="1">
+        <v>216</v>
+      </c>
+      <c r="M70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
+        <v>4166</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="C70" s="1">
-        <v>90</v>
-      </c>
-      <c r="D70" s="1">
-        <v>58</v>
-      </c>
-      <c r="E70" s="1">
-        <v>48</v>
-      </c>
-      <c r="F70" s="1">
-        <v>100</v>
-      </c>
-      <c r="G70" s="1">
-        <v>3</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J70" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K70" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L70" s="1">
-        <v>0</v>
-      </c>
-      <c r="M70" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A71" s="10">
-        <v>4166</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="C71" s="1">
         <v>90</v>
       </c>
       <c r="D71" s="1">
+        <v>58</v>
+      </c>
+      <c r="E71" s="1">
+        <v>48</v>
+      </c>
+      <c r="F71" s="1">
+        <v>100</v>
+      </c>
+      <c r="G71" s="1">
+        <v>3</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K71" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L71" s="1">
+        <v>288</v>
+      </c>
+      <c r="M71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
+        <v>4167</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" s="1">
+        <v>90</v>
+      </c>
+      <c r="D72" s="1">
         <v>60</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E72" s="1">
         <v>46</v>
       </c>
-      <c r="F71" s="1">
-        <v>100</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="F72" s="1">
+        <v>100</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J71" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K71" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L71" s="1">
-        <v>0</v>
-      </c>
-      <c r="M71" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A72" s="10">
-        <v>4167</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="J72" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K72" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L72" s="1">
+        <v>288</v>
+      </c>
+      <c r="M72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="8">
+        <v>4168</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C72" s="1">
-        <v>492</v>
-      </c>
-      <c r="D72" s="1">
-        <v>318</v>
-      </c>
-      <c r="E72" s="1">
-        <v>258</v>
-      </c>
-      <c r="F72" s="1">
-        <v>100</v>
-      </c>
-      <c r="G72" s="1">
-        <v>3</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J72" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K72" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="10">
-        <v>4168</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="C73" s="1">
         <v>492</v>
       </c>
       <c r="D73" s="1">
+        <v>318</v>
+      </c>
+      <c r="E73" s="1">
+        <v>258</v>
+      </c>
+      <c r="F73" s="1">
+        <v>100</v>
+      </c>
+      <c r="G73" s="1">
+        <v>3</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K73" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L73" s="1">
+        <v>2756</v>
+      </c>
+      <c r="M73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
+        <v>4169</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C74" s="1">
+        <v>492</v>
+      </c>
+      <c r="D74" s="1">
         <v>330</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E74" s="1">
         <v>246</v>
       </c>
-      <c r="F73" s="1">
-        <v>100</v>
-      </c>
-      <c r="G73" s="1">
+      <c r="F74" s="1">
+        <v>100</v>
+      </c>
+      <c r="G74" s="1">
         <v>1</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" s="1" t="s">
+      <c r="H74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J73" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K73" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L73" s="1">
-        <v>0</v>
-      </c>
-      <c r="M73" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A74" s="1">
-        <v>4169</v>
-      </c>
-      <c r="B74" s="3" t="s">
+      <c r="J74" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K74" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L74" s="1">
+        <v>2756</v>
+      </c>
+      <c r="M74" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
+        <v>4170</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C75" s="1">
         <v>106</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D75" s="1">
         <v>72</v>
-      </c>
-      <c r="E74" s="1">
-        <v>60</v>
-      </c>
-      <c r="F74" s="1">
-        <v>100</v>
-      </c>
-      <c r="G74" s="1">
-        <v>3</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J74" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K74" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L74" s="1">
-        <v>0</v>
-      </c>
-      <c r="M74" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A75" s="1">
-        <v>4170</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" s="1">
-        <v>108</v>
-      </c>
-      <c r="D75" s="1">
-        <v>70</v>
       </c>
       <c r="E75" s="1">
         <v>60</v>
@@ -4331,13 +4340,13 @@
         <v>100</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J75" s="1">
         <v>1002</v>
@@ -4346,162 +4355,162 @@
         <v>20000</v>
       </c>
       <c r="L75" s="1">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="M75" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A76" s="1">
+      <c r="A76" s="8">
         <v>4171</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C76" s="1">
         <v>108</v>
       </c>
       <c r="D76" s="1">
+        <v>70</v>
+      </c>
+      <c r="E76" s="1">
+        <v>60</v>
+      </c>
+      <c r="F76" s="1">
+        <v>100</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K76" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L76" s="1">
+        <v>394</v>
+      </c>
+      <c r="M76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A77" s="8">
+        <v>4172</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="1">
+        <v>108</v>
+      </c>
+      <c r="D77" s="1">
         <v>74</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E77" s="1">
         <v>62</v>
       </c>
-      <c r="F76" s="1">
-        <v>100</v>
-      </c>
-      <c r="G76" s="1">
+      <c r="F77" s="1">
+        <v>100</v>
+      </c>
+      <c r="G77" s="1">
         <v>3</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="1" t="s">
+      <c r="H77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J76" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K76" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L76" s="1">
-        <v>0</v>
-      </c>
-      <c r="M76" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A77" s="1">
-        <v>4172</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="J77" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K77" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L77" s="1">
+        <v>400</v>
+      </c>
+      <c r="M77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="8">
+        <v>4173</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C78" s="1">
         <v>111</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D78" s="1">
         <v>70</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E78" s="1">
         <v>63</v>
       </c>
-      <c r="F77" s="1">
-        <v>100</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77" s="1" t="s">
+      <c r="F78" s="1">
+        <v>100</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J77" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K77" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L77" s="1">
-        <v>0</v>
-      </c>
-      <c r="M77" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="1">
-        <v>4173</v>
-      </c>
-      <c r="B78" s="3" t="s">
+      <c r="J78" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K78" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L78" s="1">
+        <v>400</v>
+      </c>
+      <c r="M78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="8">
+        <v>4174</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C78" s="1">
-        <v>110</v>
-      </c>
-      <c r="D78" s="1">
-        <v>76</v>
-      </c>
-      <c r="E78" s="1">
-        <v>64</v>
-      </c>
-      <c r="F78" s="1">
-        <v>100</v>
-      </c>
-      <c r="G78" s="1">
-        <v>4</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J78" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K78" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L78" s="1">
-        <v>0</v>
-      </c>
-      <c r="M78" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A79" s="1">
-        <v>4174</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C79" s="1">
         <v>110</v>
       </c>
       <c r="D79" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E79" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F79" s="1">
         <v>100</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J79" s="1">
         <v>1002</v>
@@ -4510,39 +4519,39 @@
         <v>20000</v>
       </c>
       <c r="L79" s="1">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="M79" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A80" s="1">
+      <c r="A80" s="8">
         <v>4175</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C80" s="1">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D80" s="1">
         <v>78</v>
       </c>
       <c r="E80" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F80" s="1">
         <v>100</v>
       </c>
       <c r="G80" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J80" s="1">
         <v>1002</v>
@@ -4551,106 +4560,106 @@
         <v>20000</v>
       </c>
       <c r="L80" s="1">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="M80" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A81" s="1">
+      <c r="A81" s="8">
         <v>4176</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" s="1">
         <v>114</v>
       </c>
       <c r="D81" s="1">
+        <v>78</v>
+      </c>
+      <c r="E81" s="1">
+        <v>64</v>
+      </c>
+      <c r="F81" s="1">
+        <v>100</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K81" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L81" s="1">
+        <v>480</v>
+      </c>
+      <c r="M81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
+        <v>4177</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" s="1">
+        <v>114</v>
+      </c>
+      <c r="D82" s="1">
         <v>76</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E82" s="1">
         <v>66</v>
       </c>
-      <c r="F81" s="1">
-        <v>100</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" s="1" t="s">
+      <c r="F82" s="1">
+        <v>100</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J81" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K81" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L81" s="1">
-        <v>0</v>
-      </c>
-      <c r="M81" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="1">
-        <v>4177</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="J82" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K82" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L82" s="1">
+        <v>480</v>
+      </c>
+      <c r="M82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="8">
+        <v>4178</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C83" s="1">
         <v>636</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D83" s="1">
         <v>432</v>
-      </c>
-      <c r="E82" s="1">
-        <v>360</v>
-      </c>
-      <c r="F82" s="1">
-        <v>100</v>
-      </c>
-      <c r="G82" s="1">
-        <v>4</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K82" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L82" s="1">
-        <v>0</v>
-      </c>
-      <c r="M82" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A83" s="1">
-        <v>4178</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C83" s="1">
-        <v>648</v>
-      </c>
-      <c r="D83" s="1">
-        <v>420</v>
       </c>
       <c r="E83" s="1">
         <v>360</v>
@@ -4659,29 +4668,70 @@
         <v>100</v>
       </c>
       <c r="G83" s="1">
+        <v>4</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K83" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L83" s="1">
+        <v>5466</v>
+      </c>
+      <c r="M83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="8">
+        <v>4179</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" s="1">
+        <v>648</v>
+      </c>
+      <c r="D84" s="1">
+        <v>420</v>
+      </c>
+      <c r="E84" s="1">
+        <v>360</v>
+      </c>
+      <c r="F84" s="1">
+        <v>100</v>
+      </c>
+      <c r="G84" s="1">
         <v>3</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I83" s="1" t="s">
+      <c r="H84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J83" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K83" s="1">
-        <v>20000</v>
-      </c>
-      <c r="L83" s="1">
-        <v>0</v>
-      </c>
-      <c r="M83" s="1">
+      <c r="J84" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K84" s="1">
+        <v>20000</v>
+      </c>
+      <c r="L84" s="1">
+        <v>5466</v>
+      </c>
+      <c r="M84" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M83"/>
+  <autoFilter ref="A3:M84"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -4690,7 +4740,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V83"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
@@ -5377,6 +5428,9 @@
       <c r="Q15" t="s">
         <v>181</v>
       </c>
+      <c r="U15" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -5427,8 +5481,11 @@
       <c r="S16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U16" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4112</v>
       </c>
@@ -5474,8 +5531,11 @@
       <c r="Q17" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U17" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>4113</v>
       </c>
@@ -5521,8 +5581,11 @@
       <c r="Q18" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U18" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4114</v>
       </c>
@@ -5568,8 +5631,11 @@
       <c r="Q19" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U19" s="10">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4115</v>
       </c>
@@ -5615,8 +5681,11 @@
       <c r="Q20" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U20" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4116</v>
       </c>
@@ -5662,8 +5731,11 @@
       <c r="Q21" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U21" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4117</v>
       </c>
@@ -5709,8 +5781,11 @@
       <c r="Q22" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U22" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4118</v>
       </c>
@@ -5756,8 +5831,11 @@
       <c r="Q23" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U23" s="10">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4119</v>
       </c>
@@ -5803,8 +5881,11 @@
       <c r="Q24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U24" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4120</v>
       </c>
@@ -5853,8 +5934,11 @@
       <c r="S25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U25" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4121</v>
       </c>
@@ -5900,8 +5984,11 @@
       <c r="Q26" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U26" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4122</v>
       </c>
@@ -5947,8 +6034,11 @@
       <c r="Q27" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U27" s="10">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4123</v>
       </c>
@@ -5994,8 +6084,11 @@
       <c r="Q28" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U28" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4124</v>
       </c>
@@ -6041,8 +6134,11 @@
       <c r="Q29" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U29" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4125</v>
       </c>
@@ -6088,8 +6184,11 @@
       <c r="Q30" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U30" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4126</v>
       </c>
@@ -6135,8 +6234,11 @@
       <c r="Q31" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U31" s="10">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>4127</v>
       </c>
@@ -6182,8 +6284,11 @@
       <c r="Q32" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U32" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>4128</v>
       </c>
@@ -6229,8 +6334,11 @@
       <c r="Q33" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U33" s="9">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4129</v>
       </c>
@@ -6276,8 +6384,11 @@
       <c r="Q34" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U34" s="9">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4130</v>
       </c>
@@ -6326,8 +6437,11 @@
       <c r="S35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U35" s="10">
+        <v>13333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4131</v>
       </c>
@@ -6373,8 +6487,11 @@
       <c r="Q36" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U36" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4132</v>
       </c>
@@ -6420,8 +6537,11 @@
       <c r="Q37" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U37" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>4133</v>
       </c>
@@ -6467,8 +6587,11 @@
       <c r="Q38" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U38" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4134</v>
       </c>
@@ -6514,8 +6637,11 @@
       <c r="Q39" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U39" s="10">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>4135</v>
       </c>
@@ -6561,8 +6687,11 @@
       <c r="Q40" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U40" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>4136</v>
       </c>
@@ -6608,8 +6737,11 @@
       <c r="Q41" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U41" s="9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>4137</v>
       </c>
@@ -6655,8 +6787,11 @@
       <c r="Q42" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U42" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>4138</v>
       </c>
@@ -6702,8 +6837,11 @@
       <c r="Q43" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U43" s="10">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>4139</v>
       </c>
@@ -6749,8 +6887,11 @@
       <c r="Q44" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U44" s="9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>4140</v>
       </c>
@@ -6799,8 +6940,11 @@
       <c r="S45">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U45" s="9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4141</v>
       </c>
@@ -6846,8 +6990,11 @@
       <c r="Q46" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U46" s="9">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4142</v>
       </c>
@@ -6893,8 +7040,11 @@
       <c r="Q47" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U47" s="10">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4143</v>
       </c>
@@ -6940,8 +7090,11 @@
       <c r="Q48" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U48" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4144</v>
       </c>
@@ -6987,8 +7140,11 @@
       <c r="Q49" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U49" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4145</v>
       </c>
@@ -7034,8 +7190,11 @@
       <c r="Q50" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U50" s="9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4146</v>
       </c>
@@ -7081,8 +7240,11 @@
       <c r="Q51" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U51" s="10">
+        <v>12666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4147</v>
       </c>
@@ -7128,8 +7290,11 @@
       <c r="Q52" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U52" s="9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>4148</v>
       </c>
@@ -7175,8 +7340,11 @@
       <c r="Q53" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U53" s="9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>4149</v>
       </c>
@@ -7225,8 +7393,11 @@
       <c r="S54">
         <v>7</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U54" s="9">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4150</v>
       </c>
@@ -7272,8 +7443,11 @@
       <c r="Q55" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U55" s="10">
+        <v>26666</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4151</v>
       </c>
@@ -7319,8 +7493,11 @@
       <c r="Q56" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U56" s="9">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4152</v>
       </c>
@@ -7366,8 +7543,11 @@
       <c r="Q57" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U57" s="9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4153</v>
       </c>
@@ -7413,8 +7593,11 @@
       <c r="Q58" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U58" s="9">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4154</v>
       </c>
@@ -7460,8 +7643,11 @@
       <c r="Q59" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U59" s="10">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4155</v>
       </c>
@@ -7507,8 +7693,11 @@
       <c r="Q60" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U60" s="9">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4156</v>
       </c>
@@ -7554,8 +7743,11 @@
       <c r="Q61" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U61" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4157</v>
       </c>
@@ -7601,8 +7793,11 @@
       <c r="Q62" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U62" s="9">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4158</v>
       </c>
@@ -7648,8 +7843,11 @@
       <c r="Q63" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U63" s="10">
+        <v>5466</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4159</v>
       </c>
@@ -7698,8 +7896,11 @@
       <c r="S64">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U64" s="9">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4160</v>
       </c>
@@ -7745,8 +7946,11 @@
       <c r="Q65" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U65" s="9">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4161</v>
       </c>
@@ -7792,8 +7996,11 @@
       <c r="Q66" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U66" s="9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4162</v>
       </c>
@@ -7839,8 +8046,11 @@
       <c r="Q67" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U67" s="10">
+        <v>11666</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4163</v>
       </c>
@@ -7886,8 +8096,11 @@
       <c r="Q68" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U68" s="9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4164</v>
       </c>
@@ -7933,8 +8146,11 @@
       <c r="Q69" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U69" s="9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4165</v>
       </c>
@@ -7980,8 +8196,11 @@
       <c r="Q70" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U70" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4166</v>
       </c>
@@ -8027,8 +8246,11 @@
       <c r="Q71" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U71" s="10">
+        <v>17666</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4167</v>
       </c>
@@ -8074,8 +8296,11 @@
       <c r="Q72" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U72" s="9">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4168</v>
       </c>
@@ -8121,8 +8346,11 @@
       <c r="Q73" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U73" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4169</v>
       </c>
@@ -8171,8 +8399,11 @@
       <c r="S74">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U74" s="9">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4170</v>
       </c>
@@ -8218,8 +8449,11 @@
       <c r="Q75" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U75" s="10">
+        <v>30366</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4171</v>
       </c>
@@ -8265,8 +8499,11 @@
       <c r="Q76" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U76" s="9">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4172</v>
       </c>
@@ -8312,8 +8549,11 @@
       <c r="Q77" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U77" s="9">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4173</v>
       </c>
@@ -8359,8 +8599,11 @@
       <c r="Q78" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U78" s="9">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4174</v>
       </c>
@@ -8406,8 +8649,11 @@
       <c r="Q79" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U79" s="10">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4175</v>
       </c>
@@ -8453,8 +8699,11 @@
       <c r="Q80" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="U80" s="9">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4176</v>
       </c>
@@ -8500,8 +8749,11 @@
       <c r="Q81" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="U81" s="9">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4177</v>
       </c>
@@ -8547,8 +8799,11 @@
       <c r="Q82" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="U82" s="9">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4178</v>
       </c>
@@ -8594,8 +8849,179 @@
       <c r="Q83" t="s">
         <v>181</v>
       </c>
+      <c r="U83" s="10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U84" s="9">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U85" s="9">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U86" s="9">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U87" s="10">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U88" s="9">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U89" s="9">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U90" s="9">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U91" s="10">
+        <v>28333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U92" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U93" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U94" s="9">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U95" s="10">
+        <v>33333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U96" s="9">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="97" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U97" s="9">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="98" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U98" s="9">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="99" spans="21:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U99" s="10">
+        <v>8333</v>
+      </c>
+    </row>
+    <row r="100" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U100" s="9">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="101" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U101" s="9">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="102" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U102" s="9">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="103" spans="21:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U103" s="10">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="104" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U104" s="9">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="105" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U105" s="9">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="106" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U106" s="9">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="107" spans="21:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U107" s="10">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="108" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U108" s="9">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="109" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U109" s="9">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="110" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U110" s="9">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="111" spans="21:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U111" s="10">
+        <v>31200</v>
+      </c>
+    </row>
+    <row r="112" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U112" s="9">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="113" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U113" s="9">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="114" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U114" s="9">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="115" spans="21:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="U115" s="10">
+        <v>40000</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="U15:U115">
+    <filterColumn colId="0">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState ref="U16:U114">
+      <sortCondition ref="U15:U115"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="275">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -924,13 +924,28 @@
   </si>
   <si>
     <t>Monsters_29</t>
+  </si>
+  <si>
+    <t>纯净之水</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>石块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龟壳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀刃</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -942,6 +957,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -996,7 +1018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1027,6 +1049,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,17 +1342,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M84"/>
+  <dimension ref="A2:P84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15.25" style="3" customWidth="1"/>
-    <col min="3" max="7" width="9" style="1"/>
-    <col min="8" max="13" width="9" style="1" customWidth="1"/>
+    <col min="3" max="7" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="13" width="9" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1409,7 +1434,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>4001</v>
       </c>
@@ -1449,8 +1474,11 @@
       <c r="M4" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P4" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4100</v>
       </c>
@@ -1490,8 +1518,11 @@
       <c r="M5" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P5" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4101</v>
       </c>
@@ -1532,7 +1563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>4102</v>
       </c>
@@ -1572,8 +1603,11 @@
       <c r="M7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P7" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>4103</v>
       </c>
@@ -1614,7 +1648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>4104</v>
       </c>
@@ -1655,7 +1689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>4105</v>
       </c>
@@ -1695,8 +1729,11 @@
       <c r="M10" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P10" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>4106</v>
       </c>
@@ -1737,7 +1774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>4107</v>
       </c>
@@ -1778,7 +1815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>4108</v>
       </c>
@@ -1819,7 +1856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>4109</v>
       </c>
@@ -1860,7 +1897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>4110</v>
       </c>
@@ -1901,7 +1938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>4111</v>
       </c>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MonsterData!$A$3:$M$84</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="276">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -939,6 +940,10 @@
   </si>
   <si>
     <t>刀刃</t>
+  </si>
+  <si>
+    <t>木棍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1018,7 +1023,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1053,6 +1058,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1342,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P84"/>
+  <dimension ref="A2:R84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1352,7 +1358,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>4001</v>
       </c>
@@ -1478,7 +1484,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4100</v>
       </c>
@@ -1522,7 +1528,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4101</v>
       </c>
@@ -1563,7 +1569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>4102</v>
       </c>
@@ -1607,7 +1613,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>4103</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>4104</v>
       </c>
@@ -1689,7 +1695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>4105</v>
       </c>
@@ -1732,8 +1738,11 @@
       <c r="P10" s="1" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="R10" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>4106</v>
       </c>
@@ -1774,7 +1783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>4107</v>
       </c>
@@ -1815,7 +1824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>4108</v>
       </c>
@@ -1856,7 +1865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>4109</v>
       </c>
@@ -1897,7 +1906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>4110</v>
       </c>
@@ -1938,7 +1947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>4111</v>
       </c>
@@ -4778,7 +4787,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:V115"/>
+  <dimension ref="A1:V116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
@@ -5469,153 +5478,153 @@
         <v>268</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="16" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
         <v>4111</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="12">
         <v>38</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="12">
         <v>26</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="12">
         <v>24</v>
       </c>
-      <c r="F16">
-        <v>100</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="F16" s="12">
+        <v>100</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="J16" s="1">
-        <v>1002</v>
-      </c>
-      <c r="K16">
-        <v>20000</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
-      <c r="P16">
+      <c r="J16" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K16" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>2</v>
+      </c>
+      <c r="P16" s="12">
         <v>188</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="12">
         <v>3</v>
       </c>
       <c r="U16" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="17" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
         <v>4112</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="12">
         <v>42</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="12">
         <v>28</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="12">
         <v>24</v>
       </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="F17" s="12">
+        <v>100</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="J17">
-        <v>1002</v>
-      </c>
-      <c r="K17">
-        <v>20000</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="P17">
+      <c r="J17" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K17" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>2</v>
+      </c>
+      <c r="P17" s="12">
         <v>194</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q17" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U17" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12">
         <v>4113</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="12">
         <v>44</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="12">
         <v>26</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="12">
         <v>24</v>
       </c>
-      <c r="F18">
-        <v>100</v>
-      </c>
-      <c r="G18">
+      <c r="F18" s="12">
+        <v>100</v>
+      </c>
+      <c r="G18" s="12">
         <v>5</v>
       </c>
-      <c r="H18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="J18">
-        <v>1002</v>
-      </c>
-      <c r="K18">
-        <v>20000</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>2</v>
-      </c>
-      <c r="P18">
+      <c r="J18" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K18" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>2</v>
+      </c>
+      <c r="P18" s="12">
         <v>194</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q18" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U18" s="9">
@@ -5672,150 +5681,150 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="20" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
         <v>4115</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="12">
         <v>46</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="12">
         <v>30</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="12">
         <v>24</v>
       </c>
-      <c r="F20">
-        <v>100</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="F20" s="12">
+        <v>100</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J20">
-        <v>1002</v>
-      </c>
-      <c r="K20">
-        <v>20000</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>2</v>
-      </c>
-      <c r="P20">
+      <c r="J20" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K20" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L20" s="12">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
+        <v>2</v>
+      </c>
+      <c r="P20" s="12">
         <v>200</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q20" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U20" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21">
+    <row r="21" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
         <v>4116</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="12">
         <v>50</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="12">
         <v>31</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="12">
         <v>25</v>
       </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="F21" s="12">
+        <v>100</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="J21">
-        <v>1002</v>
-      </c>
-      <c r="K21">
-        <v>20000</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
-      <c r="P21">
+      <c r="J21" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K21" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L21" s="12">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12">
+        <v>2</v>
+      </c>
+      <c r="P21" s="12">
         <v>206</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q21" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U21" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22">
+    <row r="22" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12">
         <v>4117</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="12">
         <v>48</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="12">
         <v>33</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="12">
         <v>25</v>
       </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="12">
+        <v>100</v>
+      </c>
+      <c r="G22" s="12">
         <v>3</v>
       </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="H22" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J22">
-        <v>1002</v>
-      </c>
-      <c r="K22">
-        <v>20000</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>2</v>
-      </c>
-      <c r="P22">
+      <c r="J22" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K22" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L22" s="12">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
+        <v>2</v>
+      </c>
+      <c r="P22" s="12">
         <v>206</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q22" s="12" t="s">
         <v>181</v>
       </c>
       <c r="U22" s="9">
@@ -5872,153 +5881,153 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24">
+    <row r="24" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="12">
         <v>4119</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="12">
         <v>232</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="12">
         <v>150</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="12">
         <v>146</v>
       </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
-      <c r="G24">
+      <c r="F24" s="12">
+        <v>100</v>
+      </c>
+      <c r="G24" s="12">
         <v>5</v>
       </c>
-      <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="H24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="J24">
-        <v>1002</v>
-      </c>
-      <c r="K24">
-        <v>20000</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>2</v>
-      </c>
-      <c r="P24">
+      <c r="J24" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K24" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L24" s="12">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12">
+        <v>2</v>
+      </c>
+      <c r="P24" s="12">
         <v>628</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q24" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U24" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25">
+    <row r="25" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12">
         <v>4120</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="12">
         <v>25</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="12">
         <v>17</v>
       </c>
-      <c r="E25">
-        <v>16</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="E25" s="12">
+        <v>16</v>
+      </c>
+      <c r="F25" s="12">
+        <v>100</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="J25">
-        <v>1002</v>
-      </c>
-      <c r="K25">
-        <v>20000</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>2</v>
-      </c>
-      <c r="P25">
+      <c r="J25" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K25" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L25" s="12">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12">
+        <v>2</v>
+      </c>
+      <c r="P25" s="12">
         <v>158</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="Q25" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="12">
         <v>2</v>
       </c>
       <c r="U25" s="9">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26">
+    <row r="26" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="12">
         <v>4121</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="12">
         <v>25</v>
       </c>
-      <c r="D26">
-        <v>16</v>
-      </c>
-      <c r="E26">
+      <c r="D26" s="12">
+        <v>16</v>
+      </c>
+      <c r="E26" s="12">
         <v>17</v>
       </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="F26" s="12">
+        <v>100</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="J26">
-        <v>1002</v>
-      </c>
-      <c r="K26">
-        <v>20000</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>2</v>
-      </c>
-      <c r="P26">
+      <c r="J26" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K26" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L26" s="12">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12">
+        <v>2</v>
+      </c>
+      <c r="P26" s="12">
         <v>158</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="Q26" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U26" s="9">
@@ -6075,150 +6084,150 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="28" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
         <v>4123</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="12">
         <v>28</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="12">
         <v>20</v>
       </c>
-      <c r="E28">
-        <v>16</v>
-      </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
-      <c r="G28">
+      <c r="E28" s="12">
+        <v>16</v>
+      </c>
+      <c r="F28" s="12">
+        <v>100</v>
+      </c>
+      <c r="G28" s="12">
         <v>4</v>
       </c>
-      <c r="H28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="H28" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J28">
-        <v>1002</v>
-      </c>
-      <c r="K28">
-        <v>20000</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>2</v>
-      </c>
-      <c r="P28">
+      <c r="J28" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K28" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L28" s="12">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12">
+        <v>2</v>
+      </c>
+      <c r="P28" s="12">
         <v>164</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="Q28" s="12" t="s">
         <v>178</v>
       </c>
       <c r="U28" s="9">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="29" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="12">
         <v>4124</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="12">
         <v>32</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="12">
         <v>22</v>
       </c>
-      <c r="E29">
-        <v>16</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="E29" s="12">
+        <v>16</v>
+      </c>
+      <c r="F29" s="12">
+        <v>100</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J29">
-        <v>1002</v>
-      </c>
-      <c r="K29">
-        <v>20000</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>2</v>
-      </c>
-      <c r="P29">
+      <c r="J29" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K29" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L29" s="12">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12">
+        <v>2</v>
+      </c>
+      <c r="P29" s="12">
         <v>170</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="Q29" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U29" s="9">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="12">
         <v>4125</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="12">
         <v>30</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="12">
         <v>22</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="12">
         <v>18</v>
       </c>
-      <c r="F30">
-        <v>100</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="F30" s="12">
+        <v>100</v>
+      </c>
+      <c r="G30" s="12">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="J30">
-        <v>1002</v>
-      </c>
-      <c r="K30">
-        <v>20000</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>2</v>
-      </c>
-      <c r="P30">
+      <c r="J30" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K30" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L30" s="12">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12">
+        <v>2</v>
+      </c>
+      <c r="P30" s="12">
         <v>170</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="Q30" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U30" s="9">
@@ -6275,150 +6284,150 @@
         <v>6666</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="12">
         <v>4127</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="12">
         <v>32</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="12">
         <v>22</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="12">
         <v>22</v>
       </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="F32" s="12">
+        <v>100</v>
+      </c>
+      <c r="G32" s="12">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J32">
-        <v>1002</v>
-      </c>
-      <c r="K32">
-        <v>20000</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>2</v>
-      </c>
-      <c r="P32">
+      <c r="J32" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K32" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L32" s="12">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12">
+        <v>2</v>
+      </c>
+      <c r="P32" s="12">
         <v>176</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="Q32" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U32" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
         <v>4128</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="12">
         <v>150</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="12">
         <v>102</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="12">
         <v>96</v>
       </c>
-      <c r="F33">
-        <v>100</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="F33" s="12">
+        <v>100</v>
+      </c>
+      <c r="G33" s="12">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="J33">
-        <v>1002</v>
-      </c>
-      <c r="K33">
-        <v>20000</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>2</v>
-      </c>
-      <c r="P33">
+      <c r="J33" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K33" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L33" s="12">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12">
+        <v>2</v>
+      </c>
+      <c r="P33" s="12">
         <v>448</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="Q33" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U33" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
         <v>4129</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="12">
         <v>150</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="12">
         <v>106</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="12">
         <v>92</v>
       </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
+      <c r="F34" s="12">
+        <v>100</v>
+      </c>
+      <c r="G34" s="12">
         <v>4</v>
       </c>
-      <c r="H34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="H34" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="J34">
-        <v>1002</v>
-      </c>
-      <c r="K34">
-        <v>20000</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>2</v>
-      </c>
-      <c r="P34">
+      <c r="J34" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K34" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L34" s="12">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12">
+        <v>2</v>
+      </c>
+      <c r="P34" s="12">
         <v>448</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="Q34" s="12" t="s">
         <v>178</v>
       </c>
       <c r="U34" s="9">
@@ -6478,150 +6487,150 @@
         <v>13333</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12">
         <v>4131</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="12">
         <v>58</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="12">
         <v>30</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="12">
         <v>30</v>
       </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="F36" s="12">
+        <v>100</v>
+      </c>
+      <c r="G36" s="12">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="J36">
-        <v>1002</v>
-      </c>
-      <c r="K36">
-        <v>20000</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>2</v>
-      </c>
-      <c r="P36">
+      <c r="J36" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K36" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L36" s="12">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12">
+        <v>2</v>
+      </c>
+      <c r="P36" s="12">
         <v>218</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="Q36" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U36" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="37" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="12">
         <v>4132</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="12">
         <v>60</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="12">
         <v>36</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="12">
         <v>28</v>
       </c>
-      <c r="F37">
-        <v>100</v>
-      </c>
-      <c r="G37">
+      <c r="F37" s="12">
+        <v>100</v>
+      </c>
+      <c r="G37" s="12">
         <v>1</v>
       </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="H37" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="J37">
-        <v>1002</v>
-      </c>
-      <c r="K37">
-        <v>20000</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>2</v>
-      </c>
-      <c r="P37">
+      <c r="J37" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K37" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L37" s="12">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12">
+        <v>2</v>
+      </c>
+      <c r="P37" s="12">
         <v>224</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="Q37" s="12" t="s">
         <v>187</v>
       </c>
       <c r="U37" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="38" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="12">
         <v>4133</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="12">
         <v>60</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="12">
         <v>35</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="12">
         <v>29</v>
       </c>
-      <c r="F38">
-        <v>100</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="F38" s="12">
+        <v>100</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J38">
-        <v>1002</v>
-      </c>
-      <c r="K38">
-        <v>20000</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>2</v>
-      </c>
-      <c r="P38">
+      <c r="J38" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K38" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L38" s="12">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12">
+        <v>2</v>
+      </c>
+      <c r="P38" s="12">
         <v>224</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="Q38" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U38" s="9">
@@ -6678,150 +6687,150 @@
         <v>533</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="40" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
         <v>4135</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="12">
         <v>64</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="12">
         <v>34</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="12">
         <v>32</v>
       </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40">
+      <c r="F40" s="12">
+        <v>100</v>
+      </c>
+      <c r="G40" s="12">
         <v>5</v>
       </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="H40" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="J40">
-        <v>1002</v>
-      </c>
-      <c r="K40">
-        <v>20000</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-      <c r="P40">
+      <c r="J40" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K40" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L40" s="12">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12">
+        <v>2</v>
+      </c>
+      <c r="P40" s="12">
         <v>230</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="Q40" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U40" s="9">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41">
+    <row r="41" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="12">
         <v>4136</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="12">
         <v>64</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="12">
         <v>40</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="12">
         <v>32</v>
       </c>
-      <c r="F41">
-        <v>100</v>
-      </c>
-      <c r="G41">
+      <c r="F41" s="12">
+        <v>100</v>
+      </c>
+      <c r="G41" s="12">
         <v>1</v>
       </c>
-      <c r="H41" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="H41" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="J41">
-        <v>1002</v>
-      </c>
-      <c r="K41">
-        <v>20000</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>2</v>
-      </c>
-      <c r="P41">
+      <c r="J41" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K41" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L41" s="12">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12">
+        <v>2</v>
+      </c>
+      <c r="P41" s="12">
         <v>236</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="Q41" s="12" t="s">
         <v>187</v>
       </c>
       <c r="U41" s="9">
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42">
+    <row r="42" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
         <v>4137</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="12">
         <v>68</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="12">
         <v>38</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="12">
         <v>30</v>
       </c>
-      <c r="F42">
-        <v>100</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="F42" s="12">
+        <v>100</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="J42">
-        <v>1002</v>
-      </c>
-      <c r="K42">
-        <v>20000</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>2</v>
-      </c>
-      <c r="P42">
+      <c r="J42" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K42" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L42" s="12">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12">
+        <v>2</v>
+      </c>
+      <c r="P42" s="12">
         <v>236</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="Q42" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U42" s="9">
@@ -6878,153 +6887,153 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44">
+    <row r="44" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="12">
         <v>4139</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="12">
         <v>340</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="12">
         <v>208</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="12">
         <v>160</v>
       </c>
-      <c r="F44">
-        <v>100</v>
-      </c>
-      <c r="G44">
+      <c r="F44" s="12">
+        <v>100</v>
+      </c>
+      <c r="G44" s="12">
         <v>5</v>
       </c>
-      <c r="H44" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="H44" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J44">
-        <v>1002</v>
-      </c>
-      <c r="K44">
-        <v>20000</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>2</v>
-      </c>
-      <c r="P44">
+      <c r="J44" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K44" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L44" s="12">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12">
+        <v>2</v>
+      </c>
+      <c r="P44" s="12">
         <v>808</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="Q44" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U44" s="9">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45">
+    <row r="45" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="12">
         <v>4140</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="12">
         <v>70</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="12">
         <v>42</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="12">
         <v>36</v>
       </c>
-      <c r="F45">
-        <v>100</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="F45" s="12">
+        <v>100</v>
+      </c>
+      <c r="G45" s="12">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="J45">
-        <v>1002</v>
-      </c>
-      <c r="K45">
-        <v>20000</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>2</v>
-      </c>
-      <c r="P45">
+      <c r="J45" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K45" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L45" s="12">
+        <v>0</v>
+      </c>
+      <c r="M45" s="12">
+        <v>2</v>
+      </c>
+      <c r="P45" s="12">
         <v>248</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="Q45" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="12">
         <v>5</v>
       </c>
       <c r="U45" s="9">
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46">
+    <row r="46" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="12">
         <v>4141</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="12">
         <v>72</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="12">
         <v>40</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="12">
         <v>36</v>
       </c>
-      <c r="F46">
-        <v>100</v>
-      </c>
-      <c r="G46">
-        <v>2</v>
-      </c>
-      <c r="H46" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="F46" s="12">
+        <v>100</v>
+      </c>
+      <c r="G46" s="12">
+        <v>2</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="J46">
-        <v>1002</v>
-      </c>
-      <c r="K46">
-        <v>20000</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>2</v>
-      </c>
-      <c r="P46">
+      <c r="J46" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K46" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L46" s="12">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12">
+        <v>2</v>
+      </c>
+      <c r="P46" s="12">
         <v>248</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q46" s="12" t="s">
         <v>180</v>
       </c>
       <c r="U46" s="9">
@@ -7081,150 +7090,150 @@
         <v>6666</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48">
+    <row r="48" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="12">
         <v>4143</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="12">
         <v>74</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="12">
         <v>44</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="12">
         <v>36</v>
       </c>
-      <c r="F48">
-        <v>100</v>
-      </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
-      <c r="H48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="F48" s="12">
+        <v>100</v>
+      </c>
+      <c r="G48" s="12">
+        <v>2</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="J48">
-        <v>1002</v>
-      </c>
-      <c r="K48">
-        <v>20000</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>2</v>
-      </c>
-      <c r="P48">
+      <c r="J48" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K48" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L48" s="12">
+        <v>0</v>
+      </c>
+      <c r="M48" s="12">
+        <v>2</v>
+      </c>
+      <c r="P48" s="12">
         <v>254</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q48" s="12" t="s">
         <v>180</v>
       </c>
       <c r="U48" s="9">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A49">
+    <row r="49" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="12">
         <v>4144</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="12">
         <v>74</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="12">
         <v>48</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="12">
         <v>38</v>
       </c>
-      <c r="F49">
-        <v>100</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="F49" s="12">
+        <v>100</v>
+      </c>
+      <c r="G49" s="12">
+        <v>2</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="J49">
-        <v>1002</v>
-      </c>
-      <c r="K49">
-        <v>20000</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>2</v>
-      </c>
-      <c r="P49">
+      <c r="J49" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K49" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L49" s="12">
+        <v>0</v>
+      </c>
+      <c r="M49" s="12">
+        <v>2</v>
+      </c>
+      <c r="P49" s="12">
         <v>260</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q49" s="12" t="s">
         <v>180</v>
       </c>
       <c r="U49" s="9">
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A50">
+    <row r="50" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="12">
         <v>4145</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="12">
         <v>76</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="12">
         <v>44</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="12">
         <v>40</v>
       </c>
-      <c r="F50">
-        <v>100</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="F50" s="12">
+        <v>100</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="J50">
-        <v>1002</v>
-      </c>
-      <c r="K50">
-        <v>20000</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>2</v>
-      </c>
-      <c r="P50">
+      <c r="J50" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K50" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L50" s="12">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12">
+        <v>2</v>
+      </c>
+      <c r="P50" s="12">
         <v>260</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="Q50" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U50" s="9">
@@ -7281,153 +7290,153 @@
         <v>12666</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A52">
+    <row r="52" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="12">
         <v>4147</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="12">
         <v>420</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="12">
         <v>252</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="12">
         <v>216</v>
       </c>
-      <c r="F52">
-        <v>100</v>
-      </c>
-      <c r="G52">
-        <v>2</v>
-      </c>
-      <c r="H52" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="F52" s="12">
+        <v>100</v>
+      </c>
+      <c r="G52" s="12">
+        <v>2</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="J52">
-        <v>1002</v>
-      </c>
-      <c r="K52">
-        <v>20000</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>2</v>
-      </c>
-      <c r="P52">
+      <c r="J52" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K52" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L52" s="12">
+        <v>0</v>
+      </c>
+      <c r="M52" s="12">
+        <v>2</v>
+      </c>
+      <c r="P52" s="12">
         <v>988</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="Q52" s="12" t="s">
         <v>180</v>
       </c>
       <c r="U52" s="9">
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A53">
+    <row r="53" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="12">
         <v>4148</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="12">
         <v>432</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="12">
         <v>240</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="12">
         <v>216</v>
       </c>
-      <c r="F53">
-        <v>100</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="F53" s="12">
+        <v>100</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J53">
-        <v>1002</v>
-      </c>
-      <c r="K53">
-        <v>20000</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>2</v>
-      </c>
-      <c r="P53">
+      <c r="J53" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K53" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L53" s="12">
+        <v>0</v>
+      </c>
+      <c r="M53" s="12">
+        <v>2</v>
+      </c>
+      <c r="P53" s="12">
         <v>988</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="Q53" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U53" s="9">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A54">
+    <row r="54" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="12">
         <v>4149</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="12">
         <v>92</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="12">
         <v>64</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="12">
         <v>52</v>
       </c>
-      <c r="F54">
-        <v>100</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="F54" s="12">
+        <v>100</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="J54">
-        <v>1002</v>
-      </c>
-      <c r="K54">
-        <v>20000</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>2</v>
-      </c>
-      <c r="P54">
+      <c r="J54" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K54" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L54" s="12">
+        <v>0</v>
+      </c>
+      <c r="M54" s="12">
+        <v>2</v>
+      </c>
+      <c r="P54" s="12">
         <v>308</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="Q54" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="12">
         <v>7</v>
       </c>
       <c r="U54" s="9">
@@ -7484,150 +7493,150 @@
         <v>26666</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A56">
+    <row r="56" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
         <v>4151</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="12">
         <v>96</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="12">
         <v>66</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="12">
         <v>52</v>
       </c>
-      <c r="F56">
-        <v>100</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="F56" s="12">
+        <v>100</v>
+      </c>
+      <c r="G56" s="12">
+        <v>0</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J56">
-        <v>1002</v>
-      </c>
-      <c r="K56">
-        <v>20000</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>2</v>
-      </c>
-      <c r="P56">
+      <c r="J56" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K56" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L56" s="12">
+        <v>0</v>
+      </c>
+      <c r="M56" s="12">
+        <v>2</v>
+      </c>
+      <c r="P56" s="12">
         <v>314</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="Q56" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U56" s="9">
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A57">
+    <row r="57" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
         <v>4152</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="12">
         <v>96</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="12">
         <v>68</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="12">
         <v>50</v>
       </c>
-      <c r="F57">
-        <v>100</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="F57" s="12">
+        <v>100</v>
+      </c>
+      <c r="G57" s="12">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="J57">
-        <v>1002</v>
-      </c>
-      <c r="K57">
-        <v>20000</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>2</v>
-      </c>
-      <c r="P57">
+      <c r="J57" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K57" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L57" s="12">
+        <v>0</v>
+      </c>
+      <c r="M57" s="12">
+        <v>2</v>
+      </c>
+      <c r="P57" s="12">
         <v>314</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="Q57" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U57" s="9">
         <v>150</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A58">
+    <row r="58" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
         <v>4153</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C58">
-        <v>100</v>
-      </c>
-      <c r="D58">
+      <c r="C58" s="12">
+        <v>100</v>
+      </c>
+      <c r="D58" s="12">
         <v>66</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="12">
         <v>54</v>
       </c>
-      <c r="F58">
-        <v>100</v>
-      </c>
-      <c r="G58">
+      <c r="F58" s="12">
+        <v>100</v>
+      </c>
+      <c r="G58" s="12">
         <v>5</v>
       </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="H58" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="J58">
-        <v>1002</v>
-      </c>
-      <c r="K58">
-        <v>20000</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>2</v>
-      </c>
-      <c r="P58">
+      <c r="J58" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K58" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L58" s="12">
+        <v>0</v>
+      </c>
+      <c r="M58" s="12">
+        <v>2</v>
+      </c>
+      <c r="P58" s="12">
         <v>320</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="Q58" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U58" s="9">
@@ -7684,150 +7693,150 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A60">
+    <row r="60" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
         <v>4155</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="12">
         <v>104</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="12">
         <v>70</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="12">
         <v>52</v>
       </c>
-      <c r="F60">
-        <v>100</v>
-      </c>
-      <c r="G60">
+      <c r="F60" s="12">
+        <v>100</v>
+      </c>
+      <c r="G60" s="12">
         <v>5</v>
       </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="H60" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="J60">
-        <v>1002</v>
-      </c>
-      <c r="K60">
-        <v>20000</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>2</v>
-      </c>
-      <c r="P60">
+      <c r="J60" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K60" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L60" s="12">
+        <v>0</v>
+      </c>
+      <c r="M60" s="12">
+        <v>2</v>
+      </c>
+      <c r="P60" s="12">
         <v>326</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="Q60" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U60" s="9">
         <v>192</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A61">
+    <row r="61" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
         <v>4156</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="12">
         <v>102</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="12">
         <v>68</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="12">
         <v>56</v>
       </c>
-      <c r="F61">
-        <v>100</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="F61" s="12">
+        <v>100</v>
+      </c>
+      <c r="G61" s="12">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J61">
-        <v>1002</v>
-      </c>
-      <c r="K61">
-        <v>20000</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>2</v>
-      </c>
-      <c r="P61">
+      <c r="J61" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K61" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L61" s="12">
+        <v>0</v>
+      </c>
+      <c r="M61" s="12">
+        <v>2</v>
+      </c>
+      <c r="P61" s="12">
         <v>326</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="Q61" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U61" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A62">
+    <row r="62" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="12">
         <v>4157</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="12">
         <v>552</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="12">
         <v>384</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="12">
         <v>312</v>
       </c>
-      <c r="F62">
-        <v>100</v>
-      </c>
-      <c r="G62">
+      <c r="F62" s="12">
+        <v>100</v>
+      </c>
+      <c r="G62" s="12">
         <v>5</v>
       </c>
-      <c r="H62" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="H62" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J62">
-        <v>1002</v>
-      </c>
-      <c r="K62">
-        <v>20000</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>2</v>
-      </c>
-      <c r="P62">
+      <c r="J62" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K62" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L62" s="12">
+        <v>0</v>
+      </c>
+      <c r="M62" s="12">
+        <v>2</v>
+      </c>
+      <c r="P62" s="12">
         <v>1348</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="Q62" s="12" t="s">
         <v>179</v>
       </c>
       <c r="U62" s="9">
@@ -7884,153 +7893,153 @@
         <v>5466</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A64">
+    <row r="64" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="12">
         <v>4159</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="12">
         <v>82</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="12">
         <v>53</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="12">
         <v>43</v>
       </c>
-      <c r="F64">
-        <v>100</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="F64" s="12">
+        <v>100</v>
+      </c>
+      <c r="G64" s="12">
+        <v>0</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="J64">
-        <v>1002</v>
-      </c>
-      <c r="K64">
-        <v>20000</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>2</v>
-      </c>
-      <c r="P64">
+      <c r="J64" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K64" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L64" s="12">
+        <v>0</v>
+      </c>
+      <c r="M64" s="12">
+        <v>2</v>
+      </c>
+      <c r="P64" s="12">
         <v>278</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="Q64" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="S64">
+      <c r="S64" s="12">
         <v>6</v>
       </c>
       <c r="U64" s="9">
         <v>240</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A65">
+    <row r="65" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="12">
         <v>4160</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="12">
         <v>82</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="12">
         <v>55</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="12">
         <v>41</v>
       </c>
-      <c r="F65">
-        <v>100</v>
-      </c>
-      <c r="G65">
+      <c r="F65" s="12">
+        <v>100</v>
+      </c>
+      <c r="G65" s="12">
         <v>1</v>
       </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" t="s">
+      <c r="H65" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J65">
-        <v>1002</v>
-      </c>
-      <c r="K65">
-        <v>20000</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>2</v>
-      </c>
-      <c r="P65">
+      <c r="J65" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K65" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L65" s="12">
+        <v>0</v>
+      </c>
+      <c r="M65" s="12">
+        <v>2</v>
+      </c>
+      <c r="P65" s="12">
         <v>278</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="Q65" s="12" t="s">
         <v>187</v>
       </c>
       <c r="U65" s="9">
         <v>288</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A66">
+    <row r="66" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="12">
         <v>4161</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="12">
         <v>84</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="12">
         <v>55</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="12">
         <v>45</v>
       </c>
-      <c r="F66">
-        <v>100</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" t="s">
+      <c r="F66" s="12">
+        <v>100</v>
+      </c>
+      <c r="G66" s="12">
+        <v>0</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J66">
-        <v>1002</v>
-      </c>
-      <c r="K66">
-        <v>20000</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>2</v>
-      </c>
-      <c r="P66">
+      <c r="J66" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K66" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L66" s="12">
+        <v>0</v>
+      </c>
+      <c r="M66" s="12">
+        <v>2</v>
+      </c>
+      <c r="P66" s="12">
         <v>284</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="Q66" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U66" s="9">
@@ -8087,150 +8096,150 @@
         <v>11666</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A68">
+    <row r="68" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="12">
         <v>4163</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="12">
         <v>86</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="12">
         <v>56</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="12">
         <v>48</v>
       </c>
-      <c r="F68">
-        <v>100</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="F68" s="12">
+        <v>100</v>
+      </c>
+      <c r="G68" s="12">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J68">
-        <v>1002</v>
-      </c>
-      <c r="K68">
-        <v>20000</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>2</v>
-      </c>
-      <c r="P68">
+      <c r="J68" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K68" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L68" s="12">
+        <v>0</v>
+      </c>
+      <c r="M68" s="12">
+        <v>2</v>
+      </c>
+      <c r="P68" s="12">
         <v>290</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="Q68" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U68" s="9">
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A69">
+    <row r="69" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="12">
         <v>4164</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="12">
         <v>86</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="12">
         <v>54</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="12">
         <v>50</v>
       </c>
-      <c r="F69">
-        <v>100</v>
-      </c>
-      <c r="G69">
+      <c r="F69" s="12">
+        <v>100</v>
+      </c>
+      <c r="G69" s="12">
         <v>1</v>
       </c>
-      <c r="H69" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" t="s">
+      <c r="H69" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J69">
-        <v>1002</v>
-      </c>
-      <c r="K69">
-        <v>20000</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>2</v>
-      </c>
-      <c r="P69">
+      <c r="J69" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K69" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L69" s="12">
+        <v>0</v>
+      </c>
+      <c r="M69" s="12">
+        <v>2</v>
+      </c>
+      <c r="P69" s="12">
         <v>290</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="Q69" s="12" t="s">
         <v>187</v>
       </c>
       <c r="U69" s="9">
         <v>340</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A70">
+    <row r="70" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="12">
         <v>4165</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="12">
         <v>90</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="12">
         <v>58</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="12">
         <v>48</v>
       </c>
-      <c r="F70">
-        <v>100</v>
-      </c>
-      <c r="G70">
+      <c r="F70" s="12">
+        <v>100</v>
+      </c>
+      <c r="G70" s="12">
         <v>3</v>
       </c>
-      <c r="H70" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="H70" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J70">
-        <v>1002</v>
-      </c>
-      <c r="K70">
-        <v>20000</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>2</v>
-      </c>
-      <c r="P70">
+      <c r="J70" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K70" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L70" s="12">
+        <v>0</v>
+      </c>
+      <c r="M70" s="12">
+        <v>2</v>
+      </c>
+      <c r="P70" s="12">
         <v>296</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="Q70" s="12" t="s">
         <v>181</v>
       </c>
       <c r="U70" s="9">
@@ -8287,153 +8296,153 @@
         <v>17666</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A72">
+    <row r="72" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="12">
         <v>4167</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="12">
         <v>492</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="12">
         <v>318</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="12">
         <v>258</v>
       </c>
-      <c r="F72">
-        <v>100</v>
-      </c>
-      <c r="G72">
+      <c r="F72" s="12">
+        <v>100</v>
+      </c>
+      <c r="G72" s="12">
         <v>3</v>
       </c>
-      <c r="H72" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" t="s">
+      <c r="H72" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J72">
-        <v>1002</v>
-      </c>
-      <c r="K72">
-        <v>20000</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>2</v>
-      </c>
-      <c r="P72">
+      <c r="J72" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K72" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L72" s="12">
+        <v>0</v>
+      </c>
+      <c r="M72" s="12">
+        <v>2</v>
+      </c>
+      <c r="P72" s="12">
         <v>1168</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="Q72" s="12" t="s">
         <v>181</v>
       </c>
       <c r="U72" s="9">
         <v>386</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A73">
+    <row r="73" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="12">
         <v>4168</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="12">
         <v>492</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="12">
         <v>330</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="12">
         <v>246</v>
       </c>
-      <c r="F73">
-        <v>100</v>
-      </c>
-      <c r="G73">
+      <c r="F73" s="12">
+        <v>100</v>
+      </c>
+      <c r="G73" s="12">
         <v>1</v>
       </c>
-      <c r="H73" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="H73" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="J73">
-        <v>1002</v>
-      </c>
-      <c r="K73">
-        <v>20000</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>2</v>
-      </c>
-      <c r="P73">
+      <c r="J73" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K73" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L73" s="12">
+        <v>0</v>
+      </c>
+      <c r="M73" s="12">
+        <v>2</v>
+      </c>
+      <c r="P73" s="12">
         <v>1168</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="Q73" s="12" t="s">
         <v>187</v>
       </c>
       <c r="U73" s="9">
         <v>400</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A74">
+    <row r="74" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="12">
         <v>4169</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="12">
         <v>106</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="12">
         <v>72</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="12">
         <v>60</v>
       </c>
-      <c r="F74">
-        <v>100</v>
-      </c>
-      <c r="G74">
+      <c r="F74" s="12">
+        <v>100</v>
+      </c>
+      <c r="G74" s="12">
         <v>3</v>
       </c>
-      <c r="H74" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="H74" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J74">
-        <v>1002</v>
-      </c>
-      <c r="K74">
-        <v>20000</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>2</v>
-      </c>
-      <c r="P74">
+      <c r="J74" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K74" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L74" s="12">
+        <v>0</v>
+      </c>
+      <c r="M74" s="12">
+        <v>2</v>
+      </c>
+      <c r="P74" s="12">
         <v>338</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="Q74" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="12">
         <v>8</v>
       </c>
       <c r="U74" s="9">
@@ -8490,150 +8499,150 @@
         <v>30366</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A76">
+    <row r="76" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="12">
         <v>4171</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="12">
         <v>108</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="12">
         <v>74</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="12">
         <v>62</v>
       </c>
-      <c r="F76">
-        <v>100</v>
-      </c>
-      <c r="G76">
+      <c r="F76" s="12">
+        <v>100</v>
+      </c>
+      <c r="G76" s="12">
         <v>3</v>
       </c>
-      <c r="H76" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" t="s">
+      <c r="H76" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J76">
-        <v>1002</v>
-      </c>
-      <c r="K76">
-        <v>20000</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>2</v>
-      </c>
-      <c r="P76">
+      <c r="J76" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K76" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L76" s="12">
+        <v>0</v>
+      </c>
+      <c r="M76" s="12">
+        <v>2</v>
+      </c>
+      <c r="P76" s="12">
         <v>344</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="Q76" s="12" t="s">
         <v>181</v>
       </c>
       <c r="U76" s="9">
         <v>440</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A77">
+    <row r="77" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="12">
         <v>4172</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="12">
         <v>111</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="12">
         <v>70</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="12">
         <v>63</v>
       </c>
-      <c r="F77">
-        <v>100</v>
-      </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77" t="s">
+      <c r="F77" s="12">
+        <v>100</v>
+      </c>
+      <c r="G77" s="12">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="J77">
-        <v>1002</v>
-      </c>
-      <c r="K77">
-        <v>20000</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>2</v>
-      </c>
-      <c r="P77">
+      <c r="J77" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K77" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L77" s="12">
+        <v>0</v>
+      </c>
+      <c r="M77" s="12">
+        <v>2</v>
+      </c>
+      <c r="P77" s="12">
         <v>344</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="Q77" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U77" s="9">
         <v>480</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A78">
+    <row r="78" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="12">
         <v>4173</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="12">
         <v>110</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="12">
         <v>76</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="12">
         <v>64</v>
       </c>
-      <c r="F78">
-        <v>100</v>
-      </c>
-      <c r="G78">
+      <c r="F78" s="12">
+        <v>100</v>
+      </c>
+      <c r="G78" s="12">
         <v>4</v>
       </c>
-      <c r="H78" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" t="s">
+      <c r="H78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="J78">
-        <v>1002</v>
-      </c>
-      <c r="K78">
-        <v>20000</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>2</v>
-      </c>
-      <c r="P78">
+      <c r="J78" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K78" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L78" s="12">
+        <v>0</v>
+      </c>
+      <c r="M78" s="12">
+        <v>2</v>
+      </c>
+      <c r="P78" s="12">
         <v>350</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="Q78" s="12" t="s">
         <v>178</v>
       </c>
       <c r="U78" s="9">
@@ -8690,150 +8699,150 @@
         <v>4133</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A80">
+    <row r="80" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="12">
         <v>4175</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="12">
         <v>114</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="12">
         <v>78</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="12">
         <v>64</v>
       </c>
-      <c r="F80">
-        <v>100</v>
-      </c>
-      <c r="G80">
+      <c r="F80" s="12">
+        <v>100</v>
+      </c>
+      <c r="G80" s="12">
         <v>4</v>
       </c>
-      <c r="H80" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80" t="s">
+      <c r="H80" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="J80">
-        <v>1002</v>
-      </c>
-      <c r="K80">
-        <v>20000</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>2</v>
-      </c>
-      <c r="P80">
+      <c r="J80" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K80" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L80" s="12">
+        <v>0</v>
+      </c>
+      <c r="M80" s="12">
+        <v>2</v>
+      </c>
+      <c r="P80" s="12">
         <v>356</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="Q80" s="12" t="s">
         <v>178</v>
       </c>
       <c r="U80" s="9">
         <v>533</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A81">
+    <row r="81" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="12">
         <v>4176</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="12">
         <v>114</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="12">
         <v>76</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="12">
         <v>66</v>
       </c>
-      <c r="F81">
-        <v>100</v>
-      </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-      <c r="H81" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" t="s">
+      <c r="F81" s="12">
+        <v>100</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J81">
-        <v>1002</v>
-      </c>
-      <c r="K81">
-        <v>20000</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>2</v>
-      </c>
-      <c r="P81">
+      <c r="J81" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K81" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L81" s="12">
+        <v>0</v>
+      </c>
+      <c r="M81" s="12">
+        <v>2</v>
+      </c>
+      <c r="P81" s="12">
         <v>356</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="Q81" s="12" t="s">
         <v>188</v>
       </c>
       <c r="U81" s="9">
         <v>560</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A82">
+    <row r="82" spans="1:21" s="12" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="12">
         <v>4177</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="12">
         <v>636</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="12">
         <v>432</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="12">
         <v>360</v>
       </c>
-      <c r="F82">
-        <v>100</v>
-      </c>
-      <c r="G82">
+      <c r="F82" s="12">
+        <v>100</v>
+      </c>
+      <c r="G82" s="12">
         <v>4</v>
       </c>
-      <c r="H82" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" t="s">
+      <c r="H82" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J82">
-        <v>1002</v>
-      </c>
-      <c r="K82">
-        <v>20000</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>2</v>
-      </c>
-      <c r="P82">
+      <c r="J82" s="12">
+        <v>1002</v>
+      </c>
+      <c r="K82" s="12">
+        <v>20000</v>
+      </c>
+      <c r="L82" s="12">
+        <v>0</v>
+      </c>
+      <c r="M82" s="12">
+        <v>2</v>
+      </c>
+      <c r="P82" s="12">
         <v>1528</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="Q82" s="12" t="s">
         <v>178</v>
       </c>
       <c r="U82" s="9">
@@ -8890,17 +8899,17 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" s="12" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U84" s="9">
         <v>626</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U85" s="9">
         <v>626</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U86" s="9">
         <v>633</v>
       </c>
@@ -8910,17 +8919,17 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U88" s="9">
         <v>640</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U89" s="9">
         <v>653</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U90" s="9">
         <v>666</v>
       </c>
@@ -8930,17 +8939,17 @@
         <v>28333</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U92" s="9">
         <v>680</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U93" s="9">
         <v>700</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U94" s="9">
         <v>733</v>
       </c>
@@ -8950,17 +8959,17 @@
         <v>33333</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U96" s="9">
         <v>866</v>
       </c>
     </row>
-    <row r="97" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U97" s="9">
         <v>900</v>
       </c>
     </row>
-    <row r="98" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="98" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U98" s="9">
         <v>920</v>
       </c>
@@ -8970,17 +8979,17 @@
         <v>8333</v>
       </c>
     </row>
-    <row r="100" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="100" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U100" s="9">
         <v>973</v>
       </c>
     </row>
-    <row r="101" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U101" s="9">
         <v>1033</v>
       </c>
     </row>
-    <row r="102" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U102" s="9">
         <v>1080</v>
       </c>
@@ -8990,17 +8999,17 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="104" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="104" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U104" s="9">
         <v>1120</v>
       </c>
     </row>
-    <row r="105" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="105" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U105" s="9">
         <v>1120</v>
       </c>
     </row>
-    <row r="106" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="106" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U106" s="9">
         <v>1173</v>
       </c>
@@ -9010,17 +9019,17 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="108" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="108" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U108" s="9">
         <v>1186</v>
       </c>
     </row>
-    <row r="109" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="109" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U109" s="9">
         <v>1333</v>
       </c>
     </row>
-    <row r="110" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="110" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U110" s="9">
         <v>1453</v>
       </c>
@@ -9030,17 +9039,17 @@
         <v>31200</v>
       </c>
     </row>
-    <row r="112" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="112" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U112" s="9">
         <v>1453</v>
       </c>
     </row>
-    <row r="113" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="113" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U113" s="9">
         <v>1466</v>
       </c>
     </row>
-    <row r="114" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="114" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="U114" s="9">
         <v>1520</v>
       </c>
@@ -9050,6 +9059,7 @@
         <v>40000</v>
       </c>
     </row>
+    <row r="116" spans="21:21" s="12" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="U15:U115">
     <filterColumn colId="0">
@@ -9062,4 +9072,48 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B7:C14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>48</v>
+      </c>
+      <c r="C7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <f>B7*B8</f>
+        <v>288</v>
+      </c>
+      <c r="C10">
+        <f>C7*C8</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <f>96*4</f>
+        <v>384</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -1399,15 +1399,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>枯树精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部落巫医</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>scale</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枯树精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部落巫医</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1813,16 +1813,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AF84"/>
+  <dimension ref="A2:N84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.25" style="6" customWidth="1"/>
     <col min="3" max="8" width="9" style="5" customWidth="1"/>
     <col min="9" max="10" width="21.875" style="5" customWidth="1"/>
-    <col min="11" max="15" width="9" style="5" customWidth="1"/>
-    <col min="16" max="17" width="9" style="5"/>
-    <col min="33" max="16384" width="9" style="5"/>
+    <col min="11" max="14" width="9" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -1898,7 +1897,7 @@
         <v>117</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>10</v>
@@ -2907,7 +2906,7 @@
         <v>16</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J26" s="5">
         <v>1</v>
@@ -3831,7 +3830,7 @@
         <v>16</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J47" s="5">
         <v>1</v>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$H$16:$J$100</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="572">
   <si>
     <t>int</t>
   </si>
@@ -860,980 +859,984 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>召唤小青蛙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>中毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>致幻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利爪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电击1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>流血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>振奋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分裂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>镜之刃</t>
+  </si>
+  <si>
+    <t>自动反击</t>
+  </si>
+  <si>
+    <t>剑刃波动</t>
+  </si>
+  <si>
+    <t>刀剑架势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定几率反射敌人攻击造成的一半伤害</t>
+  </si>
+  <si>
+    <t>一定几率受到攻击后自动进行反击</t>
+  </si>
+  <si>
+    <t>攻击单个敌人时低概率处罚额外的溅射伤害</t>
+  </si>
+  <si>
+    <t>一定几率大幅提升本回合的灵巧值</t>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隼之斩</t>
+  </si>
+  <si>
+    <t>剑舞</t>
+  </si>
+  <si>
+    <t>横扫千军</t>
+  </si>
+  <si>
+    <t>强力斩</t>
+  </si>
+  <si>
+    <t>刃之防御</t>
+  </si>
+  <si>
+    <t>对单个敌人进行2次高速的攻击</t>
+  </si>
+  <si>
+    <t>随机对敌人攻击4次</t>
+  </si>
+  <si>
+    <t>对全体敌人造成巨大伤害</t>
+  </si>
+  <si>
+    <t>对单个敌人造成巨大伤害的攻击</t>
+  </si>
+  <si>
+    <t>提升一名同伴的防御力3个回合</t>
+  </si>
+  <si>
+    <t>对敌单体攻击，并恢复一定血量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉睡之剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击单个敌人，一定概率使其睡眠</t>
+  </si>
+  <si>
+    <t>疾风爪</t>
+  </si>
+  <si>
+    <t>裂钢爪</t>
+  </si>
+  <si>
+    <t>虎搏爪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙击爪</t>
+  </si>
+  <si>
+    <t>对一个敌人快速攻击两次</t>
+  </si>
+  <si>
+    <t>对单个敌人进行强力攻击并降防御3回合</t>
+  </si>
+  <si>
+    <t>对单个敌人进行强力攻击并一定几率使其眩晕2回合</t>
+  </si>
+  <si>
+    <t>对一个敌人的要害进行极其强烈的攻击</t>
+  </si>
+  <si>
+    <t>睡神猎杀</t>
+  </si>
+  <si>
+    <t>死神狩猎</t>
+  </si>
+  <si>
+    <t>对睡眠等定身的敌人造成6倍伤害</t>
+  </si>
+  <si>
+    <t>对流血等持续受伤的敌人造成6倍伤害</t>
+  </si>
+  <si>
+    <t>爆裂爪</t>
+  </si>
+  <si>
+    <t>爆裂</t>
+  </si>
+  <si>
+    <t>鹰切爪</t>
+  </si>
+  <si>
+    <t>涂毒</t>
+  </si>
+  <si>
+    <t>晶石风暴</t>
+  </si>
+  <si>
+    <t>攻击一个敌人并对其他敌人造成溅射伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对单个敌人进行强力攻击并一定几率使其流血</t>
+  </si>
+  <si>
+    <t>对武器涂抹毒药，3回合内一定几率使敌人中毒</t>
+  </si>
+  <si>
+    <t>一次性抛出1000晶石，无视敌方防御造成100伤害</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>刀剑架势</t>
+  </si>
+  <si>
+    <t>暗影步伐</t>
+  </si>
+  <si>
+    <t>晶石之手</t>
+  </si>
+  <si>
+    <t>偷窃之手</t>
+  </si>
+  <si>
+    <t>神秘之悟</t>
+  </si>
+  <si>
+    <t>回音之悟</t>
+  </si>
+  <si>
+    <t>元素之悟</t>
+  </si>
+  <si>
+    <t>魔道之悟</t>
+  </si>
+  <si>
+    <t>圣女守护</t>
+  </si>
+  <si>
+    <t>圣主眷恋</t>
+  </si>
+  <si>
+    <t>祷告微风</t>
+  </si>
+  <si>
+    <t>英灵守护</t>
+  </si>
+  <si>
+    <t>斩击</t>
+  </si>
+  <si>
+    <t>爪击</t>
+  </si>
+  <si>
+    <t>敲击</t>
+  </si>
+  <si>
+    <t>奥术弹</t>
+  </si>
+  <si>
+    <t>撞击</t>
+  </si>
+  <si>
+    <t>冲刺</t>
+  </si>
+  <si>
+    <t>咬击</t>
+  </si>
+  <si>
+    <t>史莱姆水滴</t>
+  </si>
+  <si>
+    <t>十字冲击</t>
+  </si>
+  <si>
+    <t>怪物飞弹</t>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+  </si>
+  <si>
+    <t>急救电击</t>
+  </si>
+  <si>
+    <t>保护</t>
+  </si>
+  <si>
+    <t>口哨</t>
+  </si>
+  <si>
+    <t>沉睡之剑</t>
+  </si>
+  <si>
+    <t>虎搏爪</t>
+  </si>
+  <si>
+    <t>蓄力</t>
+  </si>
+  <si>
+    <t>沉睡诅咒</t>
+  </si>
+  <si>
+    <t>封魔秘术</t>
+  </si>
+  <si>
+    <t>会心必中</t>
+  </si>
+  <si>
+    <t>万物归零</t>
+  </si>
+  <si>
+    <t>奥术之星</t>
+  </si>
+  <si>
+    <t>极寒冰箭</t>
+  </si>
+  <si>
+    <t>雷电之罚</t>
+  </si>
+  <si>
+    <t>沙尘风暴</t>
+  </si>
+  <si>
+    <t>烈焰冲击</t>
+  </si>
+  <si>
+    <t>魔女之吻</t>
+  </si>
+  <si>
+    <t>奥术觉醒</t>
+  </si>
+  <si>
+    <t>魔结界</t>
+  </si>
+  <si>
+    <t>冥想</t>
+  </si>
+  <si>
+    <t>祝福之杖</t>
+  </si>
+  <si>
+    <t>治愈之杖</t>
+  </si>
+  <si>
+    <t>复活之杖</t>
+  </si>
+  <si>
+    <t>苏醒之杖</t>
+  </si>
+  <si>
+    <t>能量传递</t>
+  </si>
+  <si>
+    <t>祝福之雨</t>
+  </si>
+  <si>
+    <t>恶灵驱逐</t>
+  </si>
+  <si>
+    <t>圣愈之风</t>
+  </si>
+  <si>
+    <t>牺牲惩戒</t>
+  </si>
+  <si>
+    <t>光之波动</t>
+  </si>
+  <si>
+    <t>怪物火弹</t>
+  </si>
+  <si>
+    <t>火之息</t>
+  </si>
+  <si>
+    <t>怪物电弹</t>
+  </si>
+  <si>
+    <t>冰之息</t>
+  </si>
+  <si>
+    <t>冰弹</t>
+  </si>
+  <si>
+    <t>箭矢</t>
+  </si>
+  <si>
+    <t>激光眼</t>
+  </si>
+  <si>
+    <t>投石</t>
+  </si>
+  <si>
+    <t>地刺</t>
+  </si>
+  <si>
+    <t>紧缚</t>
+  </si>
+  <si>
+    <t>风之刃</t>
+  </si>
+  <si>
+    <t>奥术冰弹</t>
+  </si>
+  <si>
+    <t>喷冰2</t>
+  </si>
+  <si>
+    <t>烈焰枪</t>
+  </si>
+  <si>
+    <t>熔岩地刺</t>
+  </si>
+  <si>
+    <t>爆裂咬</t>
+  </si>
+  <si>
+    <t>冰弹齐射</t>
+  </si>
+  <si>
+    <t>投冰块</t>
+  </si>
+  <si>
+    <t>雪崩</t>
+  </si>
+  <si>
+    <t>切割</t>
+  </si>
+  <si>
+    <t>抛骨头</t>
+  </si>
+  <si>
+    <t>刀波</t>
+  </si>
+  <si>
+    <t>震地</t>
+  </si>
+  <si>
+    <t>爆裂刺杀</t>
+  </si>
+  <si>
+    <t>致盲黑云</t>
+  </si>
+  <si>
+    <t>奇迹斩(怪物)</t>
+  </si>
+  <si>
+    <t>喷火(怪物)</t>
+  </si>
+  <si>
+    <t>横扫千军(怪物)</t>
+  </si>
+  <si>
+    <t>自我恢复(怪物)</t>
+  </si>
+  <si>
+    <t>喷冰(怪物)</t>
+  </si>
+  <si>
+    <t>祝福之雨(怪物)</t>
+  </si>
+  <si>
+    <t>震地（牛）</t>
+  </si>
+  <si>
+    <t>斩击(流血)</t>
+  </si>
+  <si>
+    <t>咬击(中毒)</t>
+  </si>
+  <si>
+    <t>怪物飞弹(致盲)</t>
+  </si>
+  <si>
+    <t>咬击（火螃蟹）</t>
+  </si>
+  <si>
+    <t>敲击(晕</t>
+  </si>
+  <si>
+    <t>爪击(流血)</t>
+  </si>
+  <si>
+    <t>怪物飞弹(沉睡)</t>
+  </si>
+  <si>
+    <t>怪物飞弹(混乱)</t>
+  </si>
+  <si>
+    <t>怪物飞弹(分散)</t>
+  </si>
+  <si>
+    <t>音波</t>
+  </si>
+  <si>
+    <t>震地（da）</t>
+  </si>
+  <si>
+    <t>沉睡</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>回春</t>
+  </si>
+  <si>
+    <t>自我恢复</t>
+  </si>
+  <si>
+    <t>减少防御</t>
+  </si>
+  <si>
+    <t>冰冻</t>
+  </si>
+  <si>
+    <t>雷霆眩晕</t>
+  </si>
+  <si>
+    <t>致盲</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>牺牲</t>
+  </si>
+  <si>
+    <t>祷告</t>
+  </si>
+  <si>
+    <t>恢复能量</t>
+  </si>
+  <si>
+    <t>回春(道具）</t>
+  </si>
+  <si>
+    <t>回春0</t>
+  </si>
+  <si>
+    <t>回春1</t>
+  </si>
+  <si>
+    <t>回春2</t>
+  </si>
+  <si>
+    <t>疗毒0</t>
+  </si>
+  <si>
+    <t>疗毒1</t>
+  </si>
+  <si>
+    <t>疗毒2</t>
+  </si>
+  <si>
+    <t>苏醒0</t>
+  </si>
+  <si>
+    <t>苏醒1</t>
+  </si>
+  <si>
+    <t>苏醒2</t>
+  </si>
+  <si>
+    <t>混乱恢复</t>
+  </si>
+  <si>
+    <t>万能药</t>
+  </si>
+  <si>
+    <t>全恢复</t>
+  </si>
+  <si>
+    <t>回能0</t>
+  </si>
+  <si>
+    <t>回能1</t>
+  </si>
+  <si>
+    <t>醒2</t>
+  </si>
+  <si>
+    <t>混乱药</t>
+  </si>
+  <si>
+    <t>减少速度</t>
+  </si>
+  <si>
+    <t>烧伤</t>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>增加攻击</t>
+  </si>
+  <si>
+    <t>增加防御</t>
+  </si>
+  <si>
+    <t>减少攻击</t>
+  </si>
+  <si>
+    <t>火之力量</t>
+  </si>
+  <si>
+    <t>冰之力量</t>
+  </si>
+  <si>
+    <t>光之力量</t>
+  </si>
+  <si>
+    <t>暗之力量</t>
+  </si>
+  <si>
+    <t>风之力量</t>
+  </si>
+  <si>
+    <t>火焰旋律</t>
+  </si>
+  <si>
+    <t>冰雪旋律</t>
+  </si>
+  <si>
+    <t>光之旋律</t>
+  </si>
+  <si>
+    <t>暗之旋律</t>
+  </si>
+  <si>
+    <t>风之旋律</t>
+  </si>
+  <si>
+    <t>notice</t>
+  </si>
+  <si>
+    <t>对敌人攻击时一定几率偷得一定数量的晶石</t>
+  </si>
+  <si>
+    <t>对敌人攻击时一定几率偷得特定的道具</t>
+  </si>
+  <si>
+    <t>一定几率使魔法消耗能量减半</t>
+  </si>
+  <si>
+    <t>一定几率提升元素攻击力</t>
+  </si>
+  <si>
+    <t>一定几率提升暴击率</t>
+  </si>
+  <si>
+    <t>一定几率提升防御力</t>
+  </si>
+  <si>
+    <t>一定几率在回合结束后自动回复部分HP</t>
+  </si>
+  <si>
+    <t>一定几率额外恢复部分能量</t>
+  </si>
+  <si>
+    <t>在死亡后有一定几率自动复活</t>
+  </si>
+  <si>
+    <t>对单个敌人造成普通伤害</t>
+  </si>
+  <si>
+    <t>对敌单体攻击，并恢复一定血量</t>
+  </si>
+  <si>
+    <t>对死亡的同伴进行急救，一定概率使其复活，并恢复一半HP</t>
+  </si>
+  <si>
+    <t>本回合代替指定的一名同伴承受所有攻击</t>
+  </si>
+  <si>
+    <t>吹口哨吸引一个敌人攻击自己</t>
+  </si>
+  <si>
+    <t>使下回合攻击力提升</t>
+  </si>
+  <si>
+    <t>攻击一个敌人并对其他敌人造成溅射伤害。</t>
+  </si>
+  <si>
+    <t>一定几率使一名敌人进入沉睡</t>
+  </si>
+  <si>
+    <t>一定几率封印一名敌人的能量增长</t>
+  </si>
+  <si>
+    <t>使一名同伴的攻击必然会心</t>
+  </si>
+  <si>
+    <t>解除一名敌人身上所有有益状态</t>
+  </si>
+  <si>
+    <t>使用奥术能量随机对敌人攻击4次</t>
+  </si>
+  <si>
+    <t>对全体敌人造成冰属性伤害，并有一定几率使其冰冻</t>
+  </si>
+  <si>
+    <t>对全体敌人造成光属性伤害，并有一定几率使其眩晕</t>
+  </si>
+  <si>
+    <t>对全体敌人造成风属性伤害，并有一定几率使其致盲</t>
+  </si>
+  <si>
+    <t>对全体敌人造成火属性伤害，并有一定几率使其燃烧</t>
+  </si>
+  <si>
+    <t>对全体敌人造成暗属性伤害，并有一定几率使其虚弱</t>
+  </si>
+  <si>
+    <t>一定几率使单个敌人混乱</t>
+  </si>
+  <si>
+    <t>大幅增加攻击伤害2回合</t>
+  </si>
+  <si>
+    <t>减弱敌人对元素伤害的抵抗力</t>
+  </si>
+  <si>
+    <t>快速回复能量</t>
+  </si>
+  <si>
+    <t>回复一名队友的HP</t>
+  </si>
+  <si>
+    <t>使一名队友的HP全满</t>
+  </si>
+  <si>
+    <t>复活一名队友，并使其HP回复一半</t>
+  </si>
+  <si>
+    <t>使沉睡的队友苏醒</t>
+  </si>
+  <si>
+    <t>将自己的一半能量传输给同伴</t>
+  </si>
+  <si>
+    <t>回复全体同伴的HP</t>
+  </si>
+  <si>
+    <t>驱逐单个同伴身上的有害状态</t>
+  </si>
+  <si>
+    <t>复活所有死亡的队友，并使其HP回复一半</t>
+  </si>
+  <si>
+    <t>以牺牲自己为代价对单个敌人造成巨大伤害</t>
+  </si>
+  <si>
+    <t>驱逐将全体同伴的有害状态，并唤醒睡眠的同伴</t>
+  </si>
+  <si>
+    <t>对群体伤害</t>
+  </si>
+  <si>
+    <t>对群体造成火属性伤害</t>
+  </si>
+  <si>
+    <t>对全体敌人造成伤害</t>
+  </si>
+  <si>
+    <t>使敌人眩晕2个回合</t>
+  </si>
+  <si>
+    <t>对单个敌人造成风属性伤害</t>
+  </si>
+  <si>
+    <t>对单个敌人造成火属性伤害</t>
+  </si>
+  <si>
+    <t>对全体敌人造成火属性伤害</t>
+  </si>
+  <si>
+    <t>对单个敌人造成普通伤害，并有一定几率使其流血</t>
+  </si>
+  <si>
+    <t>对全体敌人造成伤害，并有一定几率是其眩晕</t>
+  </si>
+  <si>
+    <t>生成黑云遮蔽一个敌人的视线</t>
+  </si>
+  <si>
+    <t>对全体敌人造成普通伤害</t>
+  </si>
+  <si>
+    <t>，一定概率使其复活，并恢复一半HP</t>
+  </si>
+  <si>
+    <t>降低防御</t>
+  </si>
+  <si>
+    <t>疗毒</t>
+  </si>
+  <si>
+    <t>使眩晕的队友苏醒</t>
+  </si>
+  <si>
+    <t>我方单体解除混乱</t>
+  </si>
+  <si>
+    <t>回能</t>
+  </si>
+  <si>
+    <t>使睡眠的队友苏醒</t>
+  </si>
+  <si>
+    <t>增加速度</t>
+  </si>
+  <si>
+    <t>为一名同伴的攻击附加火属性</t>
+  </si>
+  <si>
+    <t>为一名同伴的攻击附加冰属性</t>
+  </si>
+  <si>
+    <t>为一名同伴的攻击附加光属性</t>
+  </si>
+  <si>
+    <t>为一名同伴的攻击附加暗属性</t>
+  </si>
+  <si>
+    <t>为一名同伴的攻击附加风属性</t>
+  </si>
+  <si>
+    <t>减轻一名同伴所受到的火属性伤害</t>
+  </si>
+  <si>
+    <t>减轻一名同伴所受到的冰属性伤害</t>
+  </si>
+  <si>
+    <t>减轻一名同伴所受到的光属性伤害</t>
+  </si>
+  <si>
+    <t>减轻一名同伴所受到的暗属性伤害</t>
+  </si>
+  <si>
+    <t>减轻一名同伴所受到的风属性伤害</t>
+  </si>
+  <si>
+    <t>长剑</t>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+  </si>
+  <si>
+    <t>大地之剑</t>
+  </si>
+  <si>
+    <t>冰之刃</t>
+  </si>
+  <si>
+    <t>铁枪</t>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+  </si>
+  <si>
+    <t>血腥之枪</t>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>战斧</t>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+  </si>
+  <si>
+    <t>藤鞭</t>
+  </si>
+  <si>
+    <t>女王鞭</t>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
+  </si>
+  <si>
+    <t>烈焰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹰切爪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士冲击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒爆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒猎杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥囚笼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王之春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>风刃</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>召唤小青蛙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>眩晕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒</t>
-  </si>
-  <si>
-    <t>中毒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>致幻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>利爪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电击1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流血</t>
-  </si>
-  <si>
-    <t>流血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>振奋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>镜之刃</t>
-  </si>
-  <si>
-    <t>自动反击</t>
-  </si>
-  <si>
-    <t>剑刃波动</t>
-  </si>
-  <si>
-    <t>刀剑架势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一定几率反射敌人攻击造成的一半伤害</t>
-  </si>
-  <si>
-    <t>一定几率受到攻击后自动进行反击</t>
-  </si>
-  <si>
-    <t>攻击单个敌人时低概率处罚额外的溅射伤害</t>
-  </si>
-  <si>
-    <t>一定几率大幅提升本回合的灵巧值</t>
-  </si>
-  <si>
-    <t>奇迹斩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>隼之斩</t>
-  </si>
-  <si>
-    <t>剑舞</t>
-  </si>
-  <si>
-    <t>横扫千军</t>
-  </si>
-  <si>
-    <t>强力斩</t>
-  </si>
-  <si>
-    <t>刃之防御</t>
-  </si>
-  <si>
-    <t>对单个敌人进行2次高速的攻击</t>
-  </si>
-  <si>
-    <t>随机对敌人攻击4次</t>
-  </si>
-  <si>
-    <t>对全体敌人造成巨大伤害</t>
-  </si>
-  <si>
-    <t>对单个敌人造成巨大伤害的攻击</t>
-  </si>
-  <si>
-    <t>提升一名同伴的防御力3个回合</t>
-  </si>
-  <si>
-    <t>对敌单体攻击，并恢复一定血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉睡之剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击单个敌人，一定概率使其睡眠</t>
-  </si>
-  <si>
-    <t>疾风爪</t>
-  </si>
-  <si>
-    <t>裂钢爪</t>
-  </si>
-  <si>
-    <t>虎搏爪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙击爪</t>
-  </si>
-  <si>
-    <t>对一个敌人快速攻击两次</t>
-  </si>
-  <si>
-    <t>对单个敌人进行强力攻击并降防御3回合</t>
-  </si>
-  <si>
-    <t>对单个敌人进行强力攻击并一定几率使其眩晕2回合</t>
-  </si>
-  <si>
-    <t>对一个敌人的要害进行极其强烈的攻击</t>
-  </si>
-  <si>
-    <t>睡神猎杀</t>
-  </si>
-  <si>
-    <t>死神狩猎</t>
-  </si>
-  <si>
-    <t>对睡眠等定身的敌人造成6倍伤害</t>
-  </si>
-  <si>
-    <t>对流血等持续受伤的敌人造成6倍伤害</t>
-  </si>
-  <si>
-    <t>爆裂爪</t>
-  </si>
-  <si>
-    <t>爆裂</t>
-  </si>
-  <si>
-    <t>鹰切爪</t>
-  </si>
-  <si>
-    <t>涂毒</t>
-  </si>
-  <si>
-    <t>晶石风暴</t>
-  </si>
-  <si>
-    <t>攻击一个敌人并对其他敌人造成溅射伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对单个敌人进行强力攻击并一定几率使其流血</t>
-  </si>
-  <si>
-    <t>对武器涂抹毒药，3回合内一定几率使敌人中毒</t>
-  </si>
-  <si>
-    <t>一次性抛出1000晶石，无视敌方防御造成100伤害</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>刀剑架势</t>
-  </si>
-  <si>
-    <t>暗影步伐</t>
-  </si>
-  <si>
-    <t>晶石之手</t>
-  </si>
-  <si>
-    <t>偷窃之手</t>
-  </si>
-  <si>
-    <t>神秘之悟</t>
-  </si>
-  <si>
-    <t>回音之悟</t>
-  </si>
-  <si>
-    <t>元素之悟</t>
-  </si>
-  <si>
-    <t>魔道之悟</t>
-  </si>
-  <si>
-    <t>圣女守护</t>
-  </si>
-  <si>
-    <t>圣主眷恋</t>
-  </si>
-  <si>
-    <t>祷告微风</t>
-  </si>
-  <si>
-    <t>英灵守护</t>
-  </si>
-  <si>
-    <t>斩击</t>
-  </si>
-  <si>
-    <t>爪击</t>
-  </si>
-  <si>
-    <t>敲击</t>
-  </si>
-  <si>
-    <t>奥术弹</t>
-  </si>
-  <si>
-    <t>撞击</t>
-  </si>
-  <si>
-    <t>冲刺</t>
-  </si>
-  <si>
-    <t>咬击</t>
-  </si>
-  <si>
-    <t>史莱姆水滴</t>
-  </si>
-  <si>
-    <t>十字冲击</t>
-  </si>
-  <si>
-    <t>怪物飞弹</t>
-  </si>
-  <si>
-    <t>奇迹斩</t>
-  </si>
-  <si>
-    <t>急救电击</t>
-  </si>
-  <si>
-    <t>保护</t>
-  </si>
-  <si>
-    <t>口哨</t>
-  </si>
-  <si>
-    <t>沉睡之剑</t>
-  </si>
-  <si>
-    <t>虎搏爪</t>
-  </si>
-  <si>
-    <t>蓄力</t>
-  </si>
-  <si>
-    <t>沉睡诅咒</t>
-  </si>
-  <si>
-    <t>封魔秘术</t>
-  </si>
-  <si>
-    <t>会心必中</t>
-  </si>
-  <si>
-    <t>万物归零</t>
-  </si>
-  <si>
-    <t>奥术之星</t>
-  </si>
-  <si>
-    <t>极寒冰箭</t>
-  </si>
-  <si>
-    <t>雷电之罚</t>
-  </si>
-  <si>
-    <t>沙尘风暴</t>
-  </si>
-  <si>
-    <t>烈焰冲击</t>
-  </si>
-  <si>
-    <t>幽冥黑洞</t>
-  </si>
-  <si>
-    <t>魔女之吻</t>
-  </si>
-  <si>
-    <t>奥术觉醒</t>
-  </si>
-  <si>
-    <t>魔结界</t>
-  </si>
-  <si>
-    <t>冥想</t>
-  </si>
-  <si>
-    <t>祝福之杖</t>
-  </si>
-  <si>
-    <t>治愈之杖</t>
-  </si>
-  <si>
-    <t>复活之杖</t>
-  </si>
-  <si>
-    <t>苏醒之杖</t>
-  </si>
-  <si>
-    <t>能量传递</t>
-  </si>
-  <si>
-    <t>祝福之雨</t>
-  </si>
-  <si>
-    <t>恶灵驱逐</t>
-  </si>
-  <si>
-    <t>圣愈之风</t>
-  </si>
-  <si>
-    <t>牺牲惩戒</t>
-  </si>
-  <si>
-    <t>光之波动</t>
-  </si>
-  <si>
-    <t>怪物火弹</t>
-  </si>
-  <si>
-    <t>火之息</t>
-  </si>
-  <si>
-    <t>怪物电弹</t>
-  </si>
-  <si>
-    <t>冰之息</t>
-  </si>
-  <si>
-    <t>冰弹</t>
-  </si>
-  <si>
-    <t>箭矢</t>
-  </si>
-  <si>
-    <t>激光眼</t>
-  </si>
-  <si>
-    <t>投石</t>
-  </si>
-  <si>
-    <t>地刺</t>
-  </si>
-  <si>
-    <t>紧缚</t>
-  </si>
-  <si>
-    <t>风之刃</t>
-  </si>
-  <si>
-    <t>奥术冰弹</t>
-  </si>
-  <si>
-    <t>喷冰2</t>
-  </si>
-  <si>
-    <t>烈焰枪</t>
-  </si>
-  <si>
-    <t>熔岩地刺</t>
-  </si>
-  <si>
-    <t>爆裂咬</t>
-  </si>
-  <si>
-    <t>冰弹齐射</t>
-  </si>
-  <si>
-    <t>投冰块</t>
-  </si>
-  <si>
-    <t>雪崩</t>
-  </si>
-  <si>
-    <t>切割</t>
-  </si>
-  <si>
-    <t>抛骨头</t>
-  </si>
-  <si>
-    <t>刀波</t>
-  </si>
-  <si>
-    <t>震地</t>
-  </si>
-  <si>
-    <t>爆裂刺杀</t>
-  </si>
-  <si>
-    <t>致盲黑云</t>
-  </si>
-  <si>
-    <t>奇迹斩(怪物)</t>
-  </si>
-  <si>
-    <t>喷火(怪物)</t>
-  </si>
-  <si>
-    <t>横扫千军(怪物)</t>
-  </si>
-  <si>
-    <t>自我恢复(怪物)</t>
-  </si>
-  <si>
-    <t>喷冰(怪物)</t>
-  </si>
-  <si>
-    <t>祝福之雨(怪物)</t>
-  </si>
-  <si>
-    <t>震地（牛）</t>
-  </si>
-  <si>
-    <t>斩击(流血)</t>
-  </si>
-  <si>
-    <t>咬击(中毒)</t>
-  </si>
-  <si>
-    <t>怪物飞弹(致盲)</t>
-  </si>
-  <si>
-    <t>咬击（火螃蟹）</t>
-  </si>
-  <si>
-    <t>敲击(晕</t>
-  </si>
-  <si>
-    <t>爪击(流血)</t>
-  </si>
-  <si>
-    <t>怪物飞弹(沉睡)</t>
-  </si>
-  <si>
-    <t>怪物飞弹(混乱)</t>
-  </si>
-  <si>
-    <t>怪物飞弹(分散)</t>
-  </si>
-  <si>
-    <t>音波</t>
-  </si>
-  <si>
-    <t>震地（da）</t>
-  </si>
-  <si>
-    <t>沉睡</t>
-  </si>
-  <si>
-    <t>复活</t>
-  </si>
-  <si>
-    <t>回春</t>
-  </si>
-  <si>
-    <t>自我恢复</t>
-  </si>
-  <si>
-    <t>减少防御</t>
-  </si>
-  <si>
-    <t>冰冻</t>
-  </si>
-  <si>
-    <t>雷霆眩晕</t>
-  </si>
-  <si>
-    <t>致盲</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>牺牲</t>
-  </si>
-  <si>
-    <t>祷告</t>
-  </si>
-  <si>
-    <t>恢复能量</t>
-  </si>
-  <si>
-    <t>回春(道具）</t>
-  </si>
-  <si>
-    <t>回春0</t>
-  </si>
-  <si>
-    <t>回春1</t>
-  </si>
-  <si>
-    <t>回春2</t>
-  </si>
-  <si>
-    <t>疗毒0</t>
-  </si>
-  <si>
-    <t>疗毒1</t>
-  </si>
-  <si>
-    <t>疗毒2</t>
-  </si>
-  <si>
-    <t>苏醒0</t>
-  </si>
-  <si>
-    <t>苏醒1</t>
-  </si>
-  <si>
-    <t>苏醒2</t>
-  </si>
-  <si>
-    <t>混乱恢复</t>
-  </si>
-  <si>
-    <t>万能药</t>
-  </si>
-  <si>
-    <t>全恢复</t>
-  </si>
-  <si>
-    <t>回能0</t>
-  </si>
-  <si>
-    <t>回能1</t>
-  </si>
-  <si>
-    <t>醒2</t>
-  </si>
-  <si>
-    <t>混乱药</t>
-  </si>
-  <si>
-    <t>减少速度</t>
-  </si>
-  <si>
-    <t>烧伤</t>
-  </si>
-  <si>
-    <t>混乱</t>
-  </si>
-  <si>
-    <t>增加攻击</t>
-  </si>
-  <si>
-    <t>增加防御</t>
-  </si>
-  <si>
-    <t>减少攻击</t>
-  </si>
-  <si>
-    <t>火之力量</t>
-  </si>
-  <si>
-    <t>冰之力量</t>
-  </si>
-  <si>
-    <t>光之力量</t>
-  </si>
-  <si>
-    <t>暗之力量</t>
-  </si>
-  <si>
-    <t>风之力量</t>
-  </si>
-  <si>
-    <t>火焰旋律</t>
-  </si>
-  <si>
-    <t>冰雪旋律</t>
-  </si>
-  <si>
-    <t>光之旋律</t>
-  </si>
-  <si>
-    <t>暗之旋律</t>
-  </si>
-  <si>
-    <t>风之旋律</t>
-  </si>
-  <si>
-    <t>notice</t>
-  </si>
-  <si>
-    <t>对敌人攻击时一定几率偷得一定数量的晶石</t>
-  </si>
-  <si>
-    <t>对敌人攻击时一定几率偷得特定的道具</t>
-  </si>
-  <si>
-    <t>一定几率使魔法消耗能量减半</t>
-  </si>
-  <si>
-    <t>一定几率提升元素攻击力</t>
-  </si>
-  <si>
-    <t>一定几率提升暴击率</t>
-  </si>
-  <si>
-    <t>一定几率提升防御力</t>
-  </si>
-  <si>
-    <t>一定几率在回合结束后自动回复部分HP</t>
-  </si>
-  <si>
-    <t>一定几率额外恢复部分能量</t>
-  </si>
-  <si>
-    <t>在死亡后有一定几率自动复活</t>
-  </si>
-  <si>
-    <t>对单个敌人造成普通伤害</t>
-  </si>
-  <si>
-    <t>对敌单体攻击，并恢复一定血量</t>
-  </si>
-  <si>
-    <t>对死亡的同伴进行急救，一定概率使其复活，并恢复一半HP</t>
-  </si>
-  <si>
-    <t>本回合代替指定的一名同伴承受所有攻击</t>
-  </si>
-  <si>
-    <t>吹口哨吸引一个敌人攻击自己</t>
-  </si>
-  <si>
-    <t>使下回合攻击力提升</t>
-  </si>
-  <si>
-    <t>攻击一个敌人并对其他敌人造成溅射伤害。</t>
-  </si>
-  <si>
-    <t>一定几率使一名敌人进入沉睡</t>
-  </si>
-  <si>
-    <t>一定几率封印一名敌人的能量增长</t>
-  </si>
-  <si>
-    <t>使一名同伴的攻击必然会心</t>
-  </si>
-  <si>
-    <t>解除一名敌人身上所有有益状态</t>
-  </si>
-  <si>
-    <t>使用奥术能量随机对敌人攻击4次</t>
-  </si>
-  <si>
-    <t>对全体敌人造成冰属性伤害，并有一定几率使其冰冻</t>
-  </si>
-  <si>
-    <t>对全体敌人造成光属性伤害，并有一定几率使其眩晕</t>
-  </si>
-  <si>
-    <t>对全体敌人造成风属性伤害，并有一定几率使其致盲</t>
-  </si>
-  <si>
-    <t>对全体敌人造成火属性伤害，并有一定几率使其燃烧</t>
-  </si>
-  <si>
-    <t>对全体敌人造成暗属性伤害，并有一定几率使其虚弱</t>
-  </si>
-  <si>
-    <t>一定几率使单个敌人混乱</t>
-  </si>
-  <si>
-    <t>大幅增加攻击伤害2回合</t>
-  </si>
-  <si>
-    <t>减弱敌人对元素伤害的抵抗力</t>
-  </si>
-  <si>
-    <t>快速回复能量</t>
-  </si>
-  <si>
-    <t>回复一名队友的HP</t>
-  </si>
-  <si>
-    <t>使一名队友的HP全满</t>
-  </si>
-  <si>
-    <t>复活一名队友，并使其HP回复一半</t>
-  </si>
-  <si>
-    <t>使沉睡的队友苏醒</t>
-  </si>
-  <si>
-    <t>将自己的一半能量传输给同伴</t>
-  </si>
-  <si>
-    <t>回复全体同伴的HP</t>
-  </si>
-  <si>
-    <t>驱逐单个同伴身上的有害状态</t>
-  </si>
-  <si>
-    <t>复活所有死亡的队友，并使其HP回复一半</t>
-  </si>
-  <si>
-    <t>以牺牲自己为代价对单个敌人造成巨大伤害</t>
-  </si>
-  <si>
-    <t>驱逐将全体同伴的有害状态，并唤醒睡眠的同伴</t>
-  </si>
-  <si>
-    <t>对群体伤害</t>
-  </si>
-  <si>
-    <t>对群体造成火属性伤害</t>
-  </si>
-  <si>
-    <t>对全体敌人造成伤害</t>
-  </si>
-  <si>
-    <t>使敌人眩晕2个回合</t>
-  </si>
-  <si>
-    <t>对单个敌人造成风属性伤害</t>
-  </si>
-  <si>
-    <t>对单个敌人造成火属性伤害</t>
-  </si>
-  <si>
-    <t>对全体敌人造成火属性伤害</t>
-  </si>
-  <si>
-    <t>对单个敌人造成普通伤害，并有一定几率使其流血</t>
-  </si>
-  <si>
-    <t>对全体敌人造成伤害，并有一定几率是其眩晕</t>
-  </si>
-  <si>
-    <t>生成黑云遮蔽一个敌人的视线</t>
-  </si>
-  <si>
-    <t>对全体敌人造成普通伤害</t>
-  </si>
-  <si>
-    <t>，一定概率使其复活，并恢复一半HP</t>
-  </si>
-  <si>
-    <t>降低防御</t>
-  </si>
-  <si>
-    <t>疗毒</t>
-  </si>
-  <si>
-    <t>使眩晕的队友苏醒</t>
-  </si>
-  <si>
-    <t>我方单体解除混乱</t>
-  </si>
-  <si>
-    <t>回能</t>
-  </si>
-  <si>
-    <t>使睡眠的队友苏醒</t>
-  </si>
-  <si>
-    <t>增加速度</t>
-  </si>
-  <si>
-    <t>为一名同伴的攻击附加火属性</t>
-  </si>
-  <si>
-    <t>为一名同伴的攻击附加冰属性</t>
-  </si>
-  <si>
-    <t>为一名同伴的攻击附加光属性</t>
-  </si>
-  <si>
-    <t>为一名同伴的攻击附加暗属性</t>
-  </si>
-  <si>
-    <t>为一名同伴的攻击附加风属性</t>
-  </si>
-  <si>
-    <t>减轻一名同伴所受到的火属性伤害</t>
-  </si>
-  <si>
-    <t>减轻一名同伴所受到的冰属性伤害</t>
-  </si>
-  <si>
-    <t>减轻一名同伴所受到的光属性伤害</t>
-  </si>
-  <si>
-    <t>减轻一名同伴所受到的暗属性伤害</t>
-  </si>
-  <si>
-    <t>减轻一名同伴所受到的风属性伤害</t>
-  </si>
-  <si>
-    <t>长剑</t>
-  </si>
-  <si>
-    <t>烈焰之刃</t>
-  </si>
-  <si>
-    <t>大地之剑</t>
-  </si>
-  <si>
-    <t>冰之刃</t>
-  </si>
-  <si>
-    <t>铁枪</t>
-  </si>
-  <si>
-    <t>骑士长枪</t>
-  </si>
-  <si>
-    <t>血腥之枪</t>
-  </si>
-  <si>
-    <t>三叉戟</t>
-  </si>
-  <si>
-    <t>战斧</t>
-  </si>
-  <si>
-    <t>毒蜥之牙</t>
-  </si>
-  <si>
-    <t>恶魔之斧</t>
-  </si>
-  <si>
-    <t>蛇皮鞭</t>
-  </si>
-  <si>
-    <t>藤鞭</t>
-  </si>
-  <si>
-    <t>女王鞭</t>
-  </si>
-  <si>
-    <t>蛇牙鞭</t>
-  </si>
-  <si>
-    <t>暴雪斧</t>
-  </si>
-  <si>
-    <t>秘银长剑</t>
-  </si>
-  <si>
-    <t>幻影长枪</t>
-  </si>
-  <si>
-    <t>雷神之鞭</t>
-  </si>
-  <si>
-    <t>死亡之鞭</t>
-  </si>
-  <si>
-    <t>烈焰斩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰斩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹰切爪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹰切突击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幻影突刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷暴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女王之春</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幽冥黑洞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恶魔幻影</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙卷风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骑士冲击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奇迹斩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诅咒之剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诅咒猎杀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒爆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺颈鞭挞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>attackType</t>
   </si>
 </sst>
 </file>
@@ -1919,7 +1922,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1951,6 +1954,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5261,10 +5267,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O84"/>
+  <dimension ref="A2:P84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5296,13 +5302,13 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
         <v>2</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>3</v>
-      </c>
-      <c r="M2" t="s">
-        <v>0</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
@@ -5310,8 +5316,11 @@
       <c r="O2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -5343,22 +5352,25 @@
         <v>12</v>
       </c>
       <c r="K3" t="s">
+        <v>571</v>
+      </c>
+      <c r="L3" t="s">
         <v>13</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>14</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>15</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>16</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4001</v>
       </c>
@@ -5390,22 +5402,25 @@
         <v>18</v>
       </c>
       <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>0.4</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1002</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>4001</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4100</v>
       </c>
@@ -5437,22 +5452,25 @@
         <v>20</v>
       </c>
       <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>0.5</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1002</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>4100</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4101</v>
       </c>
@@ -5484,22 +5502,25 @@
         <v>21</v>
       </c>
       <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>0.6</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1002</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>4101</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>4</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4102</v>
       </c>
@@ -5531,22 +5552,25 @@
         <v>22</v>
       </c>
       <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>0.7</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1002</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>4102</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4103</v>
       </c>
@@ -5578,22 +5602,25 @@
         <v>23</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>0.7</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1002</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>4103</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4104</v>
       </c>
@@ -5625,22 +5652,25 @@
         <v>24</v>
       </c>
       <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>0.6</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>1002</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>4104</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>8</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>4105</v>
       </c>
@@ -5672,22 +5702,25 @@
         <v>25</v>
       </c>
       <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>0.7</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>1002</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>4105</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4106</v>
       </c>
@@ -5719,22 +5752,25 @@
         <v>26</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>0.6</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1002</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>4106</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>20</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>4107</v>
       </c>
@@ -5766,22 +5802,25 @@
         <v>27</v>
       </c>
       <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>0.7</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>1002</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>4107</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>20</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>4108</v>
       </c>
@@ -5813,22 +5852,25 @@
         <v>28</v>
       </c>
       <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>0.5</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1002</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>4108</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>116</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>4109</v>
       </c>
@@ -5860,22 +5902,25 @@
         <v>29</v>
       </c>
       <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>0.7</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1002</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>4109</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>116</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4110</v>
       </c>
@@ -5907,22 +5952,25 @@
         <v>30</v>
       </c>
       <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>0.5</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1002</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>4110</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>40</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4111</v>
       </c>
@@ -5954,22 +6002,25 @@
         <v>31</v>
       </c>
       <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <v>0.7</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1002</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>4111</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>40</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4112</v>
       </c>
@@ -6001,22 +6052,25 @@
         <v>32</v>
       </c>
       <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>0.8</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>1002</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>4112</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>52</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>4113</v>
       </c>
@@ -6048,22 +6102,25 @@
         <v>33</v>
       </c>
       <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>0.4</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>1002</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>4113</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>52</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4114</v>
       </c>
@@ -6095,22 +6152,25 @@
         <v>34</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>0.6</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>1002</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>4114</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>64</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4115</v>
       </c>
@@ -6142,22 +6202,25 @@
         <v>35</v>
       </c>
       <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>0.5</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>1002</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>4115</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>64</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4116</v>
       </c>
@@ -6189,22 +6252,25 @@
         <v>36</v>
       </c>
       <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>0.5</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>1002</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>4116</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>74</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4117</v>
       </c>
@@ -6236,22 +6302,25 @@
         <v>37</v>
       </c>
       <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>0.8</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>1002</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>4117</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>74</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4118</v>
       </c>
@@ -6283,22 +6352,25 @@
         <v>38</v>
       </c>
       <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
         <v>0.5</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>1002</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>4118</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>1066</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4119</v>
       </c>
@@ -6330,22 +6402,25 @@
         <v>39</v>
       </c>
       <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>0.6</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>1002</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>4119</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>1066</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4120</v>
       </c>
@@ -6377,22 +6452,25 @@
         <v>40</v>
       </c>
       <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>0.5</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>1002</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>4120</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>26</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4121</v>
       </c>
@@ -6424,22 +6502,25 @@
         <v>41</v>
       </c>
       <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>1</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>1002</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>4121</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>26</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4122</v>
       </c>
@@ -6471,22 +6552,25 @@
         <v>42</v>
       </c>
       <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>0.7</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>1002</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>4122</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>28</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4123</v>
       </c>
@@ -6518,22 +6602,25 @@
         <v>43</v>
       </c>
       <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>0.6</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>1002</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>4123</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>28</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4124</v>
       </c>
@@ -6565,22 +6652,25 @@
         <v>44</v>
       </c>
       <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>0.7</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>1002</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>4124</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>32</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4125</v>
       </c>
@@ -6612,22 +6702,25 @@
         <v>45</v>
       </c>
       <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>0.7</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>1002</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>4125</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>32</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4126</v>
       </c>
@@ -6659,22 +6752,25 @@
         <v>46</v>
       </c>
       <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>0.5</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>1002</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>4126</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>38</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>4127</v>
       </c>
@@ -6706,22 +6802,25 @@
         <v>47</v>
       </c>
       <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>0.7</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>1002</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>4127</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>38</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>4128</v>
       </c>
@@ -6753,22 +6852,25 @@
         <v>48</v>
       </c>
       <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
         <v>0.6</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>1002</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>4128</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>533</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4129</v>
       </c>
@@ -6800,22 +6902,25 @@
         <v>49</v>
       </c>
       <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
         <v>0.7</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>1002</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>4129</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>533</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4130</v>
       </c>
@@ -6847,22 +6952,25 @@
         <v>50</v>
       </c>
       <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>0.5</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>1002</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>4130</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>80</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4131</v>
       </c>
@@ -6894,22 +7002,25 @@
         <v>51</v>
       </c>
       <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
         <v>0.5</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>1002</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>4131</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>80</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4132</v>
       </c>
@@ -6941,22 +7052,25 @@
         <v>52</v>
       </c>
       <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
         <v>0.9</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>1002</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>4132</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>84</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>4133</v>
       </c>
@@ -6988,22 +7102,25 @@
         <v>53</v>
       </c>
       <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
         <v>0.6</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>1002</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>4133</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>84</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4134</v>
       </c>
@@ -7035,22 +7152,25 @@
         <v>54</v>
       </c>
       <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
         <v>0.6</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>1002</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>4134</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>90</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>4135</v>
       </c>
@@ -7082,22 +7202,25 @@
         <v>55</v>
       </c>
       <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
         <v>0.5</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>1002</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>4135</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>90</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>4136</v>
       </c>
@@ -7129,22 +7252,25 @@
         <v>56</v>
       </c>
       <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
         <v>0.6</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>1002</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>4136</v>
       </c>
-      <c r="N41">
-        <v>100</v>
-      </c>
       <c r="O41">
+        <v>100</v>
+      </c>
+      <c r="P41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>4137</v>
       </c>
@@ -7176,22 +7302,25 @@
         <v>57</v>
       </c>
       <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
         <v>0.6</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>1002</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>4137</v>
       </c>
-      <c r="N42">
-        <v>100</v>
-      </c>
       <c r="O42">
+        <v>100</v>
+      </c>
+      <c r="P42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>4138</v>
       </c>
@@ -7223,22 +7352,25 @@
         <v>58</v>
       </c>
       <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>0.6</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>1002</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>4138</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>1530</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>4139</v>
       </c>
@@ -7270,22 +7402,25 @@
         <v>59</v>
       </c>
       <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
         <v>0.5</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>1002</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>4139</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>1530</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>4140</v>
       </c>
@@ -7317,22 +7452,25 @@
         <v>60</v>
       </c>
       <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
         <v>0.5</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>1002</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>4140</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>132</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4141</v>
       </c>
@@ -7364,22 +7502,25 @@
         <v>61</v>
       </c>
       <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
         <v>0.8</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>1002</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>4141</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>132</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4142</v>
       </c>
@@ -7411,22 +7552,25 @@
         <v>62</v>
       </c>
       <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
         <v>1</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>1002</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>4142</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>144</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4143</v>
       </c>
@@ -7458,22 +7602,25 @@
         <v>63</v>
       </c>
       <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>0.8</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>1002</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>4143</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>144</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4144</v>
       </c>
@@ -7505,22 +7652,25 @@
         <v>64</v>
       </c>
       <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
         <v>0.5</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>1002</v>
       </c>
-      <c r="M49">
+      <c r="N49">
         <v>4144</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>168</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4145</v>
       </c>
@@ -7552,22 +7702,25 @@
         <v>65</v>
       </c>
       <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
         <v>0.5</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>1002</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>4145</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>168</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4146</v>
       </c>
@@ -7599,22 +7752,25 @@
         <v>66</v>
       </c>
       <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
         <v>1</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>1002</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>4146</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>192</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4147</v>
       </c>
@@ -7646,22 +7802,25 @@
         <v>67</v>
       </c>
       <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
         <v>1</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>1002</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>4147</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>192</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>4148</v>
       </c>
@@ -7693,22 +7852,25 @@
         <v>68</v>
       </c>
       <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
         <v>0.7</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>1002</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>4148</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>1936</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>4149</v>
       </c>
@@ -7740,22 +7902,25 @@
         <v>69</v>
       </c>
       <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
         <v>0.6</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>1002</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>4149</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>1936</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4150</v>
       </c>
@@ -7787,22 +7952,25 @@
         <v>70</v>
       </c>
       <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>0.5</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>1002</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>4150</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>266</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4151</v>
       </c>
@@ -7834,22 +8002,25 @@
         <v>71</v>
       </c>
       <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
         <v>0.6</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>1002</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>4151</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>266</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4152</v>
       </c>
@@ -7881,22 +8052,25 @@
         <v>72</v>
       </c>
       <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
         <v>0.8</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>1002</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>4152</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>282</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4153</v>
       </c>
@@ -7928,22 +8102,25 @@
         <v>73</v>
       </c>
       <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
         <v>1</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>1002</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>4153</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>282</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4154</v>
       </c>
@@ -7975,22 +8152,25 @@
         <v>74</v>
       </c>
       <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
         <v>0.5</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>1002</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>4154</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>300</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4155</v>
       </c>
@@ -8022,22 +8202,25 @@
         <v>75</v>
       </c>
       <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
         <v>1</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>1002</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>4155</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>300</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4156</v>
       </c>
@@ -8069,22 +8252,25 @@
         <v>76</v>
       </c>
       <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
         <v>0.6</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>1002</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>4156</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>354</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4157</v>
       </c>
@@ -8116,22 +8302,25 @@
         <v>77</v>
       </c>
       <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
         <v>0.9</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>1002</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>4157</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>354</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4158</v>
       </c>
@@ -8163,22 +8352,25 @@
         <v>78</v>
       </c>
       <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
         <v>0.6</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>1002</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>4158</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>4133</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4159</v>
       </c>
@@ -8210,22 +8402,25 @@
         <v>79</v>
       </c>
       <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
         <v>0.7</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>1002</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>4159</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>4133</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4160</v>
       </c>
@@ -8257,22 +8452,25 @@
         <v>80</v>
       </c>
       <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
         <v>0.5</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>1002</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>4160</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>192</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4161</v>
       </c>
@@ -8304,22 +8502,25 @@
         <v>81</v>
       </c>
       <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
         <v>0.5</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>1002</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>4161</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>192</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4162</v>
       </c>
@@ -8351,22 +8552,25 @@
         <v>82</v>
       </c>
       <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
         <v>0.7</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>1002</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>4162</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>204</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4163</v>
       </c>
@@ -8398,22 +8602,25 @@
         <v>83</v>
       </c>
       <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
         <v>0.7</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>1002</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>4163</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>204</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4164</v>
       </c>
@@ -8445,22 +8652,25 @@
         <v>84</v>
       </c>
       <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
         <v>0.9</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>1002</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>4164</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>216</v>
       </c>
-      <c r="O69">
+      <c r="P69">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4165</v>
       </c>
@@ -8492,22 +8702,25 @@
         <v>85</v>
       </c>
       <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
         <v>1</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>1002</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>4165</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>216</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4166</v>
       </c>
@@ -8539,22 +8752,25 @@
         <v>86</v>
       </c>
       <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
         <v>0.7</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>1002</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>4166</v>
       </c>
-      <c r="N71">
+      <c r="O71">
         <v>288</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4167</v>
       </c>
@@ -8586,22 +8802,25 @@
         <v>87</v>
       </c>
       <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
         <v>0.8</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>1002</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>4167</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>288</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4168</v>
       </c>
@@ -8633,22 +8852,25 @@
         <v>88</v>
       </c>
       <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
         <v>0.7</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>1002</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>4168</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>2756</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4169</v>
       </c>
@@ -8680,22 +8902,25 @@
         <v>89</v>
       </c>
       <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
         <v>0.6</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>1002</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>4169</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>2756</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4170</v>
       </c>
@@ -8727,22 +8952,25 @@
         <v>90</v>
       </c>
       <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
         <v>0.5</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>1002</v>
       </c>
-      <c r="M75">
+      <c r="N75">
         <v>4170</v>
       </c>
-      <c r="N75">
+      <c r="O75">
         <v>394</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4171</v>
       </c>
@@ -8774,22 +9002,25 @@
         <v>91</v>
       </c>
       <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
         <v>0.5</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>1002</v>
       </c>
-      <c r="M76">
+      <c r="N76">
         <v>4171</v>
       </c>
-      <c r="N76">
+      <c r="O76">
         <v>394</v>
       </c>
-      <c r="O76">
+      <c r="P76">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4172</v>
       </c>
@@ -8821,22 +9052,25 @@
         <v>92</v>
       </c>
       <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
         <v>0.5</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>1002</v>
       </c>
-      <c r="M77">
+      <c r="N77">
         <v>4172</v>
       </c>
-      <c r="N77">
+      <c r="O77">
         <v>400</v>
       </c>
-      <c r="O77">
+      <c r="P77">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4173</v>
       </c>
@@ -8868,22 +9102,25 @@
         <v>93</v>
       </c>
       <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
         <v>0.7</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>1002</v>
       </c>
-      <c r="M78">
+      <c r="N78">
         <v>4173</v>
       </c>
-      <c r="N78">
+      <c r="O78">
         <v>400</v>
       </c>
-      <c r="O78">
+      <c r="P78">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4174</v>
       </c>
@@ -8915,22 +9152,25 @@
         <v>94</v>
       </c>
       <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
         <v>0.5</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>1002</v>
       </c>
-      <c r="M79">
+      <c r="N79">
         <v>4174</v>
       </c>
-      <c r="N79">
+      <c r="O79">
         <v>412</v>
       </c>
-      <c r="O79">
+      <c r="P79">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4175</v>
       </c>
@@ -8962,22 +9202,25 @@
         <v>95</v>
       </c>
       <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
         <v>1</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>1002</v>
       </c>
-      <c r="M80">
+      <c r="N80">
         <v>4175</v>
       </c>
-      <c r="N80">
+      <c r="O80">
         <v>412</v>
       </c>
-      <c r="O80">
+      <c r="P80">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4176</v>
       </c>
@@ -9009,22 +9252,25 @@
         <v>96</v>
       </c>
       <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
         <v>0.7</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>1002</v>
       </c>
-      <c r="M81">
+      <c r="N81">
         <v>4176</v>
       </c>
-      <c r="N81">
+      <c r="O81">
         <v>480</v>
       </c>
-      <c r="O81">
+      <c r="P81">
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4177</v>
       </c>
@@ -9056,22 +9302,25 @@
         <v>97</v>
       </c>
       <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
         <v>0.8</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>1002</v>
       </c>
-      <c r="M82">
+      <c r="N82">
         <v>4177</v>
       </c>
-      <c r="N82">
+      <c r="O82">
         <v>480</v>
       </c>
-      <c r="O82">
+      <c r="P82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4178</v>
       </c>
@@ -9103,22 +9352,25 @@
         <v>98</v>
       </c>
       <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
         <v>0.6</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>1002</v>
       </c>
-      <c r="M83">
+      <c r="N83">
         <v>4178</v>
       </c>
-      <c r="N83">
+      <c r="O83">
         <v>5466</v>
       </c>
-      <c r="O83">
+      <c r="P83">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4179</v>
       </c>
@@ -9150,18 +9402,21 @@
         <v>99</v>
       </c>
       <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
         <v>0.7</v>
       </c>
-      <c r="L84">
+      <c r="M84">
         <v>1002</v>
       </c>
-      <c r="M84">
+      <c r="N84">
         <v>4179</v>
       </c>
-      <c r="N84">
+      <c r="O84">
         <v>5466</v>
       </c>
-      <c r="O84">
+      <c r="P84">
         <v>2</v>
       </c>
     </row>
@@ -10380,7 +10635,7 @@
         <v>216</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U13">
         <f>IF(D13&lt;&gt;"",VLOOKUP(D13,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -10417,8 +10672,8 @@
       <c r="J14" t="s">
         <v>217</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>259</v>
+      <c r="L14" s="3" t="s">
+        <v>570</v>
       </c>
       <c r="U14">
         <f>IF(D14&lt;&gt;"",VLOOKUP(D14,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -10436,7 +10691,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4110</v>
       </c>
@@ -10474,7 +10729,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4111</v>
       </c>
@@ -10503,7 +10758,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4112</v>
       </c>
@@ -10529,7 +10784,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>4113</v>
       </c>
@@ -10555,7 +10810,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4114</v>
       </c>
@@ -10581,7 +10836,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4115</v>
       </c>
@@ -10610,7 +10865,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4116</v>
       </c>
@@ -10639,7 +10894,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4117</v>
       </c>
@@ -10694,7 +10949,7 @@
         <v>143</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U23">
         <f>IF(D23&lt;&gt;"",VLOOKUP(D23,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -10738,7 +10993,7 @@
         <v>221</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="U24">
         <f>IF(D24&lt;&gt;"",VLOOKUP(D24,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -10756,7 +11011,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4120</v>
       </c>
@@ -10782,7 +11037,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4121</v>
       </c>
@@ -10811,7 +11066,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>4122</v>
       </c>
@@ -10840,7 +11095,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>4123</v>
       </c>
@@ -10866,7 +11121,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>4124</v>
       </c>
@@ -10895,7 +11150,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4125</v>
       </c>
@@ -10924,7 +11179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4126</v>
       </c>
@@ -10953,7 +11208,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>4127</v>
       </c>
@@ -11008,7 +11263,7 @@
         <v>156</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U33">
         <f>IF(D33&lt;&gt;"",VLOOKUP(D33,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11055,7 +11310,7 @@
         <v>157</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U34">
         <f>IF(D34&lt;&gt;"",VLOOKUP(D34,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11076,7 +11331,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4130</v>
       </c>
@@ -11108,7 +11363,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4131</v>
       </c>
@@ -11140,7 +11395,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4132</v>
       </c>
@@ -11172,7 +11427,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>4133</v>
       </c>
@@ -11204,7 +11459,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4134</v>
       </c>
@@ -11236,7 +11491,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>4135</v>
       </c>
@@ -11265,7 +11520,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>4136</v>
       </c>
@@ -11291,7 +11546,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>4137</v>
       </c>
@@ -11343,7 +11598,7 @@
         <v>116</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U43">
         <f>IF(D43&lt;&gt;"",VLOOKUP(D43,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11384,7 +11639,7 @@
         <v>172</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="U44">
         <f>IF(D44&lt;&gt;"",VLOOKUP(D44,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11402,7 +11657,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>4140</v>
       </c>
@@ -11431,7 +11686,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4141</v>
       </c>
@@ -11460,7 +11715,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4142</v>
       </c>
@@ -11489,7 +11744,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4143</v>
       </c>
@@ -11521,7 +11776,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4144</v>
       </c>
@@ -11550,7 +11805,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4145</v>
       </c>
@@ -11579,7 +11834,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4146</v>
       </c>
@@ -11608,7 +11863,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4147</v>
       </c>
@@ -11660,7 +11915,7 @@
         <v>177</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U53">
         <f>IF(D53&lt;&gt;"",VLOOKUP(D53,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11704,7 +11959,7 @@
         <v>176</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U54">
         <f>IF(D54&lt;&gt;"",VLOOKUP(D54,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -11722,7 +11977,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4150</v>
       </c>
@@ -11751,7 +12006,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4151</v>
       </c>
@@ -11783,7 +12038,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4152</v>
       </c>
@@ -11815,7 +12070,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4153</v>
       </c>
@@ -11844,7 +12099,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4154</v>
       </c>
@@ -11873,7 +12128,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4155</v>
       </c>
@@ -11905,7 +12160,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4156</v>
       </c>
@@ -11931,7 +12186,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4157</v>
       </c>
@@ -11986,7 +12241,7 @@
         <v>198</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U63">
         <f>IF(D63&lt;&gt;"",VLOOKUP(D63,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12027,7 +12282,7 @@
         <v>126</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U64">
         <f>IF(D64&lt;&gt;"",VLOOKUP(D64,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12045,7 +12300,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4160</v>
       </c>
@@ -12074,7 +12329,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4161</v>
       </c>
@@ -12103,7 +12358,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4162</v>
       </c>
@@ -12132,7 +12387,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4163</v>
       </c>
@@ -12164,7 +12419,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4164</v>
       </c>
@@ -12193,7 +12448,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4165</v>
       </c>
@@ -12222,7 +12477,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4166</v>
       </c>
@@ -12251,7 +12506,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4167</v>
       </c>
@@ -12306,7 +12561,7 @@
         <v>142</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U73">
         <f>IF(D73&lt;&gt;"",VLOOKUP(D73,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12350,7 +12605,7 @@
         <v>135</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U74">
         <f>IF(D74&lt;&gt;"",VLOOKUP(D74,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12368,7 +12623,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4170</v>
       </c>
@@ -12394,7 +12649,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4171</v>
       </c>
@@ -12423,7 +12678,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4172</v>
       </c>
@@ -12449,7 +12704,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4173</v>
       </c>
@@ -12478,7 +12733,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4174</v>
       </c>
@@ -12507,7 +12762,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4175</v>
       </c>
@@ -12536,7 +12791,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4176</v>
       </c>
@@ -12565,7 +12820,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4177</v>
       </c>
@@ -12617,7 +12872,7 @@
         <v>208</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U83">
         <f>IF(D83&lt;&gt;"",VLOOKUP(D83,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12661,7 +12916,7 @@
         <v>200</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U84">
         <f>IF(D84&lt;&gt;"",VLOOKUP(D84,[1]ItemData!$A:$B,2,FALSE),"")</f>
@@ -12743,938 +12998,938 @@
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I3" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I4" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I5" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I6" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="J7" s="9"/>
       <c r="N7" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>568</v>
+        <v>557</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>560</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>553</v>
+        <v>532</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>551</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>555</v>
+        <v>533</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>559</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>554</v>
+        <v>534</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>561</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>566</v>
+        <v>547</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>556</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>565</v>
+        <v>536</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>555</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>557</v>
+        <v>537</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>562</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="N15" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>564</v>
+        <v>538</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>563</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>558</v>
+        <v>548</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>553</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>569</v>
+        <v>540</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>558</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>563</v>
+        <v>541</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>564</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>562</v>
+        <v>546</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>565</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="10" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>560</v>
+        <v>544</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>567</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>570</v>
+        <v>545</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>569</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>559</v>
+        <v>549</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>568</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>360</v>
+        <v>550</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>566</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I28" s="8" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="I29" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N30" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N31" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N32" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N33" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N34" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N35" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N36" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N37" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N38" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O38" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N39" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N40" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O40" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N41" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N42" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N43" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N44" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N45" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N46" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O46" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N47" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N48" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N49" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N50" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N51" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N52" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O52" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N53" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="54" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N54" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O54" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="55" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N55" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N56" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O56" s="8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="57" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N57" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O57" s="8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N58" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O58" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N59" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N60" s="8" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="O60" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="61" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N61" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O61" s="8" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N62" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O62" s="8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="63" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N63" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O63" s="8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N64" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O64" s="8" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="65" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N65" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O65" s="8" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="66" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N66" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O66" s="8" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="67" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N67" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O67" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="68" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N68" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O68" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N69" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O69" s="8" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N70" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O70" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="71" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N71" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O71" s="8" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N72" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N73" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O73" s="8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N74" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O74" s="8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N75" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O75" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="76" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N76" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O76" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="77" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N77" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O77" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N78" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="79" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N79" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="O79" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N80" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N81" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="82" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N82" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N83" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="84" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N84" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="O84" s="8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="85" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N85" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O85" s="8" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="86" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N86" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O86" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="87" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N87" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="88" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N88" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="89" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N89" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O89" s="8" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="90" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N90" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="O90" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="91" spans="14:15" x14ac:dyDescent="0.2">
@@ -13682,631 +13937,631 @@
         <v>199</v>
       </c>
       <c r="O91" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="92" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N92" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N93" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="O93" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="94" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N94" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="O94" s="8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="95" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N95" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="O95" s="8" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="96" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N96" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O96" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="97" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N97" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O97" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N98" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O98" s="8" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="99" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N99" s="8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O99" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="100" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N100" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O100" s="8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="101" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N101" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O101" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="102" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N102" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="O102" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="103" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N103" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N104" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O104" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="105" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N105" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="O105" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N106" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="O106" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="107" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N107" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O107" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N108" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="O108" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="109" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N109" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="O109" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="110" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N110" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="111" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N111" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="112" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N112" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="113" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N113" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="114" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N114" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="O114" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="115" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N115" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O115" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="116" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N116" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="117" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N117" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="O117" s="8" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="118" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N118" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O118" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="119" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N119" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O119" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="120" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N120" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="O120" s="8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="121" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N121" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="O121" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="122" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N122" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O122" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N123" s="8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O123" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="124" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N124" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O124" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="125" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N125" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O125" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N126" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="O126" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="127" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N127" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="O127" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N128" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="O128" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="129" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N129" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O129" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="130" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N130" s="8" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="O130" s="8" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="131" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N131" s="8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="O131" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="132" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N132" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="O132" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="133" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N133" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="O133" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="134" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N134" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="O134" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="135" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N135" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="O135" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="136" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N136" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="O136" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="137" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N137" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="O137" s="8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="138" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N138" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="O138" s="8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N139" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="O139" s="8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="140" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N140" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O140" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="141" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N141" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="O141" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="142" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N142" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O142" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="143" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N143" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="O143" s="8" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="144" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N144" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="O144" s="8" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="145" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N145" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="O145" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="146" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N146" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="O146" s="8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="147" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N147" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O147" s="8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="148" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N148" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="O148" s="8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="149" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N149" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="O149" s="8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="150" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N150" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="O150" s="8" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="151" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N151" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O151" s="8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N152" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O152" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N153" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O153" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N154" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="O154" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="155" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N155" s="8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="O155" s="8" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="156" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N156" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="O156" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="157" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N157" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="O157" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="158" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N158" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O158" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="159" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N159" s="8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O159" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="160" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N160" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="O160" s="8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="161" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N161" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="O161" s="8" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="162" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N162" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="O162" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="163" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N163" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="O163" s="8" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="164" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N164" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="O164" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N165" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="O165" s="8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="166" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N166" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="O166" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="167" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N167" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O167" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="168" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N168" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="O168" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="169" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N169" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="O169" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -32,6 +32,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>flyer</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 默认0   刀剑攻击1 长矛攻击2 斧子攻击3 咬4 爪5 鞭6
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="572">
   <si>
@@ -1837,13 +1872,14 @@
   </si>
   <si>
     <t>attackType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1874,6 +1910,19 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -5266,7 +5315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:P84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -5552,7 +5601,7 @@
         <v>22</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>0.7</v>
@@ -5702,7 +5751,7 @@
         <v>25</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0.7</v>
@@ -5802,7 +5851,7 @@
         <v>27</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>0.7</v>
@@ -6002,7 +6051,7 @@
         <v>31</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <v>0.7</v>
@@ -6052,7 +6101,7 @@
         <v>32</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <v>0.8</v>
@@ -6102,7 +6151,7 @@
         <v>33</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0.4</v>
@@ -6152,7 +6201,7 @@
         <v>34</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>0.6</v>
@@ -6352,7 +6401,7 @@
         <v>38</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>0.5</v>
@@ -6602,7 +6651,7 @@
         <v>43</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>0.6</v>
@@ -6652,7 +6701,7 @@
         <v>44</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>0.7</v>
@@ -6752,7 +6801,7 @@
         <v>46</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
         <v>0.5</v>
@@ -6802,7 +6851,7 @@
         <v>47</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32">
         <v>0.7</v>
@@ -6852,7 +6901,7 @@
         <v>48</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <v>0.6</v>
@@ -6902,7 +6951,7 @@
         <v>49</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>0.7</v>
@@ -7002,7 +7051,7 @@
         <v>51</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>0.5</v>
@@ -7102,7 +7151,7 @@
         <v>53</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
         <v>0.6</v>
@@ -7152,7 +7201,7 @@
         <v>54</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>0.6</v>
@@ -7252,7 +7301,7 @@
         <v>56</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41">
         <v>0.6</v>
@@ -7352,7 +7401,7 @@
         <v>58</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L43">
         <v>0.6</v>
@@ -7502,7 +7551,7 @@
         <v>61</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46">
         <v>0.8</v>
@@ -7552,7 +7601,7 @@
         <v>62</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47">
         <v>1</v>
@@ -7652,7 +7701,7 @@
         <v>64</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L49">
         <v>0.5</v>
@@ -7702,7 +7751,7 @@
         <v>65</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50">
         <v>0.5</v>
@@ -7752,7 +7801,7 @@
         <v>66</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -7852,7 +7901,7 @@
         <v>68</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
         <v>0.7</v>
@@ -7902,7 +7951,7 @@
         <v>69</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54">
         <v>0.6</v>
@@ -7952,7 +8001,7 @@
         <v>70</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55">
         <v>0.5</v>
@@ -8002,7 +8051,7 @@
         <v>71</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>0.6</v>
@@ -8152,7 +8201,7 @@
         <v>74</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59">
         <v>0.5</v>
@@ -8252,7 +8301,7 @@
         <v>76</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61">
         <v>0.6</v>
@@ -8302,7 +8351,7 @@
         <v>77</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
         <v>0.9</v>
@@ -8352,7 +8401,7 @@
         <v>78</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>0.6</v>
@@ -8402,7 +8451,7 @@
         <v>79</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64">
         <v>0.7</v>
@@ -8502,7 +8551,7 @@
         <v>81</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L66">
         <v>0.5</v>
@@ -8552,7 +8601,7 @@
         <v>82</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L67">
         <v>0.7</v>
@@ -8652,7 +8701,7 @@
         <v>84</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69">
         <v>0.9</v>
@@ -8852,7 +8901,7 @@
         <v>88</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73">
         <v>0.7</v>
@@ -8902,7 +8951,7 @@
         <v>89</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L74">
         <v>0.6</v>
@@ -9002,7 +9051,7 @@
         <v>91</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L76">
         <v>0.5</v>
@@ -9152,7 +9201,7 @@
         <v>94</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79">
         <v>0.5</v>
@@ -9202,7 +9251,7 @@
         <v>95</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -9352,7 +9401,7 @@
         <v>98</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83">
         <v>0.6</v>
@@ -9402,7 +9451,7 @@
         <v>99</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84">
         <v>0.7</v>
@@ -9424,6 +9473,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -5439,7 +5439,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -5589,7 +5589,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5789,7 +5789,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -5839,7 +5839,7 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -5939,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -5989,7 +5989,7 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -6039,7 +6039,7 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6089,7 +6089,7 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -6189,7 +6189,7 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -6239,7 +6239,7 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H22">
         <v>3</v>
@@ -6389,7 +6389,7 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H23">
         <v>3</v>
@@ -6439,7 +6439,7 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -6489,7 +6489,7 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -6539,7 +6539,7 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -6589,7 +6589,7 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H28">
         <v>4</v>
@@ -6689,7 +6689,7 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -6739,7 +6739,7 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -6789,7 +6789,7 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -6889,7 +6889,7 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H34">
         <v>4</v>
@@ -6989,7 +6989,7 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -7039,7 +7039,7 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -7139,7 +7139,7 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>100</v>
       </c>
       <c r="G39">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -7239,7 +7239,7 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -7289,7 +7289,7 @@
         <v>100</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -7389,7 +7389,7 @@
         <v>100</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>100</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -7489,7 +7489,7 @@
         <v>100</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -7589,7 +7589,7 @@
         <v>100</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -7639,7 +7639,7 @@
         <v>100</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H48">
         <v>2</v>
@@ -7689,7 +7689,7 @@
         <v>100</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -7739,7 +7739,7 @@
         <v>100</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>100</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -7839,7 +7839,7 @@
         <v>100</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -7889,7 +7889,7 @@
         <v>100</v>
       </c>
       <c r="G53">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -7939,7 +7939,7 @@
         <v>100</v>
       </c>
       <c r="G54">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>100</v>
       </c>
       <c r="G55">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -8039,7 +8039,7 @@
         <v>100</v>
       </c>
       <c r="G56">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H56">
         <v>2</v>
@@ -8089,7 +8089,7 @@
         <v>100</v>
       </c>
       <c r="G57">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -8139,7 +8139,7 @@
         <v>100</v>
       </c>
       <c r="G58">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -8189,7 +8189,7 @@
         <v>100</v>
       </c>
       <c r="G59">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -8239,7 +8239,7 @@
         <v>100</v>
       </c>
       <c r="G60">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -8289,7 +8289,7 @@
         <v>100</v>
       </c>
       <c r="G61">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -8339,7 +8339,7 @@
         <v>100</v>
       </c>
       <c r="G62">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -8389,7 +8389,7 @@
         <v>100</v>
       </c>
       <c r="G63">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -8439,7 +8439,7 @@
         <v>100</v>
       </c>
       <c r="G64">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H64">
         <v>2</v>
@@ -8489,7 +8489,7 @@
         <v>100</v>
       </c>
       <c r="G65">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -8539,7 +8539,7 @@
         <v>100</v>
       </c>
       <c r="G66">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -8589,7 +8589,7 @@
         <v>100</v>
       </c>
       <c r="G67">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>100</v>
       </c>
       <c r="G68">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -8689,7 +8689,7 @@
         <v>100</v>
       </c>
       <c r="G69">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -8739,7 +8739,7 @@
         <v>100</v>
       </c>
       <c r="G70">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -8789,7 +8789,7 @@
         <v>100</v>
       </c>
       <c r="G71">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H71">
         <v>3</v>
@@ -8839,7 +8839,7 @@
         <v>100</v>
       </c>
       <c r="G72">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>100</v>
       </c>
       <c r="G73">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H73">
         <v>3</v>
@@ -8939,7 +8939,7 @@
         <v>100</v>
       </c>
       <c r="G74">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -8989,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="G75">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -9089,7 +9089,7 @@
         <v>100</v>
       </c>
       <c r="G77">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H77">
         <v>3</v>
@@ -9139,7 +9139,7 @@
         <v>100</v>
       </c>
       <c r="G78">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -9189,7 +9189,7 @@
         <v>100</v>
       </c>
       <c r="G79">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H79">
         <v>4</v>
@@ -9239,7 +9239,7 @@
         <v>100</v>
       </c>
       <c r="G80">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>100</v>
       </c>
       <c r="G81">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H81">
         <v>4</v>
@@ -9339,7 +9339,7 @@
         <v>100</v>
       </c>
       <c r="G82">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -9389,7 +9389,7 @@
         <v>100</v>
       </c>
       <c r="G83">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H83">
         <v>4</v>
@@ -9439,7 +9439,7 @@
         <v>100</v>
       </c>
       <c r="G84">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -9472,7 +9472,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -2031,7 +2031,6 @@
     <sheetNames>
       <sheetName val="ItemData"/>
       <sheetName val="Sheet2"/>
-      <sheetName val="Sheet1"/>
       <sheetName val="Sheet3"/>
     </sheetNames>
     <sheetDataSet>
@@ -5045,9 +5044,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13022,7 +13020,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -46,6 +46,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> 默认0   刀剑攻击1 长矛攻击2 斧子攻击3 咬4 爪5 鞭6
@@ -56,6 +57,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -1915,6 +1917,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1922,6 +1925,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2030,8 +2034,18 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ItemData"/>
+      <sheetName val="Sheet13"/>
       <sheetName val="Sheet2"/>
       <sheetName val="Sheet3"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet5"/>
+      <sheetName val="植物"/>
+      <sheetName val="动物"/>
+      <sheetName val="装备"/>
+      <sheetName val="Sheet8"/>
+      <sheetName val="材料"/>
+      <sheetName val="食物"/>
+      <sheetName val="鱼"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2141,2911 +2155,3065 @@
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>牧草</v>
+            <v>食物配方</v>
           </cell>
           <cell r="B15">
-            <v>100</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>木材</v>
+            <v>酒水配方</v>
           </cell>
           <cell r="B16">
-            <v>101</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>原木</v>
+            <v>铸造配方</v>
           </cell>
           <cell r="B17">
-            <v>102</v>
+            <v>22</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>木柴</v>
+            <v>缝纫配方</v>
           </cell>
           <cell r="B18">
-            <v>103</v>
+            <v>23</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>木棒</v>
+            <v>书写配方</v>
           </cell>
           <cell r="B19">
-            <v>104</v>
+            <v>24</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>干草</v>
+            <v>牧草</v>
           </cell>
           <cell r="B20">
-            <v>105</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>纯净水</v>
+            <v>木材</v>
           </cell>
           <cell r="B21">
-            <v>200</v>
+            <v>101</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>石块</v>
+            <v>原木</v>
           </cell>
           <cell r="B22">
-            <v>201</v>
+            <v>102</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>龟壳</v>
+            <v>木柴</v>
           </cell>
           <cell r="B23">
-            <v>202</v>
+            <v>103</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>兽皮</v>
+            <v>木棒</v>
           </cell>
           <cell r="B24">
-            <v>203</v>
+            <v>104</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
-            <v>布片</v>
+            <v>干草</v>
           </cell>
           <cell r="B25">
-            <v>204</v>
+            <v>105</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>石英砂</v>
+            <v>纯净水</v>
           </cell>
           <cell r="B26">
-            <v>205</v>
+            <v>200</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>草药茶</v>
+            <v>石块</v>
           </cell>
           <cell r="B27">
-            <v>207</v>
+            <v>201</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>风晶石</v>
+            <v>龟壳</v>
           </cell>
           <cell r="B28">
-            <v>208</v>
+            <v>202</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
-            <v>琥珀</v>
+            <v>兽皮</v>
           </cell>
           <cell r="B29">
-            <v>210</v>
+            <v>203</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
-            <v>狼牙</v>
+            <v>布片</v>
           </cell>
           <cell r="B30">
-            <v>211</v>
+            <v>204</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
-            <v>粘土</v>
+            <v>石英砂</v>
           </cell>
           <cell r="B31">
-            <v>212</v>
+            <v>205</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
-            <v>尖刺</v>
+            <v>草药茶</v>
           </cell>
           <cell r="B32">
-            <v>213</v>
+            <v>207</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>蛛丝</v>
+            <v>风晶石</v>
           </cell>
           <cell r="B33">
-            <v>214</v>
+            <v>208</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
-            <v>铁矿</v>
+            <v>琥珀</v>
           </cell>
           <cell r="B34">
-            <v>215</v>
+            <v>210</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
-            <v>盐矿</v>
+            <v>狼牙</v>
           </cell>
           <cell r="B35">
-            <v>216</v>
+            <v>211</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
-            <v>肥皂</v>
+            <v>粘土</v>
           </cell>
           <cell r="B36">
-            <v>217</v>
+            <v>212</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>土晶石</v>
+            <v>尖刺</v>
           </cell>
           <cell r="B37">
-            <v>218</v>
+            <v>213</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>迷幻菇</v>
+            <v>蛛丝</v>
           </cell>
           <cell r="B38">
-            <v>219</v>
+            <v>214</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
-            <v>眼球</v>
+            <v>铁矿</v>
           </cell>
           <cell r="B39">
-            <v>220</v>
+            <v>215</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
-            <v>植物的藤</v>
+            <v>盐矿</v>
           </cell>
           <cell r="B40">
-            <v>221</v>
+            <v>216</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
-            <v>鹿角</v>
+            <v>肥皂</v>
           </cell>
           <cell r="B41">
-            <v>222</v>
+            <v>217</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
-            <v>魔兽皮毛</v>
+            <v>土晶石</v>
           </cell>
           <cell r="B42">
-            <v>223</v>
+            <v>218</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>奇美拉之翼</v>
+            <v>迷幻菇</v>
           </cell>
           <cell r="B43">
-            <v>224</v>
+            <v>219</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44" t="str">
-            <v>电偶瓶</v>
+            <v>眼球</v>
           </cell>
           <cell r="B44">
-            <v>225</v>
+            <v>220</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
-            <v>海胆</v>
+            <v>植物的藤</v>
           </cell>
           <cell r="B45">
-            <v>226</v>
+            <v>221</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
-            <v>珊瑚</v>
+            <v>鹿角</v>
           </cell>
           <cell r="B46">
-            <v>227</v>
+            <v>222</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
-            <v>彩色羽毛</v>
+            <v>魔兽皮毛</v>
           </cell>
           <cell r="B47">
-            <v>228</v>
+            <v>223</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48" t="str">
-            <v>火晶石</v>
+            <v>奇美拉之翼</v>
           </cell>
           <cell r="B48">
-            <v>229</v>
+            <v>224</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49" t="str">
-            <v>玻璃瓶</v>
+            <v>电偶瓶</v>
           </cell>
           <cell r="B49">
-            <v>230</v>
+            <v>225</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50" t="str">
-            <v>水晶石</v>
+            <v>海胆</v>
           </cell>
           <cell r="B50">
-            <v>232</v>
+            <v>226</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51" t="str">
-            <v>珍珠</v>
+            <v>珊瑚</v>
           </cell>
           <cell r="B51">
-            <v>234</v>
+            <v>227</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52" t="str">
-            <v>松果</v>
+            <v>彩色羽毛</v>
           </cell>
           <cell r="B52">
-            <v>235</v>
+            <v>228</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53" t="str">
-            <v>神奇泥浆</v>
+            <v>火晶石</v>
           </cell>
           <cell r="B53">
-            <v>236</v>
+            <v>229</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
-            <v>银块</v>
+            <v>玻璃瓶</v>
           </cell>
           <cell r="B54">
-            <v>237</v>
+            <v>230</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
-            <v>蛇皮</v>
+            <v>水晶石</v>
           </cell>
           <cell r="B55">
-            <v>238</v>
+            <v>232</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
-            <v>蜂刺</v>
+            <v>珍珠</v>
           </cell>
           <cell r="B56">
-            <v>239</v>
+            <v>234</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57" t="str">
-            <v>象牙</v>
+            <v>松果</v>
           </cell>
           <cell r="B57">
-            <v>240</v>
+            <v>235</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
-            <v>兽角</v>
+            <v>神奇泥浆</v>
           </cell>
           <cell r="B58">
-            <v>241</v>
+            <v>236</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59" t="str">
-            <v>水晶球</v>
+            <v>银块</v>
           </cell>
           <cell r="B59">
-            <v>242</v>
+            <v>237</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
-            <v>蝎尾</v>
+            <v>蛇皮</v>
           </cell>
           <cell r="B60">
-            <v>243</v>
+            <v>238</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61" t="str">
-            <v>仙人掌</v>
+            <v>蜂刺</v>
           </cell>
           <cell r="B61">
-            <v>244</v>
+            <v>239</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62" t="str">
-            <v>脏绷带</v>
+            <v>象牙</v>
           </cell>
           <cell r="B62">
-            <v>245</v>
+            <v>240</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
-            <v>幽魂</v>
+            <v>兽角</v>
           </cell>
           <cell r="B63">
-            <v>246</v>
+            <v>241</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64" t="str">
-            <v>金块</v>
+            <v>水晶球</v>
           </cell>
           <cell r="B64">
-            <v>247</v>
+            <v>242</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65" t="str">
-            <v>远古的硬币</v>
+            <v>蝎尾</v>
           </cell>
           <cell r="B65">
-            <v>248</v>
+            <v>243</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
-            <v>铁钉</v>
+            <v>仙人掌</v>
           </cell>
           <cell r="B66">
-            <v>249</v>
+            <v>244</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
-            <v>遗骨</v>
+            <v>脏绷带</v>
           </cell>
           <cell r="B67">
-            <v>250</v>
+            <v>245</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68" t="str">
-            <v>妖精粉</v>
+            <v>幽魂</v>
           </cell>
           <cell r="B68">
-            <v>251</v>
+            <v>246</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69" t="str">
-            <v>雪球</v>
+            <v>金块</v>
           </cell>
           <cell r="B69">
-            <v>253</v>
+            <v>247</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70" t="str">
-            <v>毒淤泥</v>
+            <v>远古的硬币</v>
           </cell>
           <cell r="B70">
-            <v>254</v>
+            <v>248</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
-            <v>亡者之土</v>
+            <v>铁钉</v>
           </cell>
           <cell r="B71">
-            <v>255</v>
+            <v>249</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72" t="str">
-            <v>咒术药水</v>
+            <v>遗骨</v>
           </cell>
           <cell r="B72">
-            <v>256</v>
+            <v>250</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
-            <v>诅咒宝珠</v>
+            <v>妖精粉</v>
           </cell>
           <cell r="B73">
-            <v>257</v>
+            <v>251</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
-            <v>人狼之证</v>
+            <v>雪球</v>
           </cell>
           <cell r="B74">
-            <v>258</v>
+            <v>253</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
-            <v>魔族之血</v>
+            <v>毒淤泥</v>
           </cell>
           <cell r="B75">
-            <v>259</v>
+            <v>254</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
-            <v>冰晶石</v>
+            <v>亡者之土</v>
           </cell>
           <cell r="B76">
-            <v>260</v>
+            <v>255</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
-            <v>冰的结晶</v>
+            <v>咒术药水</v>
           </cell>
           <cell r="B77">
-            <v>261</v>
+            <v>256</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
-            <v>石化之眼</v>
+            <v>诅咒宝珠</v>
           </cell>
           <cell r="B78">
-            <v>263</v>
+            <v>257</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
-            <v>夜之幕</v>
+            <v>人狼之证</v>
           </cell>
           <cell r="B79">
-            <v>264</v>
+            <v>258</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80" t="str">
-            <v>星的眼泪</v>
+            <v>魔族之血</v>
           </cell>
           <cell r="B80">
-            <v>265</v>
+            <v>259</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
-            <v>冰牛角</v>
+            <v>冰晶石</v>
           </cell>
           <cell r="B81">
-            <v>266</v>
+            <v>260</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
-            <v>寒冰气息</v>
+            <v>冰的结晶</v>
           </cell>
           <cell r="B82">
-            <v>267</v>
+            <v>261</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83" t="str">
-            <v>寒冰火种</v>
+            <v>石化之眼</v>
           </cell>
           <cell r="B83">
-            <v>268</v>
+            <v>263</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84" t="str">
-            <v>幻影水晶</v>
+            <v>夜之幕</v>
           </cell>
           <cell r="B84">
-            <v>269</v>
+            <v>264</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
-            <v>雷鸣宝珠</v>
+            <v>星的眼泪</v>
           </cell>
           <cell r="B85">
-            <v>270</v>
+            <v>265</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86" t="str">
-            <v>皮革</v>
+            <v>冰牛角</v>
           </cell>
           <cell r="B86">
-            <v>271</v>
+            <v>266</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87" t="str">
-            <v>彩色的布</v>
+            <v>寒冰气息</v>
           </cell>
           <cell r="B87">
-            <v>272</v>
+            <v>267</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88" t="str">
-            <v>鳞片</v>
+            <v>寒冰火种</v>
           </cell>
           <cell r="B88">
-            <v>273</v>
+            <v>268</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89" t="str">
-            <v>刀刃</v>
+            <v>幻影水晶</v>
           </cell>
           <cell r="B89">
-            <v>274</v>
+            <v>269</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
-            <v>骑士之证</v>
+            <v>雷鸣宝珠</v>
           </cell>
           <cell r="B90">
-            <v>275</v>
+            <v>270</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
-            <v>马尾</v>
+            <v>皮革</v>
           </cell>
           <cell r="B91">
-            <v>276</v>
+            <v>271</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
-            <v>毛线</v>
+            <v>彩色的布</v>
           </cell>
           <cell r="B92">
-            <v>277</v>
+            <v>272</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
-            <v>粘液</v>
+            <v>鳞片</v>
           </cell>
           <cell r="B93">
-            <v>278</v>
+            <v>273</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
-            <v>贵族徽章</v>
+            <v>刀刃</v>
           </cell>
           <cell r="B94">
-            <v>279</v>
+            <v>274</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
-            <v>武道精华</v>
+            <v>骑士之证</v>
           </cell>
           <cell r="B95">
-            <v>280</v>
+            <v>275</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96" t="str">
-            <v>贤者晶石</v>
+            <v>马尾</v>
           </cell>
           <cell r="B96">
-            <v>281</v>
+            <v>276</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97" t="str">
-            <v>防水皮革</v>
+            <v>毛线</v>
           </cell>
           <cell r="B97">
-            <v>282</v>
+            <v>277</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98" t="str">
-            <v>羊毛</v>
+            <v>粘液</v>
           </cell>
           <cell r="B98">
-            <v>283</v>
+            <v>278</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99" t="str">
-            <v>白磷粉末</v>
+            <v>贵族徽章</v>
           </cell>
           <cell r="B99">
-            <v>284</v>
+            <v>279</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
-            <v>暮光结晶</v>
+            <v>武道精华</v>
           </cell>
           <cell r="B100">
-            <v>285</v>
+            <v>280</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
-            <v>魔力之土</v>
+            <v>贤者晶石</v>
           </cell>
           <cell r="B101">
-            <v>286</v>
+            <v>281</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102" t="str">
-            <v>迷幻孢子</v>
+            <v>防水皮革</v>
           </cell>
           <cell r="B102">
-            <v>287</v>
+            <v>282</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
-            <v>力量果实</v>
+            <v>羊毛</v>
           </cell>
           <cell r="B103">
-            <v>288</v>
+            <v>283</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104" t="str">
-            <v>恶魔花瓣</v>
+            <v>白磷粉末</v>
           </cell>
           <cell r="B104">
-            <v>289</v>
+            <v>284</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
-            <v>月之光华</v>
+            <v>暮光结晶</v>
           </cell>
           <cell r="B105">
-            <v>290</v>
+            <v>285</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
-            <v>萤火树汁</v>
+            <v>魔力之土</v>
           </cell>
           <cell r="B106">
-            <v>291</v>
+            <v>286</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
-            <v>暗夜之露</v>
+            <v>迷幻孢子</v>
           </cell>
           <cell r="B107">
-            <v>292</v>
+            <v>287</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108" t="str">
-            <v>魅惑药水</v>
+            <v>力量果实</v>
           </cell>
           <cell r="B108">
-            <v>293</v>
+            <v>288</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
-            <v>图腾号角</v>
+            <v>恶魔花瓣</v>
           </cell>
           <cell r="B109">
-            <v>294</v>
+            <v>289</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110" t="str">
-            <v>空白卷轴</v>
+            <v>月之光华</v>
           </cell>
           <cell r="B110">
-            <v>295</v>
+            <v>290</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
-            <v>废铁</v>
+            <v>萤火树汁</v>
           </cell>
           <cell r="B111">
-            <v>296</v>
+            <v>291</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
-            <v>焦炭</v>
+            <v>暗夜之露</v>
           </cell>
           <cell r="B112">
-            <v>297</v>
+            <v>292</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
-            <v>铁块</v>
+            <v>魅惑药水</v>
           </cell>
           <cell r="B113">
-            <v>298</v>
+            <v>293</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>钢</v>
+            <v>图腾号角</v>
           </cell>
           <cell r="B114">
-            <v>299</v>
+            <v>294</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
-            <v>芜菁</v>
+            <v>空白卷轴</v>
           </cell>
           <cell r="B115">
-            <v>1001</v>
+            <v>295</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
-            <v>卷心菜</v>
+            <v>废铁</v>
           </cell>
           <cell r="B116">
-            <v>1002</v>
+            <v>296</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
-            <v>葱</v>
+            <v>焦炭</v>
           </cell>
           <cell r="B117">
-            <v>1003</v>
+            <v>297</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
-            <v>萝卜</v>
+            <v>铁块</v>
           </cell>
           <cell r="B118">
-            <v>1004</v>
+            <v>298</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
-            <v>紫甘蓝</v>
+            <v>钢</v>
           </cell>
           <cell r="B119">
-            <v>1005</v>
+            <v>299</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
-            <v>黄瓜</v>
+            <v>猪粪</v>
           </cell>
           <cell r="B120">
-            <v>1006</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
-            <v>西兰花</v>
+            <v>鸭绒</v>
           </cell>
           <cell r="B121">
-            <v>1007</v>
+            <v>301</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122" t="str">
-            <v>番茄</v>
+            <v>兔子脚</v>
           </cell>
           <cell r="B122">
-            <v>1008</v>
+            <v>302</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
-            <v>胡萝卜</v>
+            <v>芜菁</v>
           </cell>
           <cell r="B123">
-            <v>1009</v>
+            <v>1001</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124" t="str">
-            <v>西瓜</v>
+            <v>卷心菜</v>
           </cell>
           <cell r="B124">
-            <v>1010</v>
+            <v>1002</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
-            <v>辣椒</v>
+            <v>葱</v>
           </cell>
           <cell r="B125">
-            <v>1011</v>
+            <v>1003</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
-            <v>奇异果</v>
+            <v>萝卜</v>
           </cell>
           <cell r="B126">
-            <v>1012</v>
+            <v>1004</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
-            <v>茄子</v>
+            <v>紫甘蓝</v>
           </cell>
           <cell r="B127">
-            <v>1013</v>
+            <v>1005</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
-            <v>豌豆</v>
+            <v>黄瓜</v>
           </cell>
           <cell r="B128">
-            <v>1014</v>
+            <v>1006</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129" t="str">
-            <v>土豆</v>
+            <v>西兰花</v>
           </cell>
           <cell r="B129">
-            <v>1015</v>
+            <v>1007</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
-            <v>大蒜</v>
+            <v>番茄</v>
           </cell>
           <cell r="B130">
-            <v>1016</v>
+            <v>1008</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
-            <v>芦笋</v>
+            <v>胡萝卜</v>
           </cell>
           <cell r="B131">
-            <v>1017</v>
+            <v>1009</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
-            <v>南瓜</v>
+            <v>西瓜</v>
           </cell>
           <cell r="B132">
-            <v>1018</v>
+            <v>1010</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133" t="str">
-            <v>玉米</v>
+            <v>辣椒</v>
           </cell>
           <cell r="B133">
-            <v>1019</v>
+            <v>1011</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
-            <v>小麦</v>
+            <v>奇异果</v>
           </cell>
           <cell r="B134">
-            <v>1020</v>
+            <v>1012</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
-            <v>啤酒花</v>
+            <v>茄子</v>
           </cell>
           <cell r="B135">
-            <v>1021</v>
+            <v>1013</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
-            <v>葡萄</v>
+            <v>豌豆</v>
           </cell>
           <cell r="B136">
-            <v>1022</v>
+            <v>1014</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
-            <v>菠萝</v>
+            <v>土豆</v>
           </cell>
           <cell r="B137">
-            <v>1023</v>
+            <v>1015</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
-            <v>咖啡</v>
+            <v>大蒜</v>
           </cell>
           <cell r="B138">
-            <v>1024</v>
+            <v>1016</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
-            <v>草莓</v>
+            <v>芦笋</v>
           </cell>
           <cell r="B139">
-            <v>1025</v>
+            <v>1017</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
-            <v>蓝莓</v>
+            <v>南瓜</v>
           </cell>
           <cell r="B140">
-            <v>1026</v>
+            <v>1018</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141" t="str">
-            <v>红薯</v>
+            <v>玉米</v>
           </cell>
           <cell r="B141">
-            <v>1027</v>
+            <v>1019</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
-            <v>甜菜</v>
+            <v>大麦</v>
           </cell>
           <cell r="B142">
-            <v>1028</v>
+            <v>1020</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
-            <v>芜菁种子</v>
+            <v>啤酒花</v>
           </cell>
           <cell r="B143">
-            <v>1101</v>
+            <v>1021</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
-            <v>卷心菜种子</v>
+            <v>葡萄</v>
           </cell>
           <cell r="B144">
-            <v>1102</v>
+            <v>1022</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
-            <v>葱种子</v>
+            <v>菠萝</v>
           </cell>
           <cell r="B145">
-            <v>1103</v>
+            <v>1023</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
-            <v>萝卜种子</v>
+            <v>咖啡</v>
           </cell>
           <cell r="B146">
-            <v>1104</v>
+            <v>1024</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
-            <v>紫甘蓝种子</v>
+            <v>草莓</v>
           </cell>
           <cell r="B147">
-            <v>1105</v>
+            <v>1025</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148" t="str">
-            <v>黄瓜种子</v>
+            <v>蓝莓</v>
           </cell>
           <cell r="B148">
-            <v>1106</v>
+            <v>1026</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149" t="str">
-            <v>西兰花种子</v>
+            <v>红薯</v>
           </cell>
           <cell r="B149">
-            <v>1107</v>
+            <v>1027</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
-            <v>番茄种子</v>
+            <v>甜菜</v>
           </cell>
           <cell r="B150">
-            <v>1108</v>
+            <v>1028</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
-            <v>胡萝卜种子</v>
+            <v>芜菁种子</v>
           </cell>
           <cell r="B151">
-            <v>1109</v>
+            <v>1101</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
-            <v>西瓜种子</v>
+            <v>卷心菜种子</v>
           </cell>
           <cell r="B152">
-            <v>1110</v>
+            <v>1102</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
-            <v>辣椒种子</v>
+            <v>葱种子</v>
           </cell>
           <cell r="B153">
-            <v>1111</v>
+            <v>1103</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
-            <v>奇异果种子</v>
+            <v>萝卜种子</v>
           </cell>
           <cell r="B154">
-            <v>1112</v>
+            <v>1104</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
-            <v>茄子种子</v>
+            <v>紫甘蓝种子</v>
           </cell>
           <cell r="B155">
-            <v>1113</v>
+            <v>1105</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
-            <v>豌豆种子</v>
+            <v>黄瓜种子</v>
           </cell>
           <cell r="B156">
-            <v>1114</v>
+            <v>1106</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
-            <v>土豆种子</v>
+            <v>西兰花种子</v>
           </cell>
           <cell r="B157">
-            <v>1115</v>
+            <v>1107</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158" t="str">
-            <v>大蒜种子</v>
+            <v>番茄种子</v>
           </cell>
           <cell r="B158">
-            <v>1116</v>
+            <v>1108</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159" t="str">
-            <v>芦笋种子</v>
+            <v>胡萝卜种子</v>
           </cell>
           <cell r="B159">
-            <v>1117</v>
+            <v>1109</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
-            <v>南瓜种子</v>
+            <v>西瓜种子</v>
           </cell>
           <cell r="B160">
-            <v>1118</v>
+            <v>1110</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
-            <v>玉米种子</v>
+            <v>辣椒种子</v>
           </cell>
           <cell r="B161">
-            <v>1119</v>
+            <v>1111</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
-            <v>大麦种子</v>
+            <v>奇异果种子</v>
           </cell>
           <cell r="B162">
-            <v>1120</v>
+            <v>1112</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
-            <v>啤酒花种子</v>
+            <v>茄子种子</v>
           </cell>
           <cell r="B163">
-            <v>1121</v>
+            <v>1113</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164" t="str">
-            <v>葡萄种子</v>
+            <v>豌豆种子</v>
           </cell>
           <cell r="B164">
-            <v>1122</v>
+            <v>1114</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165" t="str">
-            <v>菠萝种子</v>
+            <v>土豆种子</v>
           </cell>
           <cell r="B165">
-            <v>1123</v>
+            <v>1115</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
-            <v>咖啡种子</v>
+            <v>大蒜种子</v>
           </cell>
           <cell r="B166">
-            <v>1124</v>
+            <v>1116</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
-            <v>草莓种子</v>
+            <v>芦笋种子</v>
           </cell>
           <cell r="B167">
-            <v>1125</v>
+            <v>1117</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
-            <v>蓝莓种子</v>
+            <v>南瓜种子</v>
           </cell>
           <cell r="B168">
-            <v>1126</v>
+            <v>1118</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
-            <v>红薯种子</v>
+            <v>玉米种子</v>
           </cell>
           <cell r="B169">
-            <v>1127</v>
+            <v>1119</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
-            <v>甜菜种子</v>
+            <v>大麦种子</v>
           </cell>
           <cell r="B170">
-            <v>1128</v>
+            <v>1120</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
-            <v>长剑</v>
+            <v>啤酒花种子</v>
           </cell>
           <cell r="B171">
-            <v>1600</v>
+            <v>1121</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172" t="str">
-            <v>诅咒之剑</v>
+            <v>葡萄种子</v>
           </cell>
           <cell r="B172">
-            <v>1601</v>
+            <v>1122</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173" t="str">
-            <v>烈焰之刃</v>
+            <v>菠萝种子</v>
           </cell>
           <cell r="B173">
-            <v>1602</v>
+            <v>1123</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174" t="str">
-            <v>大地之剑</v>
+            <v>咖啡种子</v>
           </cell>
           <cell r="B174">
-            <v>1603</v>
+            <v>1124</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175" t="str">
-            <v>冰之刃</v>
+            <v>草莓种子</v>
           </cell>
           <cell r="B175">
-            <v>1604</v>
+            <v>1125</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
-            <v>铁枪</v>
+            <v>蓝莓种子</v>
           </cell>
           <cell r="B176">
-            <v>1605</v>
+            <v>1126</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
-            <v>骑士长枪</v>
+            <v>红薯种子</v>
           </cell>
           <cell r="B177">
-            <v>1606</v>
+            <v>1127</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178" t="str">
-            <v>血腥之枪</v>
+            <v>甜菜种子</v>
           </cell>
           <cell r="B178">
-            <v>1607</v>
+            <v>1128</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179" t="str">
-            <v>三叉戟</v>
+            <v>长剑</v>
           </cell>
           <cell r="B179">
-            <v>1608</v>
+            <v>1600</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180" t="str">
-            <v>战斧</v>
+            <v>诅咒之剑</v>
           </cell>
           <cell r="B180">
-            <v>1609</v>
+            <v>1601</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181" t="str">
-            <v>毒蜥之牙</v>
+            <v>烈焰之刃</v>
           </cell>
           <cell r="B181">
-            <v>1610</v>
+            <v>1602</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
-            <v>恶魔之斧</v>
+            <v>大地之剑</v>
           </cell>
           <cell r="B182">
-            <v>1611</v>
+            <v>1603</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183" t="str">
-            <v>蛇皮鞭</v>
+            <v>冰之刃</v>
           </cell>
           <cell r="B183">
-            <v>1612</v>
+            <v>1604</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
-            <v>藤鞭</v>
+            <v>铁枪</v>
           </cell>
           <cell r="B184">
-            <v>1613</v>
+            <v>1605</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
-            <v>女王鞭</v>
+            <v>骑士长枪</v>
           </cell>
           <cell r="B185">
-            <v>1614</v>
+            <v>1606</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
-            <v>蛇牙鞭</v>
+            <v>血腥之矛</v>
           </cell>
           <cell r="B186">
-            <v>1615</v>
+            <v>1607</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
-            <v>暴雪斧</v>
+            <v>三叉戟</v>
           </cell>
           <cell r="B187">
-            <v>1616</v>
+            <v>1608</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
-            <v>秘银长剑</v>
+            <v>战斧</v>
           </cell>
           <cell r="B188">
-            <v>1617</v>
+            <v>1609</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189" t="str">
-            <v>幻影长枪</v>
+            <v>毒蜥之牙</v>
           </cell>
           <cell r="B189">
-            <v>1618</v>
+            <v>1610</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190" t="str">
-            <v>雷神之鞭</v>
+            <v>恶魔之斧</v>
           </cell>
           <cell r="B190">
-            <v>1619</v>
+            <v>1611</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
-            <v>死亡之鞭</v>
+            <v>蛇皮鞭</v>
           </cell>
           <cell r="B191">
-            <v>1620</v>
+            <v>1612</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
-            <v>布衣</v>
+            <v>荆棘鞭</v>
           </cell>
           <cell r="B192">
-            <v>1650</v>
+            <v>1613</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
-            <v>皮铠</v>
+            <v>女王之鞭</v>
           </cell>
           <cell r="B193">
-            <v>1651</v>
+            <v>1614</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
-            <v>锁子甲</v>
+            <v>蛇牙鞭</v>
           </cell>
           <cell r="B194">
-            <v>1652</v>
+            <v>1615</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
-            <v>毛皮斗篷</v>
+            <v>暴雪斧</v>
           </cell>
           <cell r="B195">
-            <v>1653</v>
+            <v>1616</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196" t="str">
-            <v>铁铠甲</v>
+            <v>秘银长剑</v>
           </cell>
           <cell r="B196">
-            <v>1654</v>
+            <v>1617</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
-            <v>红莲之铠</v>
+            <v>幻影长枪</v>
           </cell>
           <cell r="B197">
-            <v>1655</v>
+            <v>1618</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
-            <v>铁龟铠</v>
+            <v>雷神之鞭</v>
           </cell>
           <cell r="B198">
-            <v>1656</v>
+            <v>1619</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
-            <v>华丽背心</v>
+            <v>死亡之鞭</v>
           </cell>
           <cell r="B199">
-            <v>1657</v>
+            <v>1620</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
-            <v>鳞铠</v>
+            <v>布衣</v>
           </cell>
           <cell r="B200">
-            <v>1658</v>
+            <v>1650</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
-            <v>暗之袍</v>
+            <v>皮铠</v>
           </cell>
           <cell r="B201">
-            <v>1659</v>
+            <v>1651</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
-            <v>疾风背心</v>
+            <v>锁子甲</v>
           </cell>
           <cell r="B202">
-            <v>1660</v>
+            <v>1652</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
-            <v>魔法铠甲</v>
+            <v>毛皮斗篷</v>
           </cell>
           <cell r="B203">
-            <v>1661</v>
+            <v>1653</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
-            <v>钢刃锁甲</v>
+            <v>铁铠甲</v>
           </cell>
           <cell r="B204">
-            <v>1662</v>
+            <v>1654</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
-            <v>丝织长袍</v>
+            <v>红莲之铠</v>
           </cell>
           <cell r="B205">
-            <v>1663</v>
+            <v>1655</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
-            <v>水之羽衣</v>
+            <v>铁龟铠</v>
           </cell>
           <cell r="B206">
-            <v>1664</v>
+            <v>1656</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
-            <v>贵族长裙</v>
+            <v>华丽背心</v>
           </cell>
           <cell r="B207">
-            <v>1665</v>
+            <v>1657</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
-            <v>幸运之衣</v>
+            <v>鳞铠</v>
           </cell>
           <cell r="B208">
-            <v>1666</v>
+            <v>1658</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
-            <v>布鞋</v>
+            <v>暗之袍</v>
           </cell>
           <cell r="B209">
-            <v>1700</v>
+            <v>1659</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
-            <v>皮鞋</v>
+            <v>疾风背心</v>
           </cell>
           <cell r="B210">
-            <v>1701</v>
+            <v>1660</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
-            <v>士兵长靴</v>
+            <v>魔法铠甲</v>
           </cell>
           <cell r="B211">
-            <v>1702</v>
+            <v>1661</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
-            <v>登山者之靴</v>
+            <v>钢刃锁甲</v>
           </cell>
           <cell r="B212">
-            <v>1703</v>
+            <v>1662</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213" t="str">
-            <v>运动鞋</v>
+            <v>丝织长袍</v>
           </cell>
           <cell r="B213">
-            <v>1704</v>
+            <v>1663</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214" t="str">
-            <v>贵族长靴</v>
+            <v>水之羽衣</v>
           </cell>
           <cell r="B214">
-            <v>1705</v>
+            <v>1664</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215" t="str">
-            <v>武道鞋</v>
+            <v>贵族长裙</v>
           </cell>
           <cell r="B215">
-            <v>1706</v>
+            <v>1665</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216" t="str">
-            <v>骑士护胫</v>
+            <v>幸运之衣</v>
           </cell>
           <cell r="B216">
-            <v>1707</v>
+            <v>1666</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
-            <v>贤者之履</v>
+            <v>布鞋</v>
           </cell>
           <cell r="B217">
-            <v>1708</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218" t="str">
-            <v>风神之履</v>
+            <v>皮鞋</v>
           </cell>
           <cell r="B218">
-            <v>1709</v>
+            <v>1701</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219" t="str">
-            <v>踏浪长靴</v>
+            <v>士兵长靴</v>
           </cell>
           <cell r="B219">
-            <v>1710</v>
+            <v>1702</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220" t="str">
-            <v>锄头</v>
+            <v>登山者之靴</v>
           </cell>
           <cell r="B220">
-            <v>2000</v>
+            <v>1703</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
-            <v>洒水壶</v>
+            <v>运动鞋</v>
           </cell>
           <cell r="B221">
-            <v>2001</v>
+            <v>1704</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222" t="str">
-            <v>斧头</v>
+            <v>贵族长靴</v>
           </cell>
           <cell r="B222">
-            <v>2002</v>
+            <v>1705</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223" t="str">
-            <v>镰刀</v>
+            <v>武道鞋</v>
           </cell>
           <cell r="B223">
-            <v>2003</v>
+            <v>1706</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224" t="str">
-            <v>鱼竿</v>
+            <v>骑士护胫</v>
           </cell>
           <cell r="B224">
-            <v>2004</v>
+            <v>1707</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225" t="str">
-            <v>缝纫机</v>
+            <v>贤者之履</v>
           </cell>
           <cell r="B225">
-            <v>2100</v>
+            <v>1708</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
-            <v>锻造炉</v>
+            <v>风神之履</v>
           </cell>
           <cell r="B226">
-            <v>2101</v>
+            <v>1709</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
-            <v>烘烤炉</v>
+            <v>踏浪长靴</v>
           </cell>
           <cell r="B227">
-            <v>2102</v>
+            <v>1710</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
-            <v>蒸煮锅</v>
+            <v>草帽</v>
           </cell>
           <cell r="B228">
-            <v>2103</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
-            <v>冷餐台</v>
+            <v>阳光草帽</v>
           </cell>
           <cell r="B229">
-            <v>2104</v>
+            <v>1801</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230" t="str">
-            <v>酿造桶</v>
+            <v>法师帽</v>
           </cell>
           <cell r="B230">
-            <v>2105</v>
+            <v>1802</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231" t="str">
-            <v>绘写台</v>
+            <v>士兵头盔</v>
           </cell>
           <cell r="B231">
-            <v>2106</v>
+            <v>1803</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232" t="str">
-            <v>冰箱</v>
+            <v>尖角头盔</v>
           </cell>
           <cell r="B232">
-            <v>2107</v>
+            <v>1804</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233" t="str">
-            <v>储物箱(木)</v>
+            <v>幸运头巾</v>
           </cell>
           <cell r="B233">
-            <v>2108</v>
+            <v>1805</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234" t="str">
-            <v>储物箱(银)</v>
+            <v>绅士礼帽</v>
           </cell>
           <cell r="B234">
-            <v>2109</v>
+            <v>1806</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
-            <v>储物箱(金)</v>
+            <v>贵族头巾</v>
           </cell>
           <cell r="B235">
-            <v>2110</v>
+            <v>1807</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
-            <v>普通柜台</v>
+            <v>战争头盔</v>
           </cell>
           <cell r="B236">
-            <v>2111</v>
+            <v>1808</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
-            <v>服饰架</v>
+            <v>锄头</v>
           </cell>
           <cell r="B237">
-            <v>2113</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
-            <v>沙发</v>
+            <v>洒水壶</v>
           </cell>
           <cell r="B238">
-            <v>2200</v>
+            <v>2001</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239" t="str">
-            <v>搅拌器</v>
+            <v>斧头</v>
           </cell>
           <cell r="B239">
-            <v>2114</v>
+            <v>2002</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240" t="str">
-            <v>双人床</v>
+            <v>镰刀</v>
           </cell>
           <cell r="B240">
-            <v>2201</v>
+            <v>2003</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241" t="str">
-            <v>鲫鱼</v>
+            <v>鱼竿</v>
           </cell>
           <cell r="B241">
-            <v>4000</v>
+            <v>2004</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
-            <v>小龙虾</v>
+            <v>缝纫机</v>
           </cell>
           <cell r="B242">
-            <v>4003</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
-            <v>鲤鱼</v>
+            <v>锻造炉</v>
           </cell>
           <cell r="B243">
-            <v>4004</v>
+            <v>2101</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244" t="str">
-            <v>鲮鱼</v>
+            <v>烘烤炉</v>
           </cell>
           <cell r="B244">
-            <v>4006</v>
+            <v>2102</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
-            <v>手套蟹</v>
+            <v>炖煮锅</v>
           </cell>
           <cell r="B245">
-            <v>4007</v>
+            <v>2103</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246" t="str">
-            <v>鲶鱼</v>
+            <v>冷餐台</v>
           </cell>
           <cell r="B246">
-            <v>4008</v>
+            <v>2104</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247" t="str">
-            <v>丁鱼</v>
+            <v>酿造桶</v>
           </cell>
           <cell r="B247">
-            <v>4009</v>
+            <v>2105</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248" t="str">
-            <v>锦鲤</v>
+            <v>绘写台</v>
           </cell>
           <cell r="B248">
-            <v>4010</v>
+            <v>2106</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249" t="str">
-            <v>线鱼</v>
+            <v>冰箱</v>
           </cell>
           <cell r="B249">
-            <v>4011</v>
+            <v>2107</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
-            <v>梭鲈</v>
+            <v>储物箱(木)</v>
           </cell>
           <cell r="B250">
-            <v>4012</v>
+            <v>2108</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251" t="str">
-            <v>兰寿金鱼</v>
+            <v>储物箱(银)</v>
           </cell>
           <cell r="B251">
-            <v>4013</v>
+            <v>2109</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
-            <v>樱桃鲑鱼</v>
+            <v>储物箱(金)</v>
           </cell>
           <cell r="B252">
-            <v>4014</v>
+            <v>2110</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
-            <v>虹鳟鱼</v>
+            <v>普通柜台</v>
           </cell>
           <cell r="B253">
-            <v>4015</v>
+            <v>2111</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254" t="str">
-            <v>鲷鱼</v>
+            <v>服饰架</v>
           </cell>
           <cell r="B254">
-            <v>4016</v>
+            <v>2113</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255" t="str">
-            <v>金鳟鱼</v>
+            <v>沙发</v>
           </cell>
           <cell r="B255">
-            <v>4017</v>
+            <v>2200</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256" t="str">
-            <v>霓虹脂鲤</v>
+            <v>搅拌器</v>
           </cell>
           <cell r="B256">
-            <v>4018</v>
+            <v>2114</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
-            <v>桃花鱼</v>
+            <v>双人床</v>
           </cell>
           <cell r="B257">
-            <v>4020</v>
+            <v>2201</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258" t="str">
-            <v>鲑鱼</v>
+            <v>鲫鱼</v>
           </cell>
           <cell r="B258">
-            <v>4021</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259" t="str">
-            <v>孔雀鱼</v>
+            <v>小龙虾</v>
           </cell>
           <cell r="B259">
-            <v>4022</v>
+            <v>4003</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260" t="str">
-            <v>银龙鱼</v>
+            <v>鲤鱼</v>
           </cell>
           <cell r="B260">
-            <v>4023</v>
+            <v>4004</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
-            <v>洞穴天使鱼</v>
+            <v>鲮鱼</v>
           </cell>
           <cell r="B261">
-            <v>4024</v>
+            <v>4006</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
-            <v>沙丁鱼</v>
+            <v>手套蟹</v>
           </cell>
           <cell r="B262">
-            <v>4100</v>
+            <v>4007</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
-            <v>竹荚鱼</v>
+            <v>鲶鱼</v>
           </cell>
           <cell r="B263">
-            <v>4101</v>
+            <v>4008</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264" t="str">
-            <v>海鳗</v>
+            <v>丁鱼</v>
           </cell>
           <cell r="B264">
-            <v>4103</v>
+            <v>4009</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265" t="str">
-            <v>章鱼</v>
+            <v>锦鲤</v>
           </cell>
           <cell r="B265">
-            <v>4105</v>
+            <v>4010</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266" t="str">
-            <v>比目鱼</v>
+            <v>线鱼</v>
           </cell>
           <cell r="B266">
-            <v>4106</v>
+            <v>4011</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
-            <v>河豚</v>
+            <v>梭鲈</v>
           </cell>
           <cell r="B267">
-            <v>4109</v>
+            <v>4012</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268" t="str">
-            <v>水母</v>
+            <v>兰寿金鱼</v>
           </cell>
           <cell r="B268">
-            <v>4110</v>
+            <v>4013</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
-            <v>条石鲷</v>
+            <v>樱桃鲑鱼</v>
           </cell>
           <cell r="B269">
-            <v>4111</v>
+            <v>4014</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270" t="str">
-            <v>红鲷鱼</v>
+            <v>虹鳟鱼</v>
           </cell>
           <cell r="B270">
-            <v>4112</v>
+            <v>4015</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
-            <v>蓝蟹</v>
+            <v>鲷鱼</v>
           </cell>
           <cell r="B271">
-            <v>4113</v>
+            <v>4016</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
-            <v>鲯鳅鱼</v>
+            <v>金鳟鱼</v>
           </cell>
           <cell r="B272">
-            <v>4114</v>
+            <v>4017</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
-            <v>龙虾</v>
+            <v>霓虹脂鲤</v>
           </cell>
           <cell r="B273">
-            <v>4115</v>
+            <v>4018</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
-            <v>金枪鱼</v>
+            <v>桃花鱼</v>
           </cell>
           <cell r="B274">
-            <v>4116</v>
+            <v>4020</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275" t="str">
-            <v>斑马狮子鱼</v>
+            <v>鲑鱼</v>
           </cell>
           <cell r="B275">
-            <v>4117</v>
+            <v>4021</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276" t="str">
-            <v>米饭</v>
+            <v>孔雀鱼</v>
           </cell>
           <cell r="B276">
-            <v>3000</v>
+            <v>4022</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
-            <v>发酵粉</v>
+            <v>银龙鱼</v>
           </cell>
           <cell r="B277">
-            <v>3001</v>
+            <v>4023</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278" t="str">
-            <v>盐</v>
+            <v>洞穴天使鱼</v>
           </cell>
           <cell r="B278">
-            <v>3002</v>
+            <v>4024</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
-            <v>酸味香料</v>
+            <v>沙丁鱼</v>
           </cell>
           <cell r="B279">
-            <v>3003</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
-            <v>蜂蜜</v>
+            <v>竹荚鱼</v>
           </cell>
           <cell r="B280">
-            <v>3005</v>
+            <v>4101</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
-            <v>牛奶</v>
+            <v>海鳗</v>
           </cell>
           <cell r="B281">
-            <v>3006</v>
+            <v>4103</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
-            <v>鸡蛋</v>
+            <v>章鱼</v>
           </cell>
           <cell r="B282">
-            <v>3007</v>
+            <v>4105</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
-            <v>猪肉</v>
+            <v>比目鱼</v>
           </cell>
           <cell r="B283">
-            <v>3008</v>
+            <v>4106</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284" t="str">
-            <v>面粉</v>
+            <v>河豚</v>
           </cell>
           <cell r="B284">
-            <v>3009</v>
+            <v>4109</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
-            <v>咖啡粉</v>
+            <v>水母</v>
           </cell>
           <cell r="B285">
-            <v>3010</v>
+            <v>4110</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
-            <v>海苔</v>
+            <v>条石鲷</v>
           </cell>
           <cell r="B286">
-            <v>3011</v>
+            <v>4111</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
-            <v>黄油</v>
+            <v>红鲷鱼</v>
           </cell>
           <cell r="B287">
-            <v>3011</v>
+            <v>4112</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
-            <v>腌芜菁</v>
+            <v>蓝蟹</v>
           </cell>
           <cell r="B288">
-            <v>3100</v>
+            <v>4113</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289" t="str">
-            <v>蔬菜沙拉</v>
+            <v>鲯鳅鱼</v>
           </cell>
           <cell r="B289">
-            <v>3101</v>
+            <v>4114</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290" t="str">
-            <v>三明治</v>
+            <v>龙虾</v>
           </cell>
           <cell r="B290">
-            <v>3102</v>
+            <v>4115</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291" t="str">
-            <v>腌萝卜</v>
+            <v>金枪鱼</v>
           </cell>
           <cell r="B291">
-            <v>3103</v>
+            <v>4116</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
-            <v>拉面</v>
+            <v>斑马狮子鱼</v>
           </cell>
           <cell r="B292">
-            <v>3104</v>
+            <v>4117</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293" t="str">
-            <v>蜂蜜蛋糕</v>
+            <v>米饭</v>
           </cell>
           <cell r="B293">
-            <v>3105</v>
+            <v>3000</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
-            <v>披萨</v>
+            <v>发酵粉</v>
           </cell>
           <cell r="B294">
-            <v>3106</v>
+            <v>3001</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
-            <v>腌黄瓜</v>
+            <v>盐</v>
           </cell>
           <cell r="B295">
-            <v>3107</v>
+            <v>3002</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296" t="str">
-            <v>烤西兰花</v>
+            <v>酸味香料</v>
           </cell>
           <cell r="B296">
-            <v>3108</v>
+            <v>3003</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297" t="str">
-            <v>水煮蛋</v>
+            <v>蜂蜜</v>
           </cell>
           <cell r="B297">
-            <v>3109</v>
+            <v>3005</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298" t="str">
-            <v>烤肉串</v>
+            <v>牛奶</v>
           </cell>
           <cell r="B298">
-            <v>3110</v>
+            <v>3006</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299" t="str">
-            <v>饭团</v>
+            <v>鸡蛋</v>
           </cell>
           <cell r="B299">
-            <v>3111</v>
+            <v>3007</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300" t="str">
-            <v>面包</v>
+            <v>猪肉</v>
           </cell>
           <cell r="B300">
-            <v>3112</v>
+            <v>3008</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
-            <v>烤海苔</v>
+            <v>面粉</v>
           </cell>
           <cell r="B301">
-            <v>3113</v>
+            <v>3009</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302" t="str">
-            <v>烤肉饼</v>
+            <v>咖啡粉</v>
           </cell>
           <cell r="B302">
-            <v>3114</v>
+            <v>3010</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303" t="str">
-            <v>汉堡</v>
+            <v>海苔</v>
           </cell>
           <cell r="B303">
-            <v>3115</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304" t="str">
-            <v>辣蟹堡</v>
+            <v>黄油</v>
           </cell>
           <cell r="B304">
-            <v>3116</v>
+            <v>3011</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305" t="str">
-            <v>土豆泥</v>
+            <v>腌芜菁</v>
           </cell>
           <cell r="B305">
-            <v>3117</v>
+            <v>3100</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306" t="str">
-            <v>海鲜饭</v>
+            <v>蔬菜沙拉</v>
           </cell>
           <cell r="B306">
-            <v>3118</v>
+            <v>3101</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
-            <v>烤玉米</v>
+            <v>三明治</v>
           </cell>
           <cell r="B307">
-            <v>3119</v>
+            <v>3102</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308" t="str">
-            <v>蔬菜汁</v>
+            <v>腌萝卜</v>
           </cell>
           <cell r="B308">
-            <v>3120</v>
+            <v>3103</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309" t="str">
-            <v>西瓜果汁</v>
+            <v>拉面</v>
           </cell>
           <cell r="B309">
-            <v>3121</v>
+            <v>3104</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
-            <v>奇异果汁</v>
+            <v>蜂蜜蛋糕</v>
           </cell>
           <cell r="B310">
-            <v>3122</v>
+            <v>3105</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
-            <v>葡萄汁</v>
+            <v>披萨</v>
           </cell>
           <cell r="B311">
-            <v>3123</v>
+            <v>3106</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
-            <v>菠萝汁</v>
+            <v>腌黄瓜</v>
           </cell>
           <cell r="B312">
-            <v>3124</v>
+            <v>3107</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
-            <v>草莓汁</v>
+            <v>烤西兰花</v>
           </cell>
           <cell r="B313">
-            <v>3125</v>
+            <v>3108</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314" t="str">
-            <v>蓝莓汁</v>
+            <v>水煮蛋</v>
           </cell>
           <cell r="B314">
-            <v>3126</v>
+            <v>3109</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315" t="str">
-            <v>玉米汁</v>
+            <v>烤肉串</v>
           </cell>
           <cell r="B315">
-            <v>3127</v>
+            <v>3110</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316" t="str">
-            <v>烤蜜薯</v>
+            <v>饭团</v>
           </cell>
           <cell r="B316">
-            <v>3128</v>
+            <v>3111</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
-            <v>甜菜汁</v>
+            <v>面包</v>
           </cell>
           <cell r="B317">
-            <v>3129</v>
+            <v>3112</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318" t="str">
-            <v>奶酪</v>
+            <v>烤海苔</v>
           </cell>
           <cell r="B318">
-            <v>3130</v>
+            <v>3113</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
-            <v>烤茄子</v>
+            <v>烤肉饼</v>
           </cell>
           <cell r="B319">
-            <v>3131</v>
+            <v>3114</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320" t="str">
-            <v>饺子</v>
+            <v>汉堡</v>
           </cell>
           <cell r="B320">
-            <v>3132</v>
+            <v>3115</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321" t="str">
-            <v>炖菜</v>
+            <v>辣蟹堡</v>
           </cell>
           <cell r="B321">
-            <v>3133</v>
+            <v>3116</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322" t="str">
-            <v>烤芦笋</v>
+            <v>土豆泥</v>
           </cell>
           <cell r="B322">
-            <v>3134</v>
+            <v>3117</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323" t="str">
-            <v>红菜汤</v>
+            <v>海鲜饭</v>
           </cell>
           <cell r="B323">
-            <v>3135</v>
+            <v>3118</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324" t="str">
-            <v>豌豆汤</v>
+            <v>烤玉米</v>
           </cell>
           <cell r="B324">
-            <v>3136</v>
+            <v>3119</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325" t="str">
-            <v>草莓牛奶</v>
+            <v>蔬菜汁</v>
           </cell>
           <cell r="B325">
-            <v>3137</v>
+            <v>3120</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
-            <v>莓莓果汁</v>
+            <v>西瓜果汁</v>
           </cell>
           <cell r="B326">
-            <v>3138</v>
+            <v>3121</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327" t="str">
-            <v>鲑鱼饭团</v>
+            <v>奇异果汁</v>
           </cell>
           <cell r="B327">
-            <v>3139</v>
+            <v>3122</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328" t="str">
-            <v>拿铁</v>
+            <v>葡萄汁</v>
           </cell>
           <cell r="B328">
-            <v>3140</v>
+            <v>3123</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329" t="str">
-            <v>黑咖啡</v>
+            <v>菠萝汁</v>
           </cell>
           <cell r="B329">
-            <v>3141</v>
+            <v>3124</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330" t="str">
-            <v>葡萄酒</v>
+            <v>草莓汁</v>
           </cell>
           <cell r="B330">
-            <v>3142</v>
+            <v>3125</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331" t="str">
-            <v>伏特加</v>
+            <v>蓝莓汁</v>
           </cell>
           <cell r="B331">
-            <v>3143</v>
+            <v>3126</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
-            <v>啤酒</v>
+            <v>玉米汁</v>
           </cell>
           <cell r="B332">
-            <v>3144</v>
+            <v>3127</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333" t="str">
-            <v>朗姆</v>
+            <v>烤蜜薯</v>
           </cell>
           <cell r="B333">
-            <v>3145</v>
+            <v>3128</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334" t="str">
-            <v>野蜂拉格</v>
+            <v>甜菜汁</v>
           </cell>
           <cell r="B334">
-            <v>3146</v>
+            <v>3129</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
-            <v>双莓白兰地</v>
+            <v>奶酪</v>
           </cell>
           <cell r="B335">
-            <v>3147</v>
+            <v>3130</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
-            <v>绯红之吻</v>
+            <v>烤茄子</v>
           </cell>
           <cell r="B336">
-            <v>3148</v>
+            <v>3131</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
-            <v>阳光男孩</v>
+            <v>饺子</v>
           </cell>
           <cell r="B337">
-            <v>3149</v>
+            <v>3132</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
-            <v>盐烤鲮鱼</v>
+            <v>炖菜</v>
           </cell>
           <cell r="B338">
-            <v>3150</v>
+            <v>3133</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339" t="str">
-            <v>盐烤丁鱼</v>
+            <v>烤芦笋</v>
           </cell>
           <cell r="B339">
-            <v>3151</v>
+            <v>3134</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340" t="str">
-            <v>盐烤虹鳟鱼</v>
+            <v>红菜汤</v>
           </cell>
           <cell r="B340">
-            <v>3152</v>
+            <v>3135</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341" t="str">
-            <v>烤鲷鱼</v>
+            <v>豌豆汤</v>
           </cell>
           <cell r="B341">
-            <v>3153</v>
+            <v>3136</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342" t="str">
-            <v>盐烤金鳟鱼</v>
+            <v>草莓牛奶</v>
           </cell>
           <cell r="B342">
-            <v>3154</v>
+            <v>3137</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343" t="str">
-            <v>盐烤鲑鱼</v>
+            <v>莓莓果汁</v>
           </cell>
           <cell r="B343">
-            <v>3155</v>
+            <v>3138</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344" t="str">
-            <v>烤沙丁鱼串</v>
+            <v>鲑鱼饭团</v>
           </cell>
           <cell r="B344">
-            <v>3156</v>
+            <v>3139</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345" t="str">
-            <v>烤竹荚鱼</v>
+            <v>拿铁</v>
           </cell>
           <cell r="B345">
-            <v>3157</v>
+            <v>3140</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346" t="str">
-            <v>烤海鳗</v>
+            <v>黑咖啡</v>
           </cell>
           <cell r="B346">
-            <v>3158</v>
+            <v>3141</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347" t="str">
-            <v>烤比目鱼</v>
+            <v>葡萄酒</v>
           </cell>
           <cell r="B347">
-            <v>3159</v>
+            <v>3142</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348" t="str">
-            <v>烤河豚鱼</v>
+            <v>伏特加</v>
           </cell>
           <cell r="B348">
-            <v>3160</v>
+            <v>3143</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349" t="str">
-            <v>烤条石鲷</v>
+            <v>啤酒</v>
           </cell>
           <cell r="B349">
-            <v>3161</v>
+            <v>3144</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350" t="str">
-            <v>烤红鲷鱼</v>
+            <v>朗姆</v>
           </cell>
           <cell r="B350">
-            <v>3162</v>
+            <v>3145</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351" t="str">
-            <v>烤蓝蟹</v>
+            <v>野蜂拉格</v>
           </cell>
           <cell r="B351">
-            <v>3163</v>
+            <v>3146</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352" t="str">
-            <v>烤龙虾</v>
+            <v>双莓白兰地</v>
           </cell>
           <cell r="B352">
-            <v>3164</v>
+            <v>3147</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353" t="str">
-            <v>烤金枪鱼</v>
+            <v>绯红之吻</v>
           </cell>
           <cell r="B353">
-            <v>3165</v>
+            <v>3148</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354" t="str">
-            <v>煮蟹肉</v>
+            <v>阳光男孩</v>
           </cell>
           <cell r="B354">
-            <v>3166</v>
+            <v>3149</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355" t="str">
-            <v>海鲜浓汤</v>
+            <v>盐烤鲮鱼</v>
           </cell>
           <cell r="B355">
-            <v>3167</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356" t="str">
-            <v>鳗鱼饭</v>
+            <v>盐烤丁鱼</v>
           </cell>
           <cell r="B356">
-            <v>3168</v>
+            <v>3151</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357" t="str">
-            <v>鲫鱼蔬菜汤</v>
+            <v>盐烤虹鳟鱼</v>
           </cell>
           <cell r="B357">
-            <v>3169</v>
+            <v>3152</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358" t="str">
-            <v>鲮鱼丸</v>
+            <v>烤鲷鱼</v>
           </cell>
           <cell r="B358">
-            <v>3170</v>
+            <v>3153</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359" t="str">
-            <v>鲑鱼刺身</v>
+            <v>盐烤金鳟鱼</v>
           </cell>
           <cell r="B359">
-            <v>3171</v>
+            <v>3154</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360" t="str">
-            <v>章鱼小丸子</v>
+            <v>盐烤鲑鱼</v>
           </cell>
           <cell r="B360">
-            <v>3172</v>
+            <v>3155</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361" t="str">
-            <v>炖煮条石鲷</v>
+            <v>烤沙丁鱼串</v>
           </cell>
           <cell r="B361">
-            <v>3173</v>
+            <v>3156</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362" t="str">
-            <v>红鲷刺身</v>
+            <v>烤竹荚鱼</v>
           </cell>
           <cell r="B362">
-            <v>3174</v>
+            <v>3157</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363" t="str">
-            <v>河豚刺身</v>
+            <v>烤海鳗</v>
           </cell>
           <cell r="B363">
-            <v>3175</v>
+            <v>3158</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364" t="str">
-            <v>螃蟹煲</v>
+            <v>烤比目鱼</v>
           </cell>
           <cell r="B364">
-            <v>3176</v>
+            <v>3159</v>
           </cell>
         </row>
         <row r="365">
           <cell r="A365" t="str">
-            <v>金枪鱼刺身</v>
+            <v>烤河豚鱼</v>
           </cell>
           <cell r="B365">
-            <v>3177</v>
+            <v>3160</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366" t="str">
-            <v>龙虾鱼子酱</v>
+            <v>烤条石鲷</v>
           </cell>
           <cell r="B366">
-            <v>3178</v>
+            <v>3161</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367" t="str">
-            <v>回春卷轴</v>
+            <v>烤红鲷鱼</v>
           </cell>
           <cell r="B367">
-            <v>4000</v>
+            <v>3162</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368" t="str">
-            <v>振奋卷轴</v>
+            <v>烤蓝蟹</v>
           </cell>
           <cell r="B368">
-            <v>4001</v>
+            <v>3163</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369" t="str">
-            <v>昏睡卷轴</v>
+            <v>烤龙虾</v>
           </cell>
           <cell r="B369">
-            <v>4002</v>
+            <v>3164</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370" t="str">
-            <v>感电卷轴</v>
+            <v>烤金枪鱼</v>
           </cell>
           <cell r="B370">
-            <v>4003</v>
+            <v>3165</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371" t="str">
-            <v>冰氛卷轴</v>
+            <v>煮蟹肉</v>
           </cell>
           <cell r="B371">
-            <v>4004</v>
+            <v>3166</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372" t="str">
-            <v>火氛卷轴</v>
+            <v>海鲜浓汤</v>
           </cell>
           <cell r="B372">
-            <v>4005</v>
+            <v>3167</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373" t="str">
-            <v>沉默卷轴</v>
+            <v>鳗鱼饭</v>
           </cell>
           <cell r="B373">
-            <v>4006</v>
+            <v>3168</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374" t="str">
-            <v>减速卷轴</v>
+            <v>鲫鱼蔬菜汤</v>
           </cell>
           <cell r="B374">
-            <v>4007</v>
+            <v>3169</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375" t="str">
-            <v>闪避卷轴</v>
+            <v>鲮鱼丸</v>
           </cell>
           <cell r="B375">
-            <v>4008</v>
+            <v>3170</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376" t="str">
-            <v>力量卷轴</v>
+            <v>鲑鱼刺身</v>
           </cell>
           <cell r="B376">
-            <v>4009</v>
+            <v>3171</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377" t="str">
+            <v>章鱼小丸子</v>
+          </cell>
+          <cell r="B377">
+            <v>3172</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="A378" t="str">
+            <v>炖煮条石鲷</v>
+          </cell>
+          <cell r="B378">
+            <v>3173</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="A379" t="str">
+            <v>红鲷刺身</v>
+          </cell>
+          <cell r="B379">
+            <v>3174</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="A380" t="str">
+            <v>河豚刺身</v>
+          </cell>
+          <cell r="B380">
+            <v>3175</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="A381" t="str">
+            <v>螃蟹煲</v>
+          </cell>
+          <cell r="B381">
+            <v>3176</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="A382" t="str">
+            <v>金枪鱼刺身</v>
+          </cell>
+          <cell r="B382">
+            <v>3177</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="A383" t="str">
+            <v>龙虾鱼子酱</v>
+          </cell>
+          <cell r="B383">
+            <v>3178</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="A384" t="str">
+            <v>凉茶</v>
+          </cell>
+          <cell r="B384">
+            <v>3179</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="A385" t="str">
+            <v>回春卷轴</v>
+          </cell>
+          <cell r="B385">
+            <v>4000</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="A386" t="str">
+            <v>振奋卷轴</v>
+          </cell>
+          <cell r="B386">
+            <v>4001</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="A387" t="str">
+            <v>昏睡卷轴</v>
+          </cell>
+          <cell r="B387">
+            <v>4002</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="A388" t="str">
+            <v>感电卷轴</v>
+          </cell>
+          <cell r="B388">
+            <v>4003</v>
+          </cell>
+        </row>
+        <row r="389">
+          <cell r="A389" t="str">
+            <v>冰氛卷轴</v>
+          </cell>
+          <cell r="B389">
+            <v>4004</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="A390" t="str">
+            <v>火氛卷轴</v>
+          </cell>
+          <cell r="B390">
+            <v>4005</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="A391" t="str">
+            <v>沉默卷轴</v>
+          </cell>
+          <cell r="B391">
+            <v>4006</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="A392" t="str">
+            <v>减速卷轴</v>
+          </cell>
+          <cell r="B392">
+            <v>4007</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="A393" t="str">
+            <v>闪避卷轴</v>
+          </cell>
+          <cell r="B393">
+            <v>4008</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="A394" t="str">
+            <v>力量卷轴</v>
+          </cell>
+          <cell r="B394">
+            <v>4009</v>
+          </cell>
+        </row>
+        <row r="395">
+          <cell r="A395" t="str">
             <v>魅惑卷轴</v>
           </cell>
-          <cell r="B377">
+          <cell r="B395">
             <v>4010</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Datas/MonsterData.xlsx
+++ b/Datas/MonsterData.xlsx
@@ -5596,10 +5596,10 @@
         <v>10</v>
       </c>
       <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>2</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -5646,10 +5646,10 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -5696,10 +5696,10 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -5746,10 +5746,10 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -5796,10 +5796,10 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -5846,10 +5846,10 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -5896,10 +5896,10 @@
         <v>17</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -5946,10 +5946,10 @@
         <v>20</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -5996,10 +5996,10 @@
         <v>20</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -6046,10 +6046,10 @@
         <v>96</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E13">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -6096,10 +6096,10 @@
         <v>96</v>
       </c>
       <c r="D14">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E14">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -6146,10 +6146,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -6196,10 +6196,10 @@
         <v>38</v>
       </c>
       <c r="D16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -6246,10 +6246,10 @@
         <v>42</v>
       </c>
       <c r="D17">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -6296,10 +6296,10 @@
         <v>44</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -6346,10 +6346,10 @@
         <v>48</v>
       </c>
       <c r="D19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -6396,10 +6396,10 @@
         <v>46</v>
       </c>
       <c r="D20">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -6446,10 +6446,10 @@
         <v>50</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -6496,10 +6496,10 @@
         <v>48</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -6546,10 +6546,10 @@
         <v>228</v>
       </c>
       <c r="D23">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="E23">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -6596,10 +6596,10 @@
         <v>232</v>
       </c>
       <c r="D24">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E24">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -6646,10 +6646,10 @@
         <v>25</v>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -6696,10 +6696,10 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -6746,10 +6746,10 @@
         <v>28</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -6796,10 +6796,10 @@
         <v>28</v>
       </c>
       <c r="D28">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -6846,10 +6846,10 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -6896,10 +6896,10 @@
         <v>30</v>
       </c>
       <c r="D30">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -6946,10 +6946,10 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -6996,10 +6996,10 @@
         <v>32</v>
       </c>
       <c r="D32">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -7046,10 +7046,10 @@
         <v>150</v>
       </c>
       <c r="D33">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E33">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -7096,10 +7096,10 @@
         <v>150</v>
       </c>
       <c r="D34">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E34">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -7146,10 +7146,10 @@
         <v>56</v>
       </c>
       <c r="D35">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -7196,10 +7196,10 @@
         <v>58</v>
       </c>
       <c r="D36">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E36">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -7246,10 +7246,10 @@
         <v>60</v>
       </c>
       <c r="D37">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -7296,10 +7296,10 @@
         <v>60</v>
       </c>
       <c r="D38">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -7346,10 +7346,10 @@
         <v>64</v>
       </c>
       <c r="D39">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F39">
         <v>100</v>
@@ -7396,10 +7396,10 @@
         <v>64</v>
       </c>
       <c r="D40">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -7446,10 +7446,10 @@
         <v>64</v>
       </c>
       <c r="D41">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E41">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -7496,10 +7496,10 @@
         <v>68</v>
       </c>
       <c r="D42">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F42">
         <v>100</v>
@@ -7546,10 +7546,10 @@
         <v>336</v>
       </c>
       <c r="D43">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="E43">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="F43">
         <v>100</v>
@@ -7596,10 +7596,10 @@
         <v>340</v>
       </c>
       <c r="D44">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="E44">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="F44">
         <v>100</v>
@@ -7646,10 +7646,10 @@
         <v>70</v>
       </c>
       <c r="D45">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E45">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F45">
         <v>100</v>
@@ -7696,10 +7696,10 @@
         <v>72</v>
       </c>
       <c r="D46">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E46">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F46">
         <v>100</v>
@@ -7746,10 +7746,10 @@
         <v>72</v>
       </c>
       <c r="D47">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E47">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F47">
         <v>100</v>
@@ -7796,10 +7796,10 @@
         <v>74</v>
       </c>
       <c r="D48">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E48">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F48">
         <v>100</v>
@@ -7846,10 +7846,10 @@
         <v>74</v>
       </c>
       <c r="D49">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E49">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -7896,10 +7896,10 @@
         <v>76</v>
       </c>
       <c r="D50">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E50">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -7946,10 +7946,10 @@
         <v>76</v>
       </c>
       <c r="D51">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E51">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F51">
         <v>100</v>
@@ -7996,10 +7996,10 @@
         <v>76</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E52">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F52">
         <v>100</v>
@@ -8046,10 +8046,10 @@
         <v>420</v>
       </c>
       <c r="D53">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="E53">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="F53">
         <v>100</v>
@@ -8096,10 +8096,10 @@
         <v>432</v>
       </c>
       <c r="D54">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="E54">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="F54">
         <v>100</v>
@@ -8146,10 +8146,10 @@
         <v>92</v>
       </c>
       <c r="D55">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E55">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F55">
         <v>100</v>
@@ -8196,10 +8196,10 @@
         <v>92</v>
       </c>
       <c r="D56">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F56">
         <v>100</v>
@@ -8246,10 +8246,10 @@
         <v>96</v>
       </c>
       <c r="D57">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E57">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F57">
         <v>100</v>
@@ -8296,10 +8296,10 @@
         <v>96</v>
       </c>
       <c r="D58">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E58">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F58">
         <v>100</v>
@@ -8346,10 +8346,10 @@
         <v>100</v>
       </c>
       <c r="D59">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E59">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F59">
         <v>100</v>
@@ -8396,10 +8396,10 @@
         <v>102</v>
       </c>
       <c r="D60">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F60">
         <v>100</v>
@@ -8446,10 +8446,10 @@
         <v>104</v>
       </c>
       <c r="D61">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E61">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F61">
         <v>100</v>
@@ -8496,10 +8496,10 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E62">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F62">
         <v>100</v>
@@ -8546,10 +8546,10 @@
         <v>552</v>
       </c>
       <c r="D63">
-        <v>384</v>
+        <v>499</v>
       </c>
       <c r="E63">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c r="F63">
         <v>100</v>
@@ -8596,10 +8596,10 @@
         <v>552</v>
       </c>
       <c r="D64">
-        <v>396</v>
+        <v>515</v>
       </c>
       <c r="E64">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="F64">
         <v>100</v>
@@ -8646,10 +8646,10 @@
         <v>82</v>
       </c>
       <c r="D65">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E65">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F65">
         <v>100</v>
@@ -8696,10 +8696,10 @@
         <v>82</v>
       </c>
       <c r="D66">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E66">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F66">
         <v>100</v>
@@ -8746,10 +8746,10 @@
         <v>84</v>
       </c>
       <c r="D67">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E67">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F67">
         <v>100</v>
@@ -8796,10 +8796,10 @@
         <v>84</v>
       </c>
       <c r="D68">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E68">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F68">
         <v>100</v>
@@ -8846,10 +8846,10 @@
         <v>86</v>
       </c>
       <c r="D69">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E69">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F69">
         <v>100</v>
@@ -8896,10 +8896,10 @@
         <v>86</v>
       </c>
       <c r="D70">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E70">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F70">
         <v>100</v>
@@ -8946,10 +8946,10 @@
         <v>90</v>
       </c>
       <c r="D71">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E71">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F71">
         <v>100</v>
@@ -8996,10 +8996,10 @@
         <v>90</v>
       </c>
       <c r="D72">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E72">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F72">
         <v>100</v>
@@ -9046,10 +9046,10 @@
         <v>492</v>
       </c>
       <c r="D73">
-        <v>318</v>
+        <v>413</v>
       </c>
       <c r="E73">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="F73">
         <v>100</v>
@@ -9096,10 +9096,10 @@
         <v>492</v>
       </c>
       <c r="D74">
-        <v>330</v>
+        <v>429</v>
       </c>
       <c r="E74">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="F74">
         <v>100</v>
@@ -9146,10 +9146,10 @@
         <v>106</v>
       </c>
       <c r="D75">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E75">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F75">
         <v>100</v>
@@ -9196,10 +9196,10 @@
         <v>108</v>
       </c>
       <c r="D76">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E76">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F76">
         <v>100</v>
@@ -9246,10 +9246,10 @@
         <v>108</v>
       </c>
       <c r="D77">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E77">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F77">
         <v>100</v>
@@ -9296,10 +9296,10 @@
         <v>111</v>
       </c>
       <c r="D78">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E78">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F78">
         <v>100</v>
@@ -9346,10 +9346,10 @@
         <v>110</v>
       </c>
       <c r="D79">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E79">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F79">
         <v>100</v>
@@ -9396,10 +9396,10 @@
         <v>110</v>
       </c>
       <c r="D80">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E80">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F80">
         <v>100</v>
@@ -9446,10 +9446,10 @@
         <v>114</v>
       </c>
       <c r="D81">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E81">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F81">
         <v>100</v>
@@ -9496,10 +9496,10 @@
         <v>114</v>
       </c>
       <c r="D82">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E82">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F82">
         <v>100</v>
@@ -9546,10 +9546,10 @@
         <v>636</v>
       </c>
       <c r="D83">
-        <v>432</v>
+        <v>562</v>
       </c>
       <c r="E83">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="F83">
         <v>100</v>
@@ -9596,10 +9596,10 @@
         <v>648</v>
       </c>
       <c r="D84">
-        <v>420</v>
+        <v>546</v>
       </c>
       <c r="E84">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="F84">
         <v>100</v>
@@ -9645,7 +9645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:Q100"/>
+  <dimension ref="B3:Q183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
@@ -9752,7 +9752,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.2">
       <c r="H17" s="3" t="s">
         <v>240</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.2">
       <c r="H18" t="s">
         <v>167</v>
       </c>
@@ -9771,7 +9771,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f>C19+F19</f>
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <f>C19*0.3</f>
+        <v>0.6</v>
+      </c>
+      <c r="F19">
+        <f>ROUND(E19,0)</f>
+        <v>1</v>
+      </c>
       <c r="H19" t="s">
         <v>209</v>
       </c>
@@ -9779,7 +9794,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ref="D20:D83" si="0">C20+F20</f>
+        <v>14</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:E83" si="1">C20*0.3</f>
+        <v>3.3</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ref="F20:F83" si="2">ROUND(E20,0)</f>
+        <v>3</v>
+      </c>
       <c r="H20" t="s">
         <v>211</v>
       </c>
@@ -9787,7 +9817,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
       <c r="H21" t="s">
         <v>210</v>
       </c>
@@ -9795,7 +9840,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>3.3</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
       <c r="H22" s="3" t="s">
         <v>250</v>
       </c>
@@ -9806,7 +9866,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
       <c r="H23" t="s">
         <v>152</v>
       </c>
@@ -9814,7 +9889,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
       <c r="H24" t="s">
         <v>201</v>
       </c>
@@ -9822,7 +9912,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
       <c r="H25" t="s">
         <v>204</v>
       </c>
@@ -9830,7 +9935,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
       <c r="H26" t="s">
         <v>149</v>
       </c>
@@ -9838,7 +9958,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="1"/>
+        <v>4.8</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="H27" t="s">
         <v>187</v>
       </c>
@@ -9846,7 +9981,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>40</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
       <c r="H28" t="s">
         <v>121</v>
       </c>
@@ -9854,7 +10004,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="1"/>
+        <v>12.6</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
       <c r="H29" t="s">
         <v>184</v>
       </c>
@@ -9862,7 +10027,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>24</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="1"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="H30" t="s">
         <v>155</v>
       </c>
@@ -9870,7 +10050,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>7.8</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="H31" t="s">
         <v>196</v>
       </c>
@@ -9878,7 +10073,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C32">
+        <v>28</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="1"/>
+        <v>8.4</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="H32" s="3" t="s">
         <v>252</v>
       </c>
@@ -9889,7 +10099,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C33">
+        <v>26</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="1"/>
+        <v>7.8</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="H33" t="s">
         <v>192</v>
       </c>
@@ -9897,7 +10122,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="1"/>
+        <v>8.4</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
       <c r="H34" t="s">
         <v>116</v>
       </c>
@@ -9905,7 +10145,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="H35" t="s">
         <v>231</v>
       </c>
@@ -9913,7 +10168,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C36">
+        <v>31</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="1"/>
+        <v>9.2999999999999989</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="H36" s="1" t="s">
         <v>180</v>
       </c>
@@ -9921,7 +10191,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C37">
+        <v>33</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="1"/>
+        <v>9.9</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
       <c r="H37" t="s">
         <v>170</v>
       </c>
@@ -9929,7 +10214,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C38">
+        <v>156</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>203</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="1"/>
+        <v>46.8</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
       <c r="H38" t="s">
         <v>134</v>
       </c>
@@ -9937,7 +10237,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C39">
+        <v>150</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
       <c r="H39" t="s">
         <v>179</v>
       </c>
@@ -9945,7 +10260,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C40">
+        <v>17</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="H40" t="s">
         <v>169</v>
       </c>
@@ -9953,7 +10283,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C41">
+        <v>16</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="1"/>
+        <v>4.8</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
       <c r="H41" t="s">
         <v>129</v>
       </c>
@@ -9961,7 +10306,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C42">
+        <v>19</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>5.7</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
       <c r="H42" t="s">
         <v>191</v>
       </c>
@@ -9969,7 +10329,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
       <c r="H43" t="s">
         <v>186</v>
       </c>
@@ -9977,7 +10352,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>22</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>6.6</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="H44" t="s">
         <v>130</v>
       </c>
@@ -9985,7 +10375,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C45">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>6.6</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="H45" t="s">
         <v>189</v>
       </c>
@@ -9993,7 +10398,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C46">
+        <v>20</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
       <c r="H46" t="s">
         <v>164</v>
       </c>
@@ -10001,7 +10421,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C47">
+        <v>22</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>6.6</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
       <c r="H47" t="s">
         <v>168</v>
       </c>
@@ -10009,7 +10444,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="7:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C48">
+        <v>102</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>30.599999999999998</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
       <c r="G48">
         <v>2</v>
       </c>
@@ -10023,7 +10473,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C49">
+        <v>106</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="1"/>
+        <v>31.799999999999997</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
       <c r="H49" t="s">
         <v>208</v>
       </c>
@@ -10031,7 +10496,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C50">
+        <v>34</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="1"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
       <c r="H50" s="3" t="s">
         <v>254</v>
       </c>
@@ -10042,7 +10522,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C51">
+        <v>30</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
       <c r="H51" t="s">
         <v>198</v>
       </c>
@@ -10050,7 +10545,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>36</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="1"/>
+        <v>10.799999999999999</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="H52" t="s">
         <v>181</v>
       </c>
@@ -10058,7 +10568,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C53">
+        <v>35</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="H53" t="s">
         <v>174</v>
       </c>
@@ -10066,7 +10591,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C54">
+        <v>36</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="1"/>
+        <v>10.799999999999999</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="H54" t="s">
         <v>199</v>
       </c>
@@ -10074,7 +10614,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C55">
+        <v>34</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="1"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
       <c r="H55" t="s">
         <v>163</v>
       </c>
@@ -10082,7 +10637,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C56">
+        <v>40</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
       <c r="H56" t="s">
         <v>154</v>
       </c>
@@ -10090,7 +10660,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C57">
+        <v>38</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="1"/>
+        <v>11.4</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
       <c r="H57" t="s">
         <v>153</v>
       </c>
@@ -10098,7 +10683,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C58">
+        <v>204</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>265</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="1"/>
+        <v>61.199999999999996</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
       <c r="H58" t="s">
         <v>195</v>
       </c>
@@ -10106,7 +10706,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C59">
+        <v>208</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="1"/>
+        <v>62.4</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
       <c r="H59" t="s">
         <v>185</v>
       </c>
@@ -10114,7 +10729,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C60">
+        <v>42</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="1"/>
+        <v>12.6</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
       <c r="H60" t="s">
         <v>148</v>
       </c>
@@ -10122,7 +10752,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C61">
+        <v>40</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
       <c r="H61" t="s">
         <v>158</v>
       </c>
@@ -10130,7 +10775,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>46</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="1"/>
+        <v>13.799999999999999</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
       <c r="H62" t="s">
         <v>239</v>
       </c>
@@ -10138,7 +10798,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C63">
+        <v>44</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="1"/>
+        <v>13.2</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
       <c r="H63" t="s">
         <v>194</v>
       </c>
@@ -10147,7 +10822,22 @@
       </c>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C64">
+        <v>48</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="1"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
       <c r="H64" t="s">
         <v>205</v>
       </c>
@@ -10155,7 +10845,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>44</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="1"/>
+        <v>13.2</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
       <c r="H65" s="2" t="s">
         <v>242</v>
       </c>
@@ -10166,7 +10871,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C66">
+        <v>48</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="1"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
       <c r="H66" s="3" t="s">
         <v>255</v>
       </c>
@@ -10177,7 +10897,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>50</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
       <c r="H67" s="2" t="s">
         <v>243</v>
       </c>
@@ -10188,7 +10923,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C68">
+        <v>252</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="0"/>
+        <v>328</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="1"/>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
       <c r="H68" s="3" t="s">
         <v>256</v>
       </c>
@@ -10199,7 +10949,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C69">
+        <v>240</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="0"/>
+        <v>312</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
       <c r="H69" t="s">
         <v>122</v>
       </c>
@@ -10207,7 +10972,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C70">
+        <v>64</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="1"/>
+        <v>19.2</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
       <c r="H70" s="2" t="s">
         <v>244</v>
       </c>
@@ -10218,7 +10998,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C71">
+        <v>66</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="1"/>
+        <v>19.8</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H71" t="s">
         <v>220</v>
       </c>
@@ -10226,7 +11021,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C72">
+        <v>66</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="1"/>
+        <v>19.8</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H72" s="2" t="s">
         <v>245</v>
       </c>
@@ -10237,7 +11047,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C73">
+        <v>68</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="1"/>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H73" s="6" t="s">
         <v>241</v>
       </c>
@@ -10246,7 +11071,22 @@
       </c>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C74">
+        <v>66</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="1"/>
+        <v>19.8</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H74" s="2" t="s">
         <v>246</v>
       </c>
@@ -10257,7 +11097,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C75">
+        <v>68</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="1"/>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H75" t="s">
         <v>162</v>
       </c>
@@ -10265,7 +11120,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C76">
+        <v>70</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
       <c r="H76" t="s">
         <v>156</v>
       </c>
@@ -10273,7 +11143,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C77">
+        <v>68</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="1"/>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
       <c r="H77" t="s">
         <v>146</v>
       </c>
@@ -10281,7 +11166,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C78">
+        <v>384</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="0"/>
+        <v>499</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="1"/>
+        <v>115.19999999999999</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
       <c r="H78" t="s">
         <v>234</v>
       </c>
@@ -10289,7 +11189,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C79">
+        <v>396</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="0"/>
+        <v>515</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="1"/>
+        <v>118.8</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="2"/>
+        <v>119</v>
+      </c>
       <c r="H79" s="2" t="s">
         <v>190</v>
       </c>
@@ -10300,7 +11215,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C80">
+        <v>53</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="1"/>
+        <v>15.899999999999999</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
       <c r="H80" t="s">
         <v>176</v>
       </c>
@@ -10308,7 +11238,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C81">
+        <v>55</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
       <c r="H81" t="s">
         <v>222</v>
       </c>
@@ -10316,7 +11261,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C82">
+        <v>55</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
       <c r="H82" t="s">
         <v>131</v>
       </c>
@@ -10324,7 +11284,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C83">
+        <v>53</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="1"/>
+        <v>15.899999999999999</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
       <c r="H83" t="s">
         <v>171</v>
       </c>
@@ -10332,7 +11307,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C84">
+        <v>56</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84:D100" si="3">C84+F84</f>
+        <v>73</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ref="E84:E99" si="4">C84*0.3</f>
+        <v>16.8</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ref="F84:F100" si="5">ROUND(E84,0)</f>
+        <v>17</v>
+      </c>
       <c r="H84" t="s">
         <v>151</v>
       </c>
@@ -10340,7 +11330,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C85">
+        <v>54</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="4"/>
+        <v>16.2</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
       <c r="H85" s="2" t="s">
         <v>173</v>
       </c>
@@ -10351,7 +11356,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C86">
+        <v>58</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="4"/>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
       <c r="H86" t="s">
         <v>227</v>
       </c>
@@ -10359,7 +11379,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C87">
+        <v>60</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
       <c r="H87" s="2" t="s">
         <v>200</v>
       </c>
@@ -10370,7 +11405,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C88">
+        <v>318</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="3"/>
+        <v>413</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="4"/>
+        <v>95.399999999999991</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
       <c r="H88" t="s">
         <v>177</v>
       </c>
@@ -10378,7 +11428,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C89">
+        <v>330</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="3"/>
+        <v>429</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="4"/>
+        <v>99</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="5"/>
+        <v>99</v>
+      </c>
       <c r="H89" s="2" t="s">
         <v>188</v>
       </c>
@@ -10389,7 +11454,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C90">
+        <v>72</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="3"/>
+        <v>94</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="4"/>
+        <v>21.599999999999998</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
       <c r="H90" s="2" t="s">
         <v>248</v>
       </c>
@@ -10397,7 +11477,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C91">
+        <v>70</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
       <c r="H91" t="s">
         <v>203</v>
       </c>
@@ -10405,7 +11500,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C92">
+        <v>74</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="4"/>
+        <v>22.2</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
       <c r="H92" t="s">
         <v>206</v>
       </c>
@@ -10413,7 +11523,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C93">
+        <v>70</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
       <c r="H93" t="s">
         <v>216</v>
       </c>
@@ -10421,7 +11546,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C94">
+        <v>76</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="4"/>
+        <v>22.8</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
       <c r="H94" s="2" t="s">
         <v>128</v>
       </c>
@@ -10429,7 +11569,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C95">
+        <v>78</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="3"/>
+        <v>101</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="4"/>
+        <v>23.4</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
       <c r="H95" t="s">
         <v>172</v>
       </c>
@@ -10437,7 +11592,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C96">
+        <v>78</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="3"/>
+        <v>101</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="4"/>
+        <v>23.4</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
       <c r="H96" t="s">
         <v>136</v>
       </c>
@@ -10448,7 +11618,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C97">
+        <v>76</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="4"/>
+        <v>22.8</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
       <c r="H97" t="s">
         <v>202</v>
       </c>
@@ -10456,7 +11641,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C98">
+        <v>432</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="3"/>
+        <v>562</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="4"/>
+        <v>129.6</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="5"/>
+        <v>130</v>
+      </c>
       <c r="H98" t="s">
         <v>217</v>
       </c>
@@ -10467,7 +11667,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C99">
+        <v>420</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="3"/>
+        <v>546</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="4"/>
+        <v>126</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="5"/>
+        <v>126</v>
+      </c>
       <c r="H99" t="s">
         <v>221</v>
       </c>
@@ -10475,12 +11690,1397 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="D100">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="H100" s="4" t="s">
         <v>247</v>
       </c>
       <c r="I100" s="5">
         <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103">
+        <f>C103-F103</f>
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <f>C103*0.25</f>
+        <v>0.75</v>
+      </c>
+      <c r="F103">
+        <f>ROUND(E103,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C104">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <f t="shared" ref="D104:D167" si="6">C104-F104</f>
+        <v>7</v>
+      </c>
+      <c r="E104">
+        <f t="shared" ref="E104:E167" si="7">C104*0.25</f>
+        <v>2.25</v>
+      </c>
+      <c r="F104">
+        <f t="shared" ref="F104:F167" si="8">ROUND(E104,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C105">
+        <v>8</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C106">
+        <v>11</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="7"/>
+        <v>2.75</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C107">
+        <v>9</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="7"/>
+        <v>2.25</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C108">
+        <v>11</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="7"/>
+        <v>2.75</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C109">
+        <v>12</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C110">
+        <v>14</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="7"/>
+        <v>3.5</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C111">
+        <v>12</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C112">
+        <v>44</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C113">
+        <v>42</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="6"/>
+        <v>31</v>
+      </c>
+      <c r="E113">
+        <f t="shared" si="7"/>
+        <v>10.5</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C114">
+        <v>24</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C115">
+        <v>24</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E115">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C116">
+        <v>24</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E116">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C117">
+        <v>24</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E117">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C118">
+        <v>24</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E118">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C119">
+        <v>24</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E119">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C120">
+        <v>25</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="E120">
+        <f t="shared" si="7"/>
+        <v>6.25</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C121">
+        <v>25</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="E121">
+        <f t="shared" si="7"/>
+        <v>6.25</v>
+      </c>
+      <c r="F121">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C122">
+        <v>144</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="6"/>
+        <v>108</v>
+      </c>
+      <c r="E122">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="F122">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C123">
+        <v>146</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="6"/>
+        <v>109</v>
+      </c>
+      <c r="E123">
+        <f t="shared" si="7"/>
+        <v>36.5</v>
+      </c>
+      <c r="F123">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="124" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C124">
+        <v>16</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="E124">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="F124">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C125">
+        <v>17</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="E125">
+        <f t="shared" si="7"/>
+        <v>4.25</v>
+      </c>
+      <c r="F125">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C126">
+        <v>17</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="E126">
+        <f t="shared" si="7"/>
+        <v>4.25</v>
+      </c>
+      <c r="F126">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C127">
+        <v>16</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="E127">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="F127">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C128">
+        <v>16</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="E128">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C129">
+        <v>18</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="E129">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="F129">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C130">
+        <v>24</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E130">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F130">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C131">
+        <v>22</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="E131">
+        <f t="shared" si="7"/>
+        <v>5.5</v>
+      </c>
+      <c r="F131">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C132">
+        <v>96</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
+      <c r="E132">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="F132">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C133">
+        <v>92</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="6"/>
+        <v>69</v>
+      </c>
+      <c r="E133">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="F133">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C134">
+        <v>28</v>
+      </c>
+      <c r="D134">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="E134">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F134">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C135">
+        <v>30</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E135">
+        <f t="shared" si="7"/>
+        <v>7.5</v>
+      </c>
+      <c r="F135">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C136">
+        <v>28</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="E136">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F136">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C137">
+        <v>29</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E137">
+        <f t="shared" si="7"/>
+        <v>7.25</v>
+      </c>
+      <c r="F137">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C138">
+        <v>30</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E138">
+        <f t="shared" si="7"/>
+        <v>7.5</v>
+      </c>
+      <c r="F138">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C139">
+        <v>32</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="E139">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F139">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C140">
+        <v>32</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="E140">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F140">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C141">
+        <v>30</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E141">
+        <f t="shared" si="7"/>
+        <v>7.5</v>
+      </c>
+      <c r="F141">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C142">
+        <v>168</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="6"/>
+        <v>126</v>
+      </c>
+      <c r="E142">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="F142">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C143">
+        <v>160</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="6"/>
+        <v>120</v>
+      </c>
+      <c r="E143">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="F143">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="144" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C144">
+        <v>36</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E144">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F144">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C145">
+        <v>36</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E145">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F145">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C146">
+        <v>36</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E146">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F146">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C147">
+        <v>36</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E147">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F147">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C148">
+        <v>38</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="E148">
+        <f t="shared" si="7"/>
+        <v>9.5</v>
+      </c>
+      <c r="F148">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C149">
+        <v>40</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="E149">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="F149">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C150">
+        <v>38</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="E150">
+        <f t="shared" si="7"/>
+        <v>9.5</v>
+      </c>
+      <c r="F150">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C151">
+        <v>40</v>
+      </c>
+      <c r="D151">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="E151">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="F151">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C152">
+        <v>216</v>
+      </c>
+      <c r="D152">
+        <f t="shared" si="6"/>
+        <v>162</v>
+      </c>
+      <c r="E152">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="F152">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="153" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C153">
+        <v>216</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="6"/>
+        <v>162</v>
+      </c>
+      <c r="E153">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="F153">
+        <f t="shared" si="8"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="154" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C154">
+        <v>52</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+      <c r="E154">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="F154">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C155">
+        <v>50</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
+      <c r="E155">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="F155">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C156">
+        <v>52</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+      <c r="E156">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="F156">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C157">
+        <v>50</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
+      <c r="E157">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="F157">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C158">
+        <v>54</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="E158">
+        <f t="shared" si="7"/>
+        <v>13.5</v>
+      </c>
+      <c r="F158">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C159">
+        <v>50</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
+      <c r="E159">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="F159">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C160">
+        <v>52</v>
+      </c>
+      <c r="D160">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+      <c r="E160">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="F160">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C161">
+        <v>56</v>
+      </c>
+      <c r="D161">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+      <c r="E161">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="F161">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C162">
+        <v>312</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="6"/>
+        <v>234</v>
+      </c>
+      <c r="E162">
+        <f t="shared" si="7"/>
+        <v>78</v>
+      </c>
+      <c r="F162">
+        <f t="shared" si="8"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="163" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C163">
+        <v>300</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="E163">
+        <f t="shared" si="7"/>
+        <v>75</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="164" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C164">
+        <v>43</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="E164">
+        <f t="shared" si="7"/>
+        <v>10.75</v>
+      </c>
+      <c r="F164">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C165">
+        <v>41</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="6"/>
+        <v>31</v>
+      </c>
+      <c r="E165">
+        <f t="shared" si="7"/>
+        <v>10.25</v>
+      </c>
+      <c r="F165">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C166">
+        <v>45</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+      <c r="E166">
+        <f t="shared" si="7"/>
+        <v>11.25</v>
+      </c>
+      <c r="F166">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C167">
+        <v>47</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="E167">
+        <f t="shared" si="7"/>
+        <v>11.75</v>
+      </c>
+      <c r="F167">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C168">
+        <v>48</v>
+      </c>
+      <c r="D168">
+        <f t="shared" ref="D168:D183" si="9">C168-F168</f>
+        <v>36</v>
+      </c>
+      <c r="E168">
+        <f t="shared" ref="E168:E183" si="10">C168*0.25</f>
+        <v>12</v>
+      </c>
+      <c r="F168">
+        <f t="shared" ref="F168:F183" si="11">ROUND(E168,0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C169">
+        <v>50</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="9"/>
+        <v>37</v>
+      </c>
+      <c r="E169">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="F169">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C170">
+        <v>48</v>
+      </c>
+      <c r="D170">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="E170">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="F170">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C171">
+        <v>46</v>
+      </c>
+      <c r="D171">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="E171">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="F171">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C172">
+        <v>258</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="9"/>
+        <v>193</v>
+      </c>
+      <c r="E172">
+        <f t="shared" si="10"/>
+        <v>64.5</v>
+      </c>
+      <c r="F172">
+        <f t="shared" si="11"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="173" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C173">
+        <v>246</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="9"/>
+        <v>184</v>
+      </c>
+      <c r="E173">
+        <f t="shared" si="10"/>
+        <v>61.5</v>
+      </c>
+      <c r="F173">
+        <f t="shared" si="11"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="174" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C174">
+        <v>60</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E174">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="F174">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C175">
+        <v>60</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E175">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="F175">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C176">
+        <v>62</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="9"/>
+        <v>46</v>
+      </c>
+      <c r="E176">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="F176">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C177">
+        <v>63</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="9"/>
+        <v>47</v>
+      </c>
+      <c r="E177">
+        <f t="shared" si="10"/>
+        <v>15.75</v>
+      </c>
+      <c r="F177">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C178">
+        <v>64</v>
+      </c>
+      <c r="D178">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="E178">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="F178">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C179">
+        <v>62</v>
+      </c>
+      <c r="D179">
+        <f t="shared" si="9"/>
+        <v>46</v>
+      </c>
+      <c r="E179">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="F179">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C180">
+        <v>64</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="E180">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="F180">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C181">
+        <v>66</v>
+      </c>
+      <c r="D181">
+        <f t="shared" si="9"/>
+        <v>49</v>
+      </c>
+      <c r="E181">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="F181">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C182">
+        <v>360</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="9"/>
+        <v>270</v>
+      </c>
+      <c r="E182">
+        <f t="shared" si="10"/>
+        <v>90</v>
+      </c>
+      <c r="F182">
+        <f t="shared" si="11"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="183" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C183">
+        <v>360</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="9"/>
+        <v>270</v>
+      </c>
+      <c r="E183">
+        <f t="shared" si="10"/>
+        <v>90</v>
+      </c>
+      <c r="F183">
+        <f t="shared" si="11"/>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
